--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 5/26/26, 2:42 PM</t>
+          <t>Date Export: 5/26/26, 3:46 PM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260526_1351320</t>
+          <t>SR_VTP_20260526_1351314</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Creación Diseño de Enlace Microondas CAJ0613-CAJ5517 D=0.9m</t>
+          <t>OFICIO N° 7213-2026-MTC/19.03 / INSPECCIÓN CONJUNTA</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1377,22 +1377,22 @@
       </c>
       <c r="P12" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q12" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "Less than 80"</t>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
-          <t>vtp_jhon.flores</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Provinces|VTP - LAM Branch|VTP LAM-Project Team</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="U12" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 09:55:00</t>
+          <t>26/05/2026 09:32:00</t>
         </is>
       </c>
       <c r="V12" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 10:08:00</t>
+          <t>26/05/2026 10:00:00</t>
         </is>
       </c>
       <c r="W12" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 10:08:00</t>
+          <t>04/06/2026 10:00:00</t>
         </is>
       </c>
       <c r="X12" s="8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260526_1351314</t>
+          <t>SR_VTP_20260525_1351238</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>OFICIO N° 7213-2026-MTC/19.03 / INSPECCIÓN CONJUNTA</t>
+          <t>UPDATE // OFICIO Nº 5223-2026-MTC/19.03 // presupuesto y cronograma // DEADLINE 03/06</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="Q13" s="8" t="inlineStr">
         <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
+          <t>Review letters of interference/notification/information about BITEL optical cable</t>
         </is>
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>vtp_nayeli.casas</t>
         </is>
       </c>
       <c r="S13" s="8" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="U13" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 09:32:00</t>
+          <t>25/05/2026 17:40:00</t>
         </is>
       </c>
       <c r="V13" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 10:00:00</t>
+          <t>25/05/2026 18:08:00</t>
         </is>
       </c>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t>04/06/2026 10:00:00</t>
+          <t>29/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X13" s="8" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1351238</t>
+          <t>SR_VTP_20260525_1351160</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>UPDATE // OFICIO Nº 5223-2026-MTC/19.03 // presupuesto y cronograma // DEADLINE 03/06</t>
+          <t>SME_SOLARLED_ACTUALIZACION DE DISEÑO MW_30 mbps</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1757,22 +1757,22 @@
       </c>
       <c r="P14" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q14" s="8" t="inlineStr">
         <is>
-          <t>Review letters of interference/notification/information about BITEL optical cable</t>
+          <t>Design/Redesign Corp MW links</t>
         </is>
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t>vtp_nayeli.casas</t>
+          <t>vtp_alexis.patrocinio</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Quality Service Department</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -1782,17 +1782,17 @@
       </c>
       <c r="U14" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 17:40:00</t>
+          <t>25/05/2026 15:53:00</t>
         </is>
       </c>
       <c r="V14" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 18:08:00</t>
+          <t>25/05/2026 16:13:00</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 08:00:00</t>
+          <t>28/05/2026 16:13:00</t>
         </is>
       </c>
       <c r="X14" s="8" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AG14" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*</t>
         </is>
       </c>
       <c r="AH14" s="8" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1351160</t>
+          <t>SR_VTP_20260525_1351178</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>vtp_alexis.patrocinio</t>
+          <t>vtp_edgar.arteaga</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Quality Service Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 15:53:00</t>
+          <t>25/05/2026 15:34:00</t>
         </is>
       </c>
       <c r="V15" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 16:13:00</t>
+          <t>25/05/2026 16:02:00</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 16:13:00</t>
+          <t>28/05/2026 16:02:00</t>
         </is>
       </c>
       <c r="X15" s="8" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1351178</t>
+          <t>SR_VTP_20260525_1351132</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>SME_SOLARLED_ACTUALIZACION DE DISEÑO MW_30 mbps</t>
+          <t>SOLICITO LLENADO DE INFORMACIÓN TECNICA DE CADA PROVINCIA Y DEPARTAMENTO - INFORMACIÓN REQUERIDA POR OSIPTEL - DEADLINE 26/5/2026</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t/>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="O16" s="8" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q16" s="8" t="inlineStr">
         <is>
-          <t>Design/Redesign Corp MW links</t>
+          <t>Review letters of interference/notification/information about BITEL optical cable</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>vtp_edgar.arteaga</t>
+          <t>vtp_nayeli.casas</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -2162,17 +2162,17 @@
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 15:34:00</t>
+          <t>25/05/2026 15:14:00</t>
         </is>
       </c>
       <c r="V16" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 16:02:00</t>
+          <t>25/05/2026 15:27:00</t>
         </is>
       </c>
       <c r="W16" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 16:02:00</t>
+          <t>28/05/2026 15:27:00</t>
         </is>
       </c>
       <c r="X16" s="8" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AG16" s="8" t="inlineStr">
         <is>
-          <t>*</t>
+          <t/>
         </is>
       </c>
       <c r="AH16" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1351132</t>
+          <t>SR_VTP_20260525_1350968</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>SOLICITO LLENADO DE INFORMACIÓN TECNICA DE CADA PROVINCIA Y DEPARTAMENTO - INFORMACIÓN REQUERIDA POR OSIPTEL - DEADLINE 26/5/2026</t>
+          <t>SE SOLICITA SE BRINDE FECHA DE INICIO DE TRABAJOS / PROYECTO: PUENTE MOCHE / CONVENIO STRACOM BESALCO</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="O17" s="8" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>Review letters of interference/notification/information about BITEL optical cable</t>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>vtp_nayeli.casas</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
@@ -2352,17 +2352,17 @@
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 15:14:00</t>
+          <t>25/05/2026 10:16:00</t>
         </is>
       </c>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 15:27:00</t>
+          <t>25/05/2026 10:40:00</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 15:27:00</t>
+          <t>03/06/2026 10:40:00</t>
         </is>
       </c>
       <c r="X17" s="8" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1350968</t>
+          <t>SR_VTP_20260522_1350607</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>SE SOLICITA SE BRINDE FECHA DE INICIO DE TRABAJOS / PROYECTO: PUENTE MOCHE / CONVENIO STRACOM BESALCO</t>
+          <t>TECHNICAL EVALUATION ML Q3-Q4 CORP CABLE 4FO, 12FO, 8FO</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2517,22 +2517,22 @@
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_TRANS_Bidding</t>
         </is>
       </c>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
+          <t>TRANS - Technical review for biddings</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>vtp_alisson.astudillo</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2542,17 +2542,17 @@
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 10:16:00</t>
+          <t>22/05/2026 19:24:00</t>
         </is>
       </c>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 10:40:00</t>
+          <t>22/05/2026 19:53:00</t>
         </is>
       </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 10:40:00</t>
+          <t>01/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X18" s="8" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260522_1350607</t>
+          <t>SR_VTP_20260522_1350563</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>TECHNICAL EVALUATION ML Q3-Q4 CORP CABLE 4FO, 12FO, 8FO</t>
+          <t>PROYECTO MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>28.06</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>VTP_TRANS_Bidding</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>TRANS - Technical review for biddings</t>
+          <t>Design transmission for corporate customers (&gt; 500 Link)</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>vtp_alisson.astudillo</t>
+          <t>vtp_gerardo.alvarado</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 19:24:00</t>
+          <t>22/05/2026 16:42:00</t>
         </is>
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 19:53:00</t>
+          <t>22/05/2026 17:11:00</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 08:00:00</t>
+          <t>06/07/2026 17:11:00</t>
         </is>
       </c>
       <c r="X19" s="8" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260522_1350563</t>
+          <t>SR_VTP_20260522_1350426</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>PROYECTO MINISTERIO PUBLICO</t>
+          <t>SAMPLES EVALUATION</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t/>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -2902,17 +2902,17 @@
       </c>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 500 Link)</t>
+          <t>Technical review for biddings</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>vtp_gerardo.alvarado</t>
+          <t>vtp_judith.araujo</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 16:42:00</t>
+          <t>22/05/2026 12:46:00</t>
         </is>
       </c>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 17:11:00</t>
+          <t>22/05/2026 13:13:00</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>06/07/2026 17:11:00</t>
+          <t>02/06/2026 13:13:00</t>
         </is>
       </c>
       <c r="X20" s="8" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260522_1350426</t>
+          <t>SR_VTP_20260521_1350241</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>SAMPLES EVALUATION</t>
+          <t>TECHNICAL EVALUATION - No. 052026/VTPr-Grapa Conica</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="P21" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_TRANS_Bidding</t>
         </is>
       </c>
       <c r="Q21" s="8" t="inlineStr">
         <is>
-          <t>Technical review for biddings</t>
+          <t>TRANS - Technical review for biddings</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
@@ -3112,17 +3112,17 @@
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 12:46:00</t>
+          <t>21/05/2026 17:52:00</t>
         </is>
       </c>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 13:13:00</t>
+          <t>21/05/2026 18:21:00</t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>02/06/2026 13:13:00</t>
+          <t>29/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X21" s="8" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260521_1350241</t>
+          <t>SR_VTP_20260521_1349917</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>TECHNICAL EVALUATION - No. 052026/VTPr-Grapa Conica</t>
+          <t>UPDATE // OFICIO N° 4196-2026-MTC/19.03 // REITERATIVO DE PRESUPUESTO Y CRONOGRAMA - PROYECTO MOCCUPE - PLAZO VENCIDO 20/5/2026</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_bryam.broncano</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -3252,17 +3252,17 @@
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
@@ -3277,22 +3277,22 @@
       </c>
       <c r="P22" s="8" t="inlineStr">
         <is>
-          <t>VTP_TRANS_Bidding</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t>TRANS - Technical review for biddings</t>
+          <t>Review letters of interference/notification/information about BITEL optical cable</t>
         </is>
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>vtp_judith.araujo</t>
+          <t>vtp_nayeli.casas</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -3302,22 +3302,22 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 17:52:00</t>
+          <t>21/05/2026 08:02:00</t>
         </is>
       </c>
       <c r="V22" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 18:21:00</t>
+          <t>21/05/2026 08:31:00</t>
         </is>
       </c>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 08:00:00</t>
+          <t>26/05/2026 08:31:00</t>
         </is>
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>21/05/2026 14:29:00</t>
         </is>
       </c>
       <c r="Y22" s="8" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AA22" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">2026-05-21 14:30:09.873 : [1]Nhận xét | Comments || N/A || esta pendiente de firma de mr tien 2026-05-25 14:12:44.999 : [1]Nhận xét | Comments || N/A || se ha solicitado q partner baje precios </t>
         </is>
       </c>
       <c r="AB22" s="8" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="AG22" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*</t>
         </is>
       </c>
       <c r="AH22" s="8" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AI22" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>esta pendiente de firma de mr tien,se ha solicitado q partner baje precios</t>
         </is>
       </c>
       <c r="AJ22" s="8" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260521_1349917</t>
+          <t>SR_VTP_20260518_1349100</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>UPDATE // OFICIO N° 4196-2026-MTC/19.03 // REITERATIVO DE PRESUPUESTO Y CRONOGRAMA - PROYECTO MOCCUPE - PLAZO VENCIDO 20/5/2026</t>
+          <t>OXI_Ucayali Project - SMART CITY &amp; DARK FIBER &amp; INTERNET SERVICE - 101 sites</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>vtp_bryam.broncano</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -3442,24 +3442,24 @@
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
       <c r="O23" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
@@ -3467,22 +3467,22 @@
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q23" s="8" t="inlineStr">
         <is>
-          <t>Review letters of interference/notification/information about BITEL optical cable</t>
+          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
         </is>
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>vtp_nayeli.casas</t>
+          <t>vtp_julio.inga</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -3492,22 +3492,22 @@
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 08:02:00</t>
+          <t>18/05/2026 11:34:00</t>
         </is>
       </c>
       <c r="V23" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 08:31:00</t>
+          <t>18/05/2026 12:03:00</t>
         </is>
       </c>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 08:31:00</t>
+          <t>08/06/2026 12:03:00</t>
         </is>
       </c>
       <c r="X23" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 14:29:00</t>
+          <t/>
         </is>
       </c>
       <c r="Y23" s="8" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AA23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-21 14:30:09.873 : [1]Nhận xét | Comments || N/A || esta pendiente de firma de mr tien 2026-05-25 14:12:44.999 : [1]Nhận xét | Comments || N/A || se ha solicitado q partner baje precios </t>
+          <t/>
         </is>
       </c>
       <c r="AB23" s="8" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AG23" s="8" t="inlineStr">
         <is>
-          <t>*</t>
+          <t/>
         </is>
       </c>
       <c r="AH23" s="8" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AI23" s="8" t="inlineStr">
         <is>
-          <t>esta pendiente de firma de mr tien,se ha solicitado q partner baje precios</t>
+          <t/>
         </is>
       </c>
       <c r="AJ23" s="8" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260518_1349100</t>
+          <t>SR_VTP_20260525_1351186</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -3597,17 +3597,17 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>OXI_Ucayali Project - SMART CITY &amp; DARK FIBER &amp; INTERNET SERVICE - 101 sites</t>
+          <t>CAJ0222-CAJ2004_1  Recover monitor of link 1, Upgrade MW by configuration to 512QAM,  *</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr">
@@ -3662,17 +3662,17 @@
       </c>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
+          <t>Design/Redesign Metro MW links</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>vtp_julio.inga</t>
+          <t>vtp_kathy.valle</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -3682,22 +3682,22 @@
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 11:34:00</t>
+          <t>25/05/2026 15:48:00</t>
         </is>
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 12:03:00</t>
+          <t>25/05/2026 16:16:00</t>
         </is>
       </c>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 12:03:00</t>
+          <t>28/05/2026 16:16:00</t>
         </is>
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>26/05/2026 12:46:00</t>
         </is>
       </c>
       <c r="Y24" s="8" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AA24" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">2026-05-26 12:47:09.621 : [1]Nhận xét | Comments || N/A || Incorrect unit </t>
         </is>
       </c>
       <c r="AB24" s="8" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AI24" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>Incorrect unit</t>
         </is>
       </c>
       <c r="AJ24" s="8" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1351186</t>
+          <t>SR_VTP_20260518_1349058</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>CAJ0222-CAJ2004_1  Recover monitor of link 1, Upgrade MW by configuration to 512QAM,  *</t>
+          <t>FACTIBILIDAD MINEDU 1K</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="O25" s="8" t="inlineStr">
@@ -3852,17 +3852,17 @@
       </c>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>Design/Redesign Metro MW links</t>
+          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>vtp_kathy.valle</t>
+          <t>vtp_thangnq1</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -3872,22 +3872,22 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 15:48:00</t>
+          <t>18/05/2026 10:46:00</t>
         </is>
       </c>
       <c r="V25" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 16:16:00</t>
+          <t>18/05/2026 11:15:00</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 16:16:00</t>
+          <t>08/06/2026 11:15:00</t>
         </is>
       </c>
       <c r="X25" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 12:46:00</t>
+          <t>18/05/2026 14:31:00</t>
         </is>
       </c>
       <c r="Y25" s="8" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AA25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26 12:47:09.621 : [1]Nhận xét | Comments || N/A || Incorrect unit </t>
+          <t xml:space="preserve">2026-05-18 14:31:19.315 : [1]Nhận xét | Comments || N/A || Elegir las categoria &gt; 500 links </t>
         </is>
       </c>
       <c r="AB25" s="8" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AI25" s="8" t="inlineStr">
         <is>
-          <t>Incorrect unit</t>
+          <t>Elegir las categoria &gt; 500 links</t>
         </is>
       </c>
       <c r="AJ25" s="8" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260518_1349058</t>
+          <t>SR_VTP_20260511_1347286</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>FACTIBILIDAD MINEDU 1K</t>
+          <t>KCS Testing at MInka WH for IMP-2987 03/2026/VTPr-VMC/CABLE 24FO-ML2026</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -4037,22 +4037,22 @@
       </c>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_DWDM</t>
         </is>
       </c>
       <c r="Q26" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
+          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>vtp_thangnq1</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -4062,22 +4062,22 @@
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 10:46:00</t>
+          <t>11/05/2026 17:56:00</t>
         </is>
       </c>
       <c r="V26" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 11:15:00</t>
+          <t>11/05/2026 18:23:00</t>
         </is>
       </c>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 11:15:00</t>
+          <t>18/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X26" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 14:31:00</t>
+          <t>12/05/2026 11:17:00</t>
         </is>
       </c>
       <c r="Y26" s="8" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AA26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18 14:31:19.315 : [1]Nhận xét | Comments || N/A || Elegir las categoria &gt; 500 links </t>
+          <t xml:space="preserve">2026-05-12 11:17:09.237 : [1]Nhận xét | Comments || N/A || Wrong division </t>
         </is>
       </c>
       <c r="AB26" s="8" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AI26" s="8" t="inlineStr">
         <is>
-          <t>Elegir las categoria &gt; 500 links</t>
+          <t>Wrong division</t>
         </is>
       </c>
       <c r="AJ26" s="8" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260511_1347286</t>
+          <t>SR_VTP_20260508_1346759</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for IMP-2987 03/2026/VTPr-VMC/CABLE 24FO-ML2026</t>
+          <t>KCS Testing at MInka WH for 01/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>11/05/2026 17:56:00</t>
+          <t>08/05/2026 14:39:00</t>
         </is>
       </c>
       <c r="V27" s="8" t="inlineStr">
         <is>
-          <t>11/05/2026 18:23:00</t>
+          <t>08/05/2026 15:04:00</t>
         </is>
       </c>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 08:00:00</t>
+          <t>14/05/2026 15:04:00</t>
         </is>
       </c>
       <c r="X27" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 11:17:00</t>
+          <t>08/05/2026 18:12:00</t>
         </is>
       </c>
       <c r="Y27" s="8" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AA27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-12 11:17:09.237 : [1]Nhận xét | Comments || N/A || Wrong division </t>
+          <t xml:space="preserve">2026-05-08 18:12:40.243 : [1]Nhận xét | Comments || N/A || Which plan? Not related to TRA. Detail that, </t>
         </is>
       </c>
       <c r="AB27" s="8" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AI27" s="8" t="inlineStr">
         <is>
-          <t>Wrong division</t>
+          <t>Which plan? Not related to TRA. Detail that,</t>
         </is>
       </c>
       <c r="AJ27" s="8" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260508_1346759</t>
+          <t>SR_VTP_20260507_1346521</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 01/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
+          <t>DISEÑO LAST MILLE -   MINEDU WAN</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
@@ -4417,22 +4417,22 @@
       </c>
       <c r="P28" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
+          <t>Design Transmission for new BTS "Less than 80"</t>
         </is>
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_ronald.jimenez</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -4442,22 +4442,22 @@
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 14:39:00</t>
+          <t>07/05/2026 17:47:00</t>
         </is>
       </c>
       <c r="V28" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 15:04:00</t>
+          <t>07/05/2026 18:10:00</t>
         </is>
       </c>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 15:04:00</t>
+          <t>13/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 18:12:00</t>
+          <t>08/05/2026 12:43:00</t>
         </is>
       </c>
       <c r="Y28" s="8" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="AA28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 18:12:40.243 : [1]Nhận xét | Comments || N/A || Which plan? Not related to TRA. Detail that, </t>
+          <t xml:space="preserve">2026-05-08 12:43:00.713 : [1]Nhận xét | Comments || N/A || Cambiar de categoria a diseño &lt; 50 enlaces </t>
         </is>
       </c>
       <c r="AB28" s="8" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AI28" s="8" t="inlineStr">
         <is>
-          <t>Which plan? Not related to TRA. Detail that,</t>
+          <t>Cambiar de categoria a diseño &lt; 50 enlaces</t>
         </is>
       </c>
       <c r="AJ28" s="8" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346521</t>
+          <t>SR_VTP_20260507_1346500</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE -   MINEDU WAN</t>
+          <t>KCS Testing at MInka WH for 03/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_DWDM</t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "Less than 80"</t>
+          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>vtp_ronald.jimenez</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:47:00</t>
+          <t>07/05/2026 16:51:00</t>
         </is>
       </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 18:10:00</t>
+          <t>07/05/2026 17:20:00</t>
         </is>
       </c>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 08:00:00</t>
+          <t>13/05/2026 17:20:00</t>
         </is>
       </c>
       <c r="X29" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 12:43:00</t>
+          <t>08/05/2026 11:05:00</t>
         </is>
       </c>
       <c r="Y29" s="8" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AA29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 12:43:00.713 : [1]Nhận xét | Comments || N/A || Cambiar de categoria a diseño &lt; 50 enlaces </t>
+          <t xml:space="preserve">2026-05-08 11:05:45.017 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
         </is>
       </c>
       <c r="AB29" s="8" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="AI29" s="8" t="inlineStr">
         <is>
-          <t>Cambiar de categoria a diseño &lt; 50 enlaces</t>
+          <t>If requested without TRA confirmation of quality then that team responsible,</t>
         </is>
       </c>
       <c r="AJ29" s="8" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346500</t>
+          <t>SR_VTP_20260507_1346501</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 03/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
+          <t>KCS Testing at MInka WH for 02/2026/VTPr-GFORESTAL/ESSALUD/POLES</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -4822,22 +4822,22 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 16:51:00</t>
+          <t>07/05/2026 16:59:00</t>
         </is>
       </c>
       <c r="V30" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:20:00</t>
+          <t>07/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 17:20:00</t>
+          <t>13/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="X30" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 11:05:00</t>
+          <t>08/05/2026 11:02:00</t>
         </is>
       </c>
       <c r="Y30" s="8" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AA30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 11:05:45.017 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
+          <t xml:space="preserve">2026-05-08 11:02:52.613 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
         </is>
       </c>
       <c r="AB30" s="8" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346501</t>
+          <t>SR_VTP_20260507_1346469</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 02/2026/VTPr-GFORESTAL/ESSALUD/POLES</t>
+          <t>DISEÑO LAST MILLE - HNHU (Hospital Nacional Hipólito Unanue)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
@@ -4987,22 +4987,22 @@
       </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
+          <t>Design Transmission for new BTS "Less than 80"</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_ronald.jimenez</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -5012,22 +5012,22 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 16:59:00</t>
+          <t>07/05/2026 15:40:00</t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:28:00</t>
+          <t>07/05/2026 15:57:00</t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 17:28:00</t>
+          <t>12/05/2026 15:57:00</t>
         </is>
       </c>
       <c r="X31" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 11:02:00</t>
+          <t>07/05/2026 18:08:00</t>
         </is>
       </c>
       <c r="Y31" s="8" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AA31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 11:02:52.613 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
+          <t xml:space="preserve">2026-05-07 18:04:17.794 : [1]Nhận xét | Comments || N/A || Pueder ser diseñado por Preventa, son 2 enlaces </t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AI31" s="8" t="inlineStr">
         <is>
-          <t>If requested without TRA confirmation of quality then that team responsible,</t>
+          <t>Pueder ser diseñado por Preventa, son 2 enlaces</t>
         </is>
       </c>
       <c r="AJ31" s="8" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346469</t>
+          <t>SR_VTP_20260505_1345858</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE - HNHU (Hospital Nacional Hipólito Unanue)</t>
+          <t>DISEÑO LAST MILLE - INO -  2 LINKS</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -5202,22 +5202,22 @@
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 15:40:00</t>
+          <t>05/05/2026 16:59:00</t>
         </is>
       </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 15:57:00</t>
+          <t>05/05/2026 17:22:00</t>
         </is>
       </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 15:57:00</t>
+          <t>08/05/2026 17:22:00</t>
         </is>
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 18:08:00</t>
+          <t>06/05/2026 16:48:00</t>
         </is>
       </c>
       <c r="Y32" s="8" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="AA32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-07 18:04:17.794 : [1]Nhận xét | Comments || N/A || Pueder ser diseñado por Preventa, son 2 enlaces </t>
+          <t xml:space="preserve">2026-05-06 16:48:30.879 : [1]Nhận xét | Comments || N/A || 2 enlaces, lo puede diseñar Preventa </t>
         </is>
       </c>
       <c r="AB32" s="8" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AI32" s="8" t="inlineStr">
         <is>
-          <t>Pueder ser diseñado por Preventa, son 2 enlaces</t>
+          <t>2 enlaces, lo puede diseñar Preventa</t>
         </is>
       </c>
       <c r="AJ32" s="8" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260505_1345858</t>
+          <t>SR_VTP_20260504_1345314</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE - INO -  2 LINKS</t>
+          <t>Carta No. 000190-2026/PROINVERSION/DPP/VI.34 // INFORMATIVO</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_fernando.munoz</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -5367,22 +5367,22 @@
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "Less than 80"</t>
+          <t>Review letters of interference/notification/information about BITEL optical cable</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>vtp_ronald.jimenez</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -5392,22 +5392,22 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>05/05/2026 16:59:00</t>
+          <t>04/05/2026 11:24:00</t>
         </is>
       </c>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t>05/05/2026 17:22:00</t>
+          <t>04/05/2026 11:53:00</t>
         </is>
       </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 17:22:00</t>
+          <t>07/05/2026 11:53:00</t>
         </is>
       </c>
       <c r="X33" s="8" t="inlineStr">
         <is>
-          <t>06/05/2026 16:48:00</t>
+          <t>04/05/2026 11:43:00</t>
         </is>
       </c>
       <c r="Y33" s="8" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="AA33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-06 16:48:30.879 : [1]Nhận xét | Comments || N/A || 2 enlaces, lo puede diseñar Preventa </t>
+          <t xml:space="preserve">2026-05-04 11:43:26.02 : [1]Nhận xét | Comments || N/A || No se adjuntaron los archivos al momento de publicar el SR. </t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AI33" s="8" t="inlineStr">
         <is>
-          <t>2 enlaces, lo puede diseñar Preventa</t>
+          <t>No se adjuntaron los archivos al momento de publicar el SR.</t>
         </is>
       </c>
       <c r="AJ33" s="8" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260504_1345314</t>
+          <t>SR_VTP_20260424_1343697</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Carta No. 000190-2026/PROINVERSION/DPP/VI.34 // INFORMATIVO</t>
+          <t>Solicito personal SOPORTE DE REVISIÓN MW EXISTENTE CLIENTE MINJUS - MINJUSDH0126_0413_INT</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>vtp_fernando.munoz</t>
+          <t>vtp_vanessa.balbuena</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
@@ -5557,22 +5557,22 @@
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_MICROWAVE</t>
         </is>
       </c>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>Review letters of interference/notification/information about BITEL optical cable</t>
+          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>danielmr_vtp</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Infrastructure Center VTP|Infrastructure Corporate Department</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -5582,22 +5582,22 @@
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:24:00</t>
+          <t>24/04/2026 10:42:00</t>
         </is>
       </c>
       <c r="V34" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:53:00</t>
+          <t>24/04/2026 11:12:00</t>
         </is>
       </c>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 11:53:00</t>
+          <t>30/04/2026 11:12:00</t>
         </is>
       </c>
       <c r="X34" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:43:00</t>
+          <t>24/04/2026 10:50:00</t>
         </is>
       </c>
       <c r="Y34" s="8" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AA34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04 11:43:26.02 : [1]Nhận xét | Comments || N/A || No se adjuntaron los archivos al momento de publicar el SR. </t>
+          <t xml:space="preserve">2026-04-24 10:50:19.854 : [1]Nhận xét | Comments || N/A || Wrong unit </t>
         </is>
       </c>
       <c r="AB34" s="8" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AG34" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*****</t>
         </is>
       </c>
       <c r="AH34" s="8" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AI34" s="8" t="inlineStr">
         <is>
-          <t>No se adjuntaron los archivos al momento de publicar el SR.</t>
+          <t>Wrong unit</t>
         </is>
       </c>
       <c r="AJ34" s="8" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260424_1343697</t>
+          <t>SR_VTP_20260521_1350086</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -5687,22 +5687,22 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Solicito personal SOPORTE DE REVISIÓN MW EXISTENTE CLIENTE MINJUS - MINJUSDH0126_0413_INT</t>
+          <t>BDS - CORP - PMO - ENVIO DE MATERIAL SEGUN ULTIMO DISEÑO PARA NUEVA RUTA ARE0088-ARE0089 EN PROYECTO MSOUTHERN0723_0038_INT-AN02</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>vtp_vanessa.balbuena</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -5747,22 +5747,22 @@
       </c>
       <c r="P35" s="8" t="inlineStr">
         <is>
-          <t>VTP_MICROWAVE</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
+          <t>Design/redesign optical fiber routes</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>danielmr_vtp</t>
+          <t>wilsonvc_lim</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Infrastructure Center VTP|Infrastructure Corporate Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -5772,22 +5772,22 @@
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 10:42:00</t>
+          <t>21/05/2026 11:58:00</t>
         </is>
       </c>
       <c r="V35" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 11:12:00</t>
+          <t>21/05/2026 15:00:00</t>
         </is>
       </c>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t>30/04/2026 11:12:00</t>
+          <t>26/05/2026 15:00:00</t>
         </is>
       </c>
       <c r="X35" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 10:50:00</t>
+          <t>25/05/2026 09:26:00</t>
         </is>
       </c>
       <c r="Y35" s="8" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AA35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-24 10:50:19.854 : [1]Nhận xét | Comments || N/A || Wrong unit </t>
+          <t xml:space="preserve">2026-05-25 09:26:39.946 : [1]Nhận xét | Comments || N/A || This CORP project, not TRA project. </t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AG35" s="8" t="inlineStr">
         <is>
-          <t>*****</t>
+          <t/>
         </is>
       </c>
       <c r="AH35" s="8" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AI35" s="8" t="inlineStr">
         <is>
-          <t>Wrong unit</t>
+          <t>This CORP project, not TRA project.</t>
         </is>
       </c>
       <c r="AJ35" s="8" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260521_1350086</t>
+          <t>SR_VTP_20260514_1348134</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>BDS - CORP - PMO - ENVIO DE MATERIAL SEGUN ULTIMO DISEÑO PARA NUEVA RUTA ARE0088-ARE0089 EN PROYECTO MSOUTHERN0723_0038_INT-AN02</t>
+          <t>CLIENTE: PNP || DESIGN OF BACK UP LINKS || 185 LINKS</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>Design/redesign optical fiber routes</t>
+          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
         </is>
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>wilsonvc_lim</t>
+          <t>vtp_ulises.benvenuto</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
@@ -5962,22 +5962,22 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 11:58:00</t>
+          <t>14/05/2026 09:36:00</t>
         </is>
       </c>
       <c r="V36" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 15:00:00</t>
+          <t>14/05/2026 09:57:00</t>
         </is>
       </c>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 15:00:00</t>
+          <t>04/06/2026 09:57:00</t>
         </is>
       </c>
       <c r="X36" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:26:00</t>
+          <t>21/05/2026 10:40:00</t>
         </is>
       </c>
       <c r="Y36" s="8" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AA36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 09:26:39.946 : [1]Nhận xét | Comments || N/A || This CORP project, not TRA project. </t>
+          <t xml:space="preserve">2026-05-21 10:40:25.226 : [1]Nhận xét | Comments || N/A || No information attached </t>
         </is>
       </c>
       <c r="AB36" s="8" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="AI36" s="8" t="inlineStr">
         <is>
-          <t>This CORP project, not TRA project.</t>
+          <t>No information attached</t>
         </is>
       </c>
       <c r="AJ36" s="8" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260514_1348134</t>
+          <t>SR_VTP_20260522_1350434</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>CLIENTE: PNP || DESIGN OF BACK UP LINKS || 185 LINKS</t>
+          <t>Checklist MW CAJ0606 (CAJ0464-CAJ0606)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Evaluated</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_diana.idrugo</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">
@@ -6127,22 +6127,22 @@
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_MICROWAVE</t>
         </is>
       </c>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
+          <t>MW_REVIEW CHECKLIST</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>vtp_ulises.benvenuto</t>
+          <t>vtp_diana.idrugo</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 09:36:00</t>
+          <t>22/05/2026 14:28:00</t>
         </is>
       </c>
       <c r="V37" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 09:57:00</t>
+          <t>22/05/2026 14:58:00</t>
         </is>
       </c>
       <c r="W37" s="8" t="inlineStr">
         <is>
-          <t>04/06/2026 09:57:00</t>
+          <t>27/05/2026 14:58:00</t>
         </is>
       </c>
       <c r="X37" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 10:40:00</t>
+          <t>22/05/2026 14:29:00</t>
         </is>
       </c>
       <c r="Y37" s="8" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="AA37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-21 10:40:25.226 : [1]Nhận xét | Comments || N/A || No information attached </t>
+          <t/>
         </is>
       </c>
       <c r="AB37" s="8" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AI37" s="8" t="inlineStr">
         <is>
-          <t>No information attached</t>
+          <t/>
         </is>
       </c>
       <c r="AJ37" s="8" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260522_1350434</t>
+          <t>SR_VTP_20260512_1347391</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Checklist MW CAJ0606 (CAJ0464-CAJ0606)</t>
+          <t>Sends Reports F008-CIT-2A, F009-CIT-2B</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>vtp_diana.idrugo</t>
+          <t>vtp_vanessa.balbuena</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
@@ -6322,17 +6322,17 @@
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>MW_REVIEW CHECKLIST</t>
+          <t>MW_SIGEP_SIGIEP REPORT</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>vtp_diana.idrugo</t>
+          <t>cesarsa_vtp</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|IT Center VTP|Business Process VTP|PMO Division</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -6342,22 +6342,22 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 14:28:00</t>
+          <t>12/05/2026 10:36:00</t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 14:58:00</t>
+          <t>12/05/2026 10:54:00</t>
         </is>
       </c>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>27/05/2026 14:58:00</t>
+          <t>26/05/2026 10:54:00</t>
         </is>
       </c>
       <c r="X38" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 14:29:00</t>
+          <t>12/05/2026 10:41:00</t>
         </is>
       </c>
       <c r="Y38" s="8" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260512_1347391</t>
+          <t>SR_VTP_20260521_1349952</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -6447,17 +6447,17 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Sends Reports F008-CIT-2A, F009-CIT-2B</t>
+          <t>Solicito personal SOPORTE MW - CATALINAHUANCA0426_0002_INT</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Evaluated</t>
+          <t>Assigned Planning</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>vtp_vanessa.balbuena</t>
+          <t>vtp_kelly.alvarado</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -6482,24 +6482,24 @@
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
@@ -6512,17 +6512,17 @@
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>MW_SIGEP_SIGIEP REPORT</t>
+          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>cesarsa_vtp</t>
+          <t>danielmr_vtp</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|IT Center VTP|Business Process VTP|PMO Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Infrastructure Center VTP|Infrastructure Corporate Department</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -6532,27 +6532,27 @@
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 10:36:00</t>
+          <t>21/05/2026 09:34:00</t>
         </is>
       </c>
       <c r="V39" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 10:54:00</t>
+          <t>21/05/2026 09:51:00</t>
         </is>
       </c>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 10:54:00</t>
+          <t>28/05/2026 09:51:00</t>
         </is>
       </c>
       <c r="X39" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 10:41:00</t>
+          <t>25/05/2026 17:09:00</t>
         </is>
       </c>
       <c r="Y39" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>CR_NORMAL_TRANSMISSION_20025261603</t>
         </is>
       </c>
       <c r="Z39" s="8" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AA39" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">2026-05-25 17:09:28.3 : [1]Nhận xét | Comments || N/A || MOP_INCREASE_CAPACITY_ZTE_AYA0240-CID5719 </t>
         </is>
       </c>
       <c r="AB39" s="8" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="AG39" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*</t>
         </is>
       </c>
       <c r="AH39" s="8" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="AI39" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>MOP_INCREASE_CAPACITY_ZTE_AYA0240-CID5719</t>
         </is>
       </c>
       <c r="AJ39" s="8" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260521_1349952</t>
+          <t>SR_VTP_20260522_1350529</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Solicito personal SOPORTE MW - CATALINAHUANCA0426_0002_INT</t>
+          <t>LAM0190B3U2-PIU0415_1 Reconfigure link to work in parallel</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Assigned Planning</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>In due</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
@@ -6702,17 +6702,17 @@
       </c>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
+          <t>MW_RESTRUCTURE NETWORK</t>
         </is>
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>danielmr_vtp</t>
+          <t>vtp_kathy.valle</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Infrastructure Center VTP|Infrastructure Corporate Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -6722,27 +6722,27 @@
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 09:34:00</t>
+          <t>22/05/2026 16:04:00</t>
         </is>
       </c>
       <c r="V40" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 09:51:00</t>
+          <t>22/05/2026 16:33:00</t>
         </is>
       </c>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 09:51:00</t>
+          <t>29/05/2026 16:33:00</t>
         </is>
       </c>
       <c r="X40" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 17:09:00</t>
+          <t>25/05/2026 17:05:00</t>
         </is>
       </c>
       <c r="Y40" s="8" t="inlineStr">
         <is>
-          <t>CR_NORMAL_TRANSMISSION_20025261603</t>
+          <t>CR_NORMAL_TRANSMISSION_20025257002</t>
         </is>
       </c>
       <c r="Z40" s="8" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AA40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 17:09:28.3 : [1]Nhận xét | Comments || N/A || MOP_INCREASE_CAPACITY_ZTE_AYA0240-CID5719 </t>
+          <t xml:space="preserve">2026-05-22 18:14:03.256 : [1]Nhận xét | Comments || N/A || MOP_Change Outband and Transparent HUAWEI_LAM0190B3U2-PIU0415_1 </t>
         </is>
       </c>
       <c r="AB40" s="8" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="AG40" s="8" t="inlineStr">
         <is>
-          <t>*</t>
+          <t/>
         </is>
       </c>
       <c r="AH40" s="8" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AI40" s="8" t="inlineStr">
         <is>
-          <t>MOP_INCREASE_CAPACITY_ZTE_AYA0240-CID5719</t>
+          <t>MOP_Change Outband and Transparent HUAWEI_LAM0190B3U2-PIU0415_1</t>
         </is>
       </c>
       <c r="AJ40" s="8" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260522_1350529</t>
+          <t>SR_VTP_20260521_1350200</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>LAM0190B3U2-PIU0415_1 Reconfigure link to work in parallel</t>
+          <t>CAJ0059-CAJ0345 -&gt;  Upgrade by config 112Mhz SIAEALFOPLUS2</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
@@ -6912,27 +6912,27 @@
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 16:04:00</t>
+          <t>21/05/2026 16:10:00</t>
         </is>
       </c>
       <c r="V41" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 16:33:00</t>
+          <t>21/05/2026 16:39:00</t>
         </is>
       </c>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 16:33:00</t>
+          <t>28/05/2026 16:39:00</t>
         </is>
       </c>
       <c r="X41" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 17:05:00</t>
+          <t>25/05/2026 17:00:00</t>
         </is>
       </c>
       <c r="Y41" s="8" t="inlineStr">
         <is>
-          <t>CR_NORMAL_TRANSMISSION_20025257002</t>
+          <t>CR_NORMAL_TRANSMISSION_20025256809</t>
         </is>
       </c>
       <c r="Z41" s="8" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="AA41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-22 18:14:03.256 : [1]Nhận xét | Comments || N/A || MOP_Change Outband and Transparent HUAWEI_LAM0190B3U2-PIU0415_1 </t>
+          <t xml:space="preserve">2026-05-22 18:29:02.229 : [1]Nhận xét | Comments || N/A || MOP_TRANSPARENT MODE_CHANGE BANDWITH_SIAEALFOPlus2_CAJ0059-CAJ0345 </t>
         </is>
       </c>
       <c r="AB41" s="8" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AI41" s="8" t="inlineStr">
         <is>
-          <t>MOP_Change Outband and Transparent HUAWEI_LAM0190B3U2-PIU0415_1</t>
+          <t>MOP_TRANSPARENT MODE_CHANGE BANDWITH_SIAEALFOPlus2_CAJ0059-CAJ0345</t>
         </is>
       </c>
       <c r="AJ41" s="8" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260521_1350200</t>
+          <t>SR_VTP_20260521_1350194</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>CAJ0059-CAJ0345 -&gt;  Upgrade by config 112Mhz SIAEALFOPLUS2</t>
+          <t>ANC0047-ANC0243</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>vtp_kelly.alvarado</t>
+          <t>vtp_luis.anthony</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
@@ -7102,27 +7102,27 @@
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 16:10:00</t>
+          <t>21/05/2026 16:04:00</t>
         </is>
       </c>
       <c r="V42" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 16:39:00</t>
+          <t>21/05/2026 17:30:00</t>
         </is>
       </c>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 16:39:00</t>
+          <t>28/05/2026 17:30:00</t>
         </is>
       </c>
       <c r="X42" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 17:00:00</t>
+          <t>22/05/2026 16:30:00</t>
         </is>
       </c>
       <c r="Y42" s="8" t="inlineStr">
         <is>
-          <t>CR_NORMAL_TRANSMISSION_20025256809</t>
+          <t>CR_NORMAL_TRANSMISSION_20025254226</t>
         </is>
       </c>
       <c r="Z42" s="8" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="AA42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-22 18:29:02.229 : [1]Nhận xét | Comments || N/A || MOP_TRANSPARENT MODE_CHANGE BANDWITH_SIAEALFOPlus2_CAJ0059-CAJ0345 </t>
+          <t xml:space="preserve">2026-05-21 18:36:25.363 : [1]Nhận xét | Comments || N/A || Is to reconfigure link and do test interference </t>
         </is>
       </c>
       <c r="AB42" s="8" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AI42" s="8" t="inlineStr">
         <is>
-          <t>MOP_TRANSPARENT MODE_CHANGE BANDWITH_SIAEALFOPlus2_CAJ0059-CAJ0345</t>
+          <t>Is to reconfigure link and do test interference</t>
         </is>
       </c>
       <c r="AJ42" s="8" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260521_1350194</t>
+          <t>SR_VTP_20260526_1351320</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -7207,22 +7207,22 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>ANC0047-ANC0243</t>
+          <t>Creación Diseño de Enlace Microondas CAJ0613-CAJ5517 D=0.9m</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Concluded</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>vtp_luis.anthony</t>
+          <t>vtp_jeremi.alfaro</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>In due</t>
+          <t/>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="O43" s="8" t="inlineStr">
@@ -7267,22 +7267,22 @@
       </c>
       <c r="P43" s="8" t="inlineStr">
         <is>
-          <t>VTP_MICROWAVE</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>MW_RESTRUCTURE NETWORK</t>
+          <t>Design Transmission for new BTS "Less than 80"</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>vtp_kathy.valle</t>
+          <t>vtp_jhon.flores</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Provinces|VTP - LAM Branch|VTP LAM-Project Team</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -7292,37 +7292,37 @@
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 16:04:00</t>
+          <t>26/05/2026 09:55:00</t>
         </is>
       </c>
       <c r="V43" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 17:30:00</t>
+          <t>26/05/2026 10:08:00</t>
         </is>
       </c>
       <c r="W43" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 17:30:00</t>
+          <t>29/05/2026 10:08:00</t>
         </is>
       </c>
       <c r="X43" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 16:30:00</t>
+          <t>26/05/2026 14:44:00</t>
         </is>
       </c>
       <c r="Y43" s="8" t="inlineStr">
         <is>
-          <t>CR_NORMAL_TRANSMISSION_20025254226</t>
+          <t/>
         </is>
       </c>
       <c r="Z43" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>0.20 Day</t>
         </is>
       </c>
       <c r="AA43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-21 18:36:25.363 : [1]Nhận xét | Comments || N/A || Is to reconfigure link and do test interference </t>
+          <t/>
         </is>
       </c>
       <c r="AB43" s="8" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AI43" s="8" t="inlineStr">
         <is>
-          <t>Is to reconfigure link and do test interference</t>
+          <t/>
         </is>
       </c>
       <c r="AJ43" s="8" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1350939</t>
+          <t>SR_VTP_20260525_1350932</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Carta N.º ALF-PE-097-2026 / INFORMATIVO</t>
+          <t>CRD-104-2026 / INFORMATIVO</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -13182,17 +13182,17 @@
       </c>
       <c r="U74" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 08:56:00</t>
+          <t>25/05/2026 09:22:00</t>
         </is>
       </c>
       <c r="V74" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:24:00</t>
+          <t>25/05/2026 09:50:00</t>
         </is>
       </c>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 09:24:00</t>
+          <t>03/06/2026 09:50:00</t>
         </is>
       </c>
       <c r="X74" s="8" t="inlineStr">
@@ -13207,12 +13207,12 @@
       </c>
       <c r="Z74" s="8" t="inlineStr">
         <is>
-          <t>0.02 Day</t>
+          <t>0.01 Day</t>
         </is>
       </c>
       <c r="AA74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 09:29:56.367 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
+          <t xml:space="preserve">2026-05-25 09:43:27.099 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
         </is>
       </c>
       <c r="AB74" s="8" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="AD74" s="8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AE74" s="8" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1350932</t>
+          <t>SR_VTP_20260525_1350935</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>CRD-104-2026 / INFORMATIVO</t>
+          <t>CORREO 22/05 14:58 / INFORMATIVO (fecha de inicio de trabajos)</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -13372,17 +13372,17 @@
       </c>
       <c r="U75" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:22:00</t>
+          <t>25/05/2026 09:32:00</t>
         </is>
       </c>
       <c r="V75" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:50:00</t>
+          <t>25/05/2026 10:00:00</t>
         </is>
       </c>
       <c r="W75" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 09:50:00</t>
+          <t>03/06/2026 10:00:00</t>
         </is>
       </c>
       <c r="X75" s="8" t="inlineStr">
@@ -13397,200 +13397,10 @@
       </c>
       <c r="Z75" s="8" t="inlineStr">
         <is>
-          <t>0.01 Day</t>
+          <t>0.09 Day</t>
         </is>
       </c>
       <c r="AA75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-25 09:43:27.099 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
-        </is>
-      </c>
-      <c r="AB75" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC75" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD75" s="8" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AE75" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF75" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG75" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH75" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI75" s="8" t="inlineStr">
-        <is>
-          <t>Si hay interferencia en la zona indicada</t>
-        </is>
-      </c>
-      <c r="AJ75" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK75" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL75" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="76" customHeight="true" ht="12.5">
-      <c r="A76" s="11" t="n">
-        <v>68.0</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260525_1350935</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>CORREO 22/05 14:58 / INFORMATIVO (fecha de inicio de trabajos)</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>vtp_palomino.carlos</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K76" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L76" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M76" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N76" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O76" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P76" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q76" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R76" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S76" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U76" s="8" t="inlineStr">
-        <is>
-          <t>25/05/2026 09:32:00</t>
-        </is>
-      </c>
-      <c r="V76" s="8" t="inlineStr">
-        <is>
-          <t>25/05/2026 10:00:00</t>
-        </is>
-      </c>
-      <c r="W76" s="8" t="inlineStr">
-        <is>
-          <t>03/06/2026 10:00:00</t>
-        </is>
-      </c>
-      <c r="X76" s="8" t="inlineStr">
-        <is>
-          <t>25/05/2026 18:00:00</t>
-        </is>
-      </c>
-      <c r="Y76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z76" s="8" t="inlineStr">
-        <is>
-          <t>0.09 Day</t>
-        </is>
-      </c>
-      <c r="AA76" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-25 09:47:16.938 : [1]Nhận xét | Comments || N/A || Estimados,
 En respuesta a: [SR_VTP_20260525_1350927 / Carta N.º ALF-PE-095-2026]
@@ -13602,42 +13412,42 @@
 Agradeceríamos su apoyo y su pronta atención, teniendo en cuenta el nivel de urgencia de este caso. Así como CONFIRMAR SI SE TRABAJARÁ CON PARTNER O NO, DE NO SER EL CASO, ASIGNAR UNA CUADRILLA PARA AVANCE DE TRABAJOS. </t>
         </is>
       </c>
-      <c r="AB76" s="8" t="inlineStr">
+      <c r="AB75" s="8" t="inlineStr">
         <is>
           <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
         </is>
       </c>
-      <c r="AC76" s="8" t="inlineStr">
+      <c r="AC75" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AD76" s="8" t="inlineStr">
+      <c r="AD75" s="8" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="AE76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG76" s="8" t="inlineStr">
+      <c r="AE75" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF75" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG75" s="8" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="AH76" s="8" t="inlineStr">
+      <c r="AH75" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AI76" s="8" t="inlineStr">
+      <c r="AI75" s="8" t="inlineStr">
         <is>
           <t>Estimados,
 En respuesta a: [SR_VTP_20260525_1350927 / Carta N.º ALF-PE-095-2026]
@@ -13649,152 +13459,152 @@
 Agradeceríamos su apoyo y su pronta atención, teniendo en cuenta el nivel de urgencia de este caso. Así como CONFIRMAR SI SE TRABAJARÁ CON PARTNER O NO, DE NO SER EL CASO, ASIGNAR UNA CUADRILLA PARA AVANCE DE TRABAJOS.</t>
         </is>
       </c>
-      <c r="AJ76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK76" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL76" s="8" t="inlineStr">
+      <c r="AJ75" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK75" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL75" s="8" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="77" customHeight="true" ht="12.5">
-      <c r="A77" s="11" t="n">
-        <v>69.0</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+    <row r="76" customHeight="true" ht="12.5">
+      <c r="A76" s="11" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>SR_VTP_20260525_1350927</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Carta N.º ALF-PE-095-2026 / INFORMATIVO</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>vtp_fernando.munoz</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K77" s="8" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L77" s="8" t="inlineStr">
+      <c r="L76" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M77" s="8" t="inlineStr">
+      <c r="M76" s="8" t="inlineStr">
         <is>
           <t>In deadline</t>
         </is>
       </c>
-      <c r="N77" s="8" t="inlineStr">
+      <c r="N76" s="8" t="inlineStr">
         <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O76" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
         </is>
       </c>
-      <c r="P77" s="8" t="inlineStr">
+      <c r="P76" s="8" t="inlineStr">
         <is>
           <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
-      <c r="Q77" s="8" t="inlineStr">
+      <c r="Q76" s="8" t="inlineStr">
         <is>
           <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
-      <c r="R77" s="8" t="inlineStr">
+      <c r="R76" s="8" t="inlineStr">
         <is>
           <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
-      <c r="S77" s="8" t="inlineStr">
+      <c r="S76" s="8" t="inlineStr">
         <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
-      <c r="T77" s="8" t="inlineStr">
+      <c r="T76" s="8" t="inlineStr">
         <is>
           <t>Peru (VTP)</t>
         </is>
       </c>
-      <c r="U77" s="8" t="inlineStr">
+      <c r="U76" s="8" t="inlineStr">
         <is>
           <t>25/05/2026 09:00:00</t>
         </is>
       </c>
-      <c r="V77" s="8" t="inlineStr">
+      <c r="V76" s="8" t="inlineStr">
         <is>
           <t>25/05/2026 09:29:00</t>
         </is>
       </c>
-      <c r="W77" s="8" t="inlineStr">
+      <c r="W76" s="8" t="inlineStr">
         <is>
           <t>03/06/2026 09:29:00</t>
         </is>
       </c>
-      <c r="X77" s="8" t="inlineStr">
+      <c r="X76" s="8" t="inlineStr">
         <is>
           <t>25/05/2026 18:00:00</t>
         </is>
       </c>
-      <c r="Y77" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z77" s="8" t="inlineStr">
+      <c r="Y76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z76" s="8" t="inlineStr">
         <is>
           <t>0.03 Day</t>
         </is>
       </c>
-      <c r="AA77" s="8" t="inlineStr">
+      <c r="AA76" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-25 09:48:06.434 : [1]Nhận xét | Comments || N/A || Estimados,
 En respuesta a: [SR_VTP_20260525_1350927 / Carta N.º ALF-PE-095-2026]
@@ -13803,42 +13613,42 @@
 https://drive.google.com/drive/folders/1kLvT4LbOWfq2hZG5LGug4kScPSxT9AiY?usp=drive_link </t>
         </is>
       </c>
-      <c r="AB77" s="8" t="inlineStr">
+      <c r="AB76" s="8" t="inlineStr">
         <is>
           <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
         </is>
       </c>
-      <c r="AC77" s="8" t="inlineStr">
+      <c r="AC76" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AD77" s="8" t="inlineStr">
+      <c r="AD76" s="8" t="inlineStr">
         <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="AE77" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF77" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG77" s="8" t="inlineStr">
+      <c r="AE76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG76" s="8" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="AH77" s="8" t="inlineStr">
+      <c r="AH76" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AI77" s="8" t="inlineStr">
+      <c r="AI76" s="8" t="inlineStr">
         <is>
           <t>Estimados,
 En respuesta a: [SR_VTP_20260525_1350927 / Carta N.º ALF-PE-095-2026]
@@ -13847,6 +13657,196 @@
 https://drive.google.com/drive/folders/1kLvT4LbOWfq2hZG5LGug4kScPSxT9AiY?usp=drive_link</t>
         </is>
       </c>
+      <c r="AJ76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL76" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77" customHeight="true" ht="12.5">
+      <c r="A77" s="11" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260525_1350939</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Carta N.º ALF-PE-097-2026 / INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>vtp_palomino.carlos</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N77" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P77" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R77" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S77" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U77" s="8" t="inlineStr">
+        <is>
+          <t>25/05/2026 08:56:00</t>
+        </is>
+      </c>
+      <c r="V77" s="8" t="inlineStr">
+        <is>
+          <t>25/05/2026 09:24:00</t>
+        </is>
+      </c>
+      <c r="W77" s="8" t="inlineStr">
+        <is>
+          <t>03/06/2026 09:24:00</t>
+        </is>
+      </c>
+      <c r="X77" s="8" t="inlineStr">
+        <is>
+          <t>25/05/2026 18:00:00</t>
+        </is>
+      </c>
+      <c r="Y77" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z77" s="8" t="inlineStr">
+        <is>
+          <t>0.02 Day</t>
+        </is>
+      </c>
+      <c r="AA77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-25 09:29:56.367 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
+        </is>
+      </c>
+      <c r="AB77" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC77" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD77" s="8" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AE77" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF77" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG77" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH77" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI77" s="8" t="inlineStr">
+        <is>
+          <t>Si hay interferencia en la zona indicada</t>
+        </is>
+      </c>
       <c r="AJ77" s="8" t="inlineStr">
         <is>
           <t/>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1350945</t>
+          <t>SR_VTP_20260514_1348133</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>CARTA-PT-ING-123-2026 / INFORMATIVO</t>
+          <t>Carta 1760-2026-GP-BRH-T / CRONOGRAMA Y PRESUPUESTO</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>vtp_palomino.carlos</t>
+          <t>vtp_fernando.munoz</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="K78" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L78" s="8" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
+          <t>Budget Project design for fiber relocation for MTC projects</t>
         </is>
       </c>
       <c r="R78" s="8" t="inlineStr">
@@ -13964,17 +13964,17 @@
       </c>
       <c r="U78" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:20:00</t>
+          <t>14/05/2026 09:30:00</t>
         </is>
       </c>
       <c r="V78" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:47:00</t>
+          <t>14/05/2026 09:56:00</t>
         </is>
       </c>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 09:47:00</t>
+          <t>04/06/2026 09:56:00</t>
         </is>
       </c>
       <c r="X78" s="8" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="Z78" s="8" t="inlineStr">
         <is>
-          <t>0.04 Day</t>
+          <t>6.07 Days</t>
         </is>
       </c>
       <c r="AA78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 10:13:00.727 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
+          <t xml:space="preserve">2026-05-22 11:17:10.109 : [1]Nhận xét | Comments || N/A || Se coordinó la inspección conjunta con el TM y la Ing. Ana, representante de Benito Roggio e Hijos, para el día martes 2 de junio a las 10AM. </t>
         </is>
       </c>
       <c r="AB78" s="8" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="AD78" s="8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AE78" s="8" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AI78" s="8" t="inlineStr">
         <is>
-          <t>Si hay interferencia en la zona indicada</t>
+          <t>Se coordinó la inspección conjunta con el TM y la Ing. Ana, representante de Benito Roggio e Hijos, para el día martes 2 de junio a las 10AM.</t>
         </is>
       </c>
       <c r="AJ78" s="8" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260515_1348614</t>
+          <t>SR_VTP_20260525_1350945</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>OFICIO N° 6556-2026-MTC/19.03 // INSPECCIÓN CONJUNTA</t>
+          <t>CARTA-PT-ING-123-2026 / INFORMATIVO</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>vtp_bryam.broncano</t>
+          <t>vtp_palomino.carlos</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="U79" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 17:29:00</t>
+          <t>25/05/2026 09:20:00</t>
         </is>
       </c>
       <c r="V79" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 17:57:00</t>
+          <t>25/05/2026 09:47:00</t>
         </is>
       </c>
       <c r="W79" s="8" t="inlineStr">
         <is>
-          <t>27/05/2026 08:00:00</t>
+          <t>03/06/2026 09:47:00</t>
         </is>
       </c>
       <c r="X79" s="8" t="inlineStr">
@@ -14179,12 +14179,12 @@
       </c>
       <c r="Z79" s="8" t="inlineStr">
         <is>
-          <t>5.78 Days</t>
+          <t>0.04 Day</t>
         </is>
       </c>
       <c r="AA79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 12:05:49.676 : [1]Nhận xét | Comments || N/A || Se coordino con tm para que puedan ir ese dia establecido </t>
+          <t xml:space="preserve">2026-05-25 10:13:00.727 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
         </is>
       </c>
       <c r="AB79" s="8" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="AD79" s="8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AE79" s="8" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="AI79" s="8" t="inlineStr">
         <is>
-          <t>Se coordino con tm para que puedan ir ese dia establecido</t>
+          <t>Si hay interferencia en la zona indicada</t>
         </is>
       </c>
       <c r="AJ79" s="8" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1350929</t>
+          <t>SR_VTP_20260515_1348614</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Carta Nº 326- GYACSAC-2026 / INFORMATIVO</t>
+          <t>OFICIO N° 6556-2026-MTC/19.03 // INSPECCIÓN CONJUNTA</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>vtp_palomino.carlos</t>
+          <t>vtp_bryam.broncano</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -14344,17 +14344,17 @@
       </c>
       <c r="U80" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:16:00</t>
+          <t>15/05/2026 17:29:00</t>
         </is>
       </c>
       <c r="V80" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:35:00</t>
+          <t>15/05/2026 17:57:00</t>
         </is>
       </c>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 09:35:00</t>
+          <t>27/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X80" s="8" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="Z80" s="8" t="inlineStr">
         <is>
-          <t>0.03 Day</t>
+          <t>5.78 Days</t>
         </is>
       </c>
       <c r="AA80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 09:56:54.29 : [1]Nhận xét | Comments || N/A || No hay interferencia en la zona indicada </t>
+          <t xml:space="preserve">2026-05-25 12:05:49.676 : [1]Nhận xét | Comments || N/A || Se coordino con tm para que puedan ir ese dia establecido </t>
         </is>
       </c>
       <c r="AB80" s="8" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="AD80" s="8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AE80" s="8" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="AI80" s="8" t="inlineStr">
         <is>
-          <t>No hay interferencia en la zona indicada</t>
+          <t>Se coordino con tm para que puedan ir ese dia establecido</t>
         </is>
       </c>
       <c r="AJ80" s="8" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260515_1348633</t>
+          <t>SR_VTP_20260525_1350929</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>OFICIO N° 6557-2026-MTC/19.03 / INSPECCIÓN CONJUNTA</t>
+          <t>Carta Nº 326- GYACSAC-2026 / INFORMATIVO</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>vtp_bryam.broncano</t>
+          <t>vtp_palomino.carlos</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
@@ -14534,17 +14534,17 @@
       </c>
       <c r="U81" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 17:47:00</t>
+          <t>25/05/2026 09:16:00</t>
         </is>
       </c>
       <c r="V81" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 18:14:00</t>
+          <t>25/05/2026 09:35:00</t>
         </is>
       </c>
       <c r="W81" s="8" t="inlineStr">
         <is>
-          <t>27/05/2026 08:00:00</t>
+          <t>03/06/2026 09:35:00</t>
         </is>
       </c>
       <c r="X81" s="8" t="inlineStr">
@@ -14559,12 +14559,12 @@
       </c>
       <c r="Z81" s="8" t="inlineStr">
         <is>
-          <t>5.71 Days</t>
+          <t>0.03 Day</t>
         </is>
       </c>
       <c r="AA81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 10:49:56.489 : [1]Nhận xét | Comments || N/A || se confirmo con tm asistencia de bitel, el personal sera asiganado un dia antes </t>
+          <t xml:space="preserve">2026-05-25 09:56:54.29 : [1]Nhận xét | Comments || N/A || No hay interferencia en la zona indicada </t>
         </is>
       </c>
       <c r="AB81" s="8" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="AD81" s="8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AE81" s="8" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="AI81" s="8" t="inlineStr">
         <is>
-          <t>se confirmo con tm asistencia de bitel, el personal sera asiganado un dia antes</t>
+          <t>No hay interferencia en la zona indicada</t>
         </is>
       </c>
       <c r="AJ81" s="8" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260514_1348133</t>
+          <t>SR_VTP_20260515_1348633</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Carta 1760-2026-GP-BRH-T / CRONOGRAMA Y PRESUPUESTO</t>
+          <t>OFICIO N° 6557-2026-MTC/19.03 / INSPECCIÓN CONJUNTA</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>vtp_fernando.munoz</t>
+          <t>vtp_bryam.broncano</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L82" s="8" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>Budget Project design for fiber relocation for MTC projects</t>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr">
@@ -14724,17 +14724,17 @@
       </c>
       <c r="U82" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 09:30:00</t>
+          <t>15/05/2026 17:47:00</t>
         </is>
       </c>
       <c r="V82" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 09:56:00</t>
+          <t>15/05/2026 18:14:00</t>
         </is>
       </c>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>04/06/2026 09:56:00</t>
+          <t>27/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X82" s="8" t="inlineStr">
@@ -14749,12 +14749,12 @@
       </c>
       <c r="Z82" s="8" t="inlineStr">
         <is>
-          <t>6.07 Days</t>
+          <t>5.71 Days</t>
         </is>
       </c>
       <c r="AA82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-22 11:17:10.109 : [1]Nhận xét | Comments || N/A || Se coordinó la inspección conjunta con el TM y la Ing. Ana, representante de Benito Roggio e Hijos, para el día martes 2 de junio a las 10AM. </t>
+          <t xml:space="preserve">2026-05-25 10:49:56.489 : [1]Nhận xét | Comments || N/A || se confirmo con tm asistencia de bitel, el personal sera asiganado un dia antes </t>
         </is>
       </c>
       <c r="AB82" s="8" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="AD82" s="8" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AE82" s="8" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="AI82" s="8" t="inlineStr">
         <is>
-          <t>Se coordinó la inspección conjunta con el TM y la Ing. Ana, representante de Benito Roggio e Hijos, para el día martes 2 de junio a las 10AM.</t>
+          <t>se confirmo con tm asistencia de bitel, el personal sera asiganado un dia antes</t>
         </is>
       </c>
       <c r="AJ82" s="8" t="inlineStr">
@@ -15581,130 +15581,1092 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
+          <t>SR_VTP_20260515_1348591</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Oficio Nº 6346-2026-MTC/19.03 // INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>vtp_palomino.carlos</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P87" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q87" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R87" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S87" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 16:19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 16:49:00</t>
+        </is>
+      </c>
+      <c r="W87" s="8" t="inlineStr">
+        <is>
+          <t>26/05/2026 16:49:00</t>
+        </is>
+      </c>
+      <c r="X87" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z87" s="8" t="inlineStr">
+        <is>
+          <t>2.72 Days</t>
+        </is>
+      </c>
+      <c r="AA87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-20 09:40:23.683 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
+        </is>
+      </c>
+      <c r="AB87" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC87" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD87" s="8" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AE87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG87" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH87" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI87" s="8" t="inlineStr">
+        <is>
+          <t>Si hay interferencia en la zona indicada</t>
+        </is>
+      </c>
+      <c r="AJ87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL87" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="88" customHeight="true" ht="12.5">
+      <c r="A88" s="11" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260512_1347612</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>GT-0658-2026 / SOLICITUD DE IDENTIFICACIÓN DE UBICACIONES DE CABLEADO EN MAL ESTADO</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>vtp_fernando.munoz</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L88" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O88" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P88" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q88" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R88" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S88" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>12/05/2026 16:42:00</t>
+        </is>
+      </c>
+      <c r="V88" s="8" t="inlineStr">
+        <is>
+          <t>12/05/2026 17:11:00</t>
+        </is>
+      </c>
+      <c r="W88" s="8" t="inlineStr">
+        <is>
+          <t>21/05/2026 17:11:00</t>
+        </is>
+      </c>
+      <c r="X88" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z88" s="8" t="inlineStr">
+        <is>
+          <t>6.93 Days</t>
+        </is>
+      </c>
+      <c r="AA88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-21 15:00:52.062 : [1]Nhận xét | Comments || N/A || Se coordinó con TM Flavio Ingaroca para que pueda proporcionar las evidencias fotográficas, sobre los cables en desuso (si es el caso). Queda pendiente el envío de las mismas. </t>
+        </is>
+      </c>
+      <c r="AB88" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC88" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD88" s="8" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="AE88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG88" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH88" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI88" s="8" t="inlineStr">
+        <is>
+          <t>Se coordinó con TM Flavio Ingaroca para que pueda proporcionar las evidencias fotográficas, sobre los cables en desuso (si es el caso). Queda pendiente el envío de las mismas.</t>
+        </is>
+      </c>
+      <c r="AJ88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL88" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="89" customHeight="true" ht="12.5">
+      <c r="A89" s="11" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260518_1349147</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>S-2026-0191 / INSPECCIÓN CONJUNTA</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>vtp_fernando.munoz</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K89" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M89" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P89" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R89" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S89" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U89" s="8" t="inlineStr">
+        <is>
+          <t>18/05/2026 16:04:00</t>
+        </is>
+      </c>
+      <c r="V89" s="8" t="inlineStr">
+        <is>
+          <t>18/05/2026 16:32:00</t>
+        </is>
+      </c>
+      <c r="W89" s="8" t="inlineStr">
+        <is>
+          <t>27/05/2026 16:32:00</t>
+        </is>
+      </c>
+      <c r="X89" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z89" s="8" t="inlineStr">
+        <is>
+          <t>2.85 Days</t>
+        </is>
+      </c>
+      <c r="AA89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-21 12:27:23.122 : [1]Nhận xét | Comments || N/A || Se coordinó con el Ing. Luis Sánchez del Consorcio Santa Inés y con el TL Julio, Branch ICA, para llevar a cabo la inspección conjunta el día martes 26/05 a las 8am. 2026-05-21 12:30:13.363 : [1]Nhận xét | Comments || N/A || Se adjunta el número de contacto de los responsables:
+Ing. Luis Sánchez.  | Tlf.: +51 917 170 433
+TL ICA Julio Escate | Tlf.: +51 918 028 191 </t>
+        </is>
+      </c>
+      <c r="AB89" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC89" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD89" s="8" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AE89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG89" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH89" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI89" s="8" t="inlineStr">
+        <is>
+          <t>Se coordinó con el Ing. Luis Sánchez del Consorcio Santa Inés y con el TL Julio, Branch ICA, para llevar a cabo la inspección conjunta el día martes 26/05 a las 8am.,Se adjunta el número de contacto de los responsables:
+Ing. Luis Sánchez.  | Tlf.: +51 917 170 433
+TL ICA Julio Escate | Tlf.: +51 918 028 191</t>
+        </is>
+      </c>
+      <c r="AJ89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL89" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="90" customHeight="true" ht="12.5">
+      <c r="A90" s="11" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260515_1348636</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Carta Nº 010-2026-CCAL / INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>vtp_palomino.carlos</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K90" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M90" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P90" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R90" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S90" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U90" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 17:54:00</t>
+        </is>
+      </c>
+      <c r="V90" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 18:22:00</t>
+        </is>
+      </c>
+      <c r="W90" s="8" t="inlineStr">
+        <is>
+          <t>27/05/2026 08:00:00</t>
+        </is>
+      </c>
+      <c r="X90" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z90" s="8" t="inlineStr">
+        <is>
+          <t>0.77 Day</t>
+        </is>
+      </c>
+      <c r="AA90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-18 09:30:04.126 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona de trabajo indicada </t>
+        </is>
+      </c>
+      <c r="AB90" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC90" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD90" s="8" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="AE90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG90" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH90" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI90" s="8" t="inlineStr">
+        <is>
+          <t>Si hay interferencia en la zona de trabajo indicada</t>
+        </is>
+      </c>
+      <c r="AJ90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL90" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="91" customHeight="true" ht="12.5">
+      <c r="A91" s="11" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260518_1349170</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>CARTA N° 000869-2026-INVERMET-GP // INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>vtp_fernando.munoz</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M91" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P91" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R91" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S91" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="inlineStr">
+        <is>
+          <t>18/05/2026 16:26:00</t>
+        </is>
+      </c>
+      <c r="V91" s="8" t="inlineStr">
+        <is>
+          <t>18/05/2026 16:55:00</t>
+        </is>
+      </c>
+      <c r="W91" s="8" t="inlineStr">
+        <is>
+          <t>27/05/2026 16:55:00</t>
+        </is>
+      </c>
+      <c r="X91" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z91" s="8" t="inlineStr">
+        <is>
+          <t>1.00 Day</t>
+        </is>
+      </c>
+      <c r="AA91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-19 16:23:55.137 : [1]Nhận xét | Comments || N/A || Estimados,
+En respuesta a: [SR_VTP_20260518_1349170 / CARTA N° 000869-2026-INVERMET-GP]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
+Se adjunta link de documentos: 
+https://drive.google.com/drive/folders/1cBGXdrX9m3keAxVwt1KRKgfLQOjMNcMY?usp=drive_link </t>
+        </is>
+      </c>
+      <c r="AB91" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC91" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD91" s="8" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="AE91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG91" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH91" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI91" s="8" t="inlineStr">
+        <is>
+          <t>Estimados,
+En respuesta a: [SR_VTP_20260518_1349170 / CARTA N° 000869-2026-INVERMET-GP]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
+Se adjunta link de documentos: 
+https://drive.google.com/drive/folders/1cBGXdrX9m3keAxVwt1KRKgfLQOjMNcMY?usp=drive_link</t>
+        </is>
+      </c>
+      <c r="AJ91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL91" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="92" customHeight="true" ht="12.5">
+      <c r="A92" s="11" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
           <t>SR_VTP_20260515_1348573</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>Carta N.º ALF-PE-096-2026 / INFORMATIVO</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>vtp_fernando.munoz</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K87" s="8" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L87" s="8" t="inlineStr">
+      <c r="L92" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M87" s="8" t="inlineStr">
+      <c r="M92" s="8" t="inlineStr">
         <is>
           <t>In deadline</t>
         </is>
       </c>
-      <c r="N87" s="8" t="inlineStr">
+      <c r="N92" s="8" t="inlineStr">
         <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O92" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
         </is>
       </c>
-      <c r="P87" s="8" t="inlineStr">
+      <c r="P92" s="8" t="inlineStr">
         <is>
           <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
-      <c r="Q87" s="8" t="inlineStr">
+      <c r="Q92" s="8" t="inlineStr">
         <is>
           <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
-      <c r="R87" s="8" t="inlineStr">
+      <c r="R92" s="8" t="inlineStr">
         <is>
           <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
-      <c r="S87" s="8" t="inlineStr">
+      <c r="S92" s="8" t="inlineStr">
         <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
-      <c r="T87" s="8" t="inlineStr">
+      <c r="T92" s="8" t="inlineStr">
         <is>
           <t>Peru (VTP)</t>
         </is>
       </c>
-      <c r="U87" s="8" t="inlineStr">
+      <c r="U92" s="8" t="inlineStr">
         <is>
           <t>15/05/2026 15:42:00</t>
         </is>
       </c>
-      <c r="V87" s="8" t="inlineStr">
+      <c r="V92" s="8" t="inlineStr">
         <is>
           <t>15/05/2026 16:11:00</t>
         </is>
       </c>
-      <c r="W87" s="8" t="inlineStr">
+      <c r="W92" s="8" t="inlineStr">
         <is>
           <t>26/05/2026 16:11:00</t>
         </is>
       </c>
-      <c r="X87" s="8" t="inlineStr">
+      <c r="X92" s="8" t="inlineStr">
         <is>
           <t>22/05/2026 09:19:00</t>
         </is>
       </c>
-      <c r="Y87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z87" s="8" t="inlineStr">
+      <c r="Y92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z92" s="8" t="inlineStr">
         <is>
           <t>2.96 Days</t>
         </is>
       </c>
-      <c r="AA87" s="8" t="inlineStr">
+      <c r="AA92" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-20 14:50:04.241 : [1]Nhận xét | Comments || N/A || Estimados,
 En respuesta a: [SR_VTP_20260515_1348573 / Carta N.º ALF-PE-096-2026]
@@ -15713,42 +16675,42 @@
 https://drive.google.com/drive/folders/1NswlaTjOIz4mbF6boJobHF3DFB-Tzr1M?usp=drive_link </t>
         </is>
       </c>
-      <c r="AB87" s="8" t="inlineStr">
+      <c r="AB92" s="8" t="inlineStr">
         <is>
           <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
         </is>
       </c>
-      <c r="AC87" s="8" t="inlineStr">
+      <c r="AC92" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AD87" s="8" t="inlineStr">
+      <c r="AD92" s="8" t="inlineStr">
         <is>
           <t>4.73</t>
         </is>
       </c>
-      <c r="AE87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG87" s="8" t="inlineStr">
+      <c r="AE92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG92" s="8" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="AH87" s="8" t="inlineStr">
+      <c r="AH92" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AI87" s="8" t="inlineStr">
+      <c r="AI92" s="8" t="inlineStr">
         <is>
           <t>Estimados,
 En respuesta a: [SR_VTP_20260515_1348573 / Carta N.º ALF-PE-096-2026]
@@ -15757,152 +16719,152 @@
 https://drive.google.com/drive/folders/1NswlaTjOIz4mbF6boJobHF3DFB-Tzr1M?usp=drive_link</t>
         </is>
       </c>
-      <c r="AJ87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK87" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL87" s="8" t="inlineStr">
+      <c r="AJ92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK92" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL92" s="8" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="88" customHeight="true" ht="12.5">
-      <c r="A88" s="11" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
+    <row r="93" customHeight="true" ht="12.5">
+      <c r="A93" s="11" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>SR_VTP_20260515_1348602</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>Oficio Nº 6348-2026-MTC/19.03 // INFORMATIVO</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>vtp_fernando.munoz</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K88" s="8" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K93" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L88" s="8" t="inlineStr">
+      <c r="L93" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M88" s="8" t="inlineStr">
+      <c r="M93" s="8" t="inlineStr">
         <is>
           <t>In deadline</t>
         </is>
       </c>
-      <c r="N88" s="8" t="inlineStr">
+      <c r="N93" s="8" t="inlineStr">
         <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O93" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
         </is>
       </c>
-      <c r="P88" s="8" t="inlineStr">
+      <c r="P93" s="8" t="inlineStr">
         <is>
           <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
-      <c r="Q88" s="8" t="inlineStr">
+      <c r="Q93" s="8" t="inlineStr">
         <is>
           <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
-      <c r="R88" s="8" t="inlineStr">
+      <c r="R93" s="8" t="inlineStr">
         <is>
           <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
-      <c r="S88" s="8" t="inlineStr">
+      <c r="S93" s="8" t="inlineStr">
         <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
-      <c r="T88" s="8" t="inlineStr">
+      <c r="T93" s="8" t="inlineStr">
         <is>
           <t>Peru (VTP)</t>
         </is>
       </c>
-      <c r="U88" s="8" t="inlineStr">
+      <c r="U93" s="8" t="inlineStr">
         <is>
           <t>15/05/2026 16:16:00</t>
         </is>
       </c>
-      <c r="V88" s="8" t="inlineStr">
+      <c r="V93" s="8" t="inlineStr">
         <is>
           <t>15/05/2026 16:45:00</t>
         </is>
       </c>
-      <c r="W88" s="8" t="inlineStr">
+      <c r="W93" s="8" t="inlineStr">
         <is>
           <t>26/05/2026 16:45:00</t>
         </is>
       </c>
-      <c r="X88" s="8" t="inlineStr">
+      <c r="X93" s="8" t="inlineStr">
         <is>
           <t>22/05/2026 09:19:00</t>
         </is>
       </c>
-      <c r="Y88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z88" s="8" t="inlineStr">
+      <c r="Y93" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z93" s="8" t="inlineStr">
         <is>
           <t>2.05 Days</t>
         </is>
       </c>
-      <c r="AA88" s="8" t="inlineStr">
+      <c r="AA93" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-19 17:33:26.356 : [1]Nhận xét | Comments || N/A || Estimados,
 En respuesta a: [SR_VTP_20260515_1348602 / Oficio Nº 6348-2026-MTC]
@@ -15911,42 +16873,42 @@
 https://drive.google.com/drive/folders/1WB3hqS7dgGKvtQAxKSlVeOCxg6qGxnDZ?usp=drive_link </t>
         </is>
       </c>
-      <c r="AB88" s="8" t="inlineStr">
+      <c r="AB93" s="8" t="inlineStr">
         <is>
           <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
         </is>
       </c>
-      <c r="AC88" s="8" t="inlineStr">
+      <c r="AC93" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AD88" s="8" t="inlineStr">
+      <c r="AD93" s="8" t="inlineStr">
         <is>
           <t>4.71</t>
         </is>
       </c>
-      <c r="AE88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG88" s="8" t="inlineStr">
+      <c r="AE93" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF93" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG93" s="8" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="AH88" s="8" t="inlineStr">
+      <c r="AH93" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AI88" s="8" t="inlineStr">
+      <c r="AI93" s="8" t="inlineStr">
         <is>
           <t>Estimados,
 En respuesta a: [SR_VTP_20260515_1348602 / Oficio Nº 6348-2026-MTC]
@@ -15955,962 +16917,6 @@
 https://drive.google.com/drive/folders/1WB3hqS7dgGKvtQAxKSlVeOCxg6qGxnDZ?usp=drive_link</t>
         </is>
       </c>
-      <c r="AJ88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL88" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="89" customHeight="true" ht="12.5">
-      <c r="A89" s="11" t="n">
-        <v>81.0</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260515_1348619</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>OFICIO N° 6425-2026-MTC/19.03 / INFORMATIVO</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>vtp_palomino.carlos</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K89" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L89" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M89" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N89" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O89" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P89" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q89" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R89" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S89" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U89" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 16:33:00</t>
-        </is>
-      </c>
-      <c r="V89" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 17:01:00</t>
-        </is>
-      </c>
-      <c r="W89" s="8" t="inlineStr">
-        <is>
-          <t>26/05/2026 17:01:00</t>
-        </is>
-      </c>
-      <c r="X89" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z89" s="8" t="inlineStr">
-        <is>
-          <t>2.70 Days</t>
-        </is>
-      </c>
-      <c r="AA89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 09:26:19.339 : [1]Nhận xét | Comments || N/A || Si hay intereferencia en la zona indicada </t>
-        </is>
-      </c>
-      <c r="AB89" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC89" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD89" s="8" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="AE89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG89" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH89" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI89" s="8" t="inlineStr">
-        <is>
-          <t>Si hay intereferencia en la zona indicada</t>
-        </is>
-      </c>
-      <c r="AJ89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL89" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="90" customHeight="true" ht="12.5">
-      <c r="A90" s="11" t="n">
-        <v>82.0</v>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260515_1348605</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Oficio Nº 6371-2026-MTC/19.03 // INFORMATIVO</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>vtp_palomino.carlos</t>
-        </is>
-      </c>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K90" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M90" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N90" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O90" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P90" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q90" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R90" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S90" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U90" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 16:24:00</t>
-        </is>
-      </c>
-      <c r="V90" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 16:54:00</t>
-        </is>
-      </c>
-      <c r="W90" s="8" t="inlineStr">
-        <is>
-          <t>26/05/2026 16:54:00</t>
-        </is>
-      </c>
-      <c r="X90" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z90" s="8" t="inlineStr">
-        <is>
-          <t>2.73 Days</t>
-        </is>
-      </c>
-      <c r="AA90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 09:59:51.335 : [1]Nhận xét | Comments || N/A || si hay interferencia en la zona indicada </t>
-        </is>
-      </c>
-      <c r="AB90" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC90" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD90" s="8" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="AE90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG90" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH90" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI90" s="8" t="inlineStr">
-        <is>
-          <t>si hay interferencia en la zona indicada</t>
-        </is>
-      </c>
-      <c r="AJ90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL90" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="91" customHeight="true" ht="12.5">
-      <c r="A91" s="11" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260518_1349152</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>CARTA N° 06 – 2026 / INFORMATIVO</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>vtp_palomino.carlos</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K91" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L91" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M91" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N91" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O91" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P91" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q91" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R91" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S91" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U91" s="8" t="inlineStr">
-        <is>
-          <t>18/05/2026 16:16:00</t>
-        </is>
-      </c>
-      <c r="V91" s="8" t="inlineStr">
-        <is>
-          <t>18/05/2026 16:44:00</t>
-        </is>
-      </c>
-      <c r="W91" s="8" t="inlineStr">
-        <is>
-          <t>27/05/2026 16:44:00</t>
-        </is>
-      </c>
-      <c r="X91" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z91" s="8" t="inlineStr">
-        <is>
-          <t>1.73 Days</t>
-        </is>
-      </c>
-      <c r="AA91" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 09:47:54.337 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
-        </is>
-      </c>
-      <c r="AB91" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC91" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD91" s="8" t="inlineStr">
-        <is>
-          <t>3.71</t>
-        </is>
-      </c>
-      <c r="AE91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG91" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH91" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI91" s="8" t="inlineStr">
-        <is>
-          <t>Si hay interferencia en la zona indicada</t>
-        </is>
-      </c>
-      <c r="AJ91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL91" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="92" customHeight="true" ht="12.5">
-      <c r="A92" s="11" t="n">
-        <v>84.0</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260515_1348506</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>Carta N° 026-2026_05MAY2026 / INFORMATIVO</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>vtp_fernando.munoz</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K92" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L92" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M92" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N92" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O92" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P92" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q92" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R92" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S92" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T92" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U92" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 11:24:00</t>
-        </is>
-      </c>
-      <c r="V92" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 11:44:00</t>
-        </is>
-      </c>
-      <c r="W92" s="8" t="inlineStr">
-        <is>
-          <t>26/05/2026 11:44:00</t>
-        </is>
-      </c>
-      <c r="X92" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z92" s="8" t="inlineStr">
-        <is>
-          <t>2.21 Days</t>
-        </is>
-      </c>
-      <c r="AA92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-19 16:32:17.078 : [1]Nhận xét | Comments || N/A || Estimados,
-En respuesta a: [SR_VTP_20260515_1348506 / Carta N° 026-2026_05MAY2026]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que NO contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud. </t>
-        </is>
-      </c>
-      <c r="AB92" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC92" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD92" s="8" t="inlineStr">
-        <is>
-          <t>4.91</t>
-        </is>
-      </c>
-      <c r="AE92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG92" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH92" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI92" s="8" t="inlineStr">
-        <is>
-          <t>Estimados,
-En respuesta a: [SR_VTP_20260515_1348506 / Carta N° 026-2026_05MAY2026]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que NO contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.</t>
-        </is>
-      </c>
-      <c r="AJ92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL92" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="93" customHeight="true" ht="12.5">
-      <c r="A93" s="11" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260513_1347945</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>SE SOLICITA TODA DOCUMENTACIÓN AVANZADA EN SU MOMENTO POR PARTE DE JUAN SERNAQUE REFERENTE A PROYECTO ANILLO VIAL PERIFERICO</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>vtp_bryam.broncano</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J93" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K93" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M93" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N93" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O93" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P93" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q93" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R93" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S93" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T93" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U93" s="8" t="inlineStr">
-        <is>
-          <t>13/05/2026 15:24:00</t>
-        </is>
-      </c>
-      <c r="V93" s="8" t="inlineStr">
-        <is>
-          <t>13/05/2026 15:47:00</t>
-        </is>
-      </c>
-      <c r="W93" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 15:47:00</t>
-        </is>
-      </c>
-      <c r="X93" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y93" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z93" s="8" t="inlineStr">
-        <is>
-          <t>6.00 Days</t>
-        </is>
-      </c>
-      <c r="AA93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-21 12:15:09.303 : [1]Nhận xét | Comments || N/A || se suben a carpeta los archvios que se recopilo de juan 2026-05-21 12:29:19.076 : [1]Nhận xét | Comments || N/A || archivos recuperados
-https://drive.google.com/drive/folders/1fdpOW-K8Co-nex1AGVCawTa64W4Wryv1?usp=drive_link 2026-05-21 12:30:12.943 : [1]Nhận xét | Comments || N/A || carpeta de juan: https://drive.google.com/drive/folders/12gs_ZWlOGriV-H-bMqFoGZdyob56uLBo?usp=drive_link </t>
-        </is>
-      </c>
-      <c r="AB93" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC93" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD93" s="8" t="inlineStr">
-        <is>
-          <t>6.75</t>
-        </is>
-      </c>
-      <c r="AE93" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF93" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG93" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH93" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI93" s="8" t="inlineStr">
-        <is>
-          <t>se suben a carpeta los archvios que se recopilo de juan,archivos recuperados
-https://drive.google.com/drive/folders/1fdpOW-K8Co-nex1AGVCawTa64W4Wryv1?usp=drive_link,carpeta de juan: https://drive.google.com/drive/folders/12gs_ZWlOGriV-H-bMqFoGZdyob56uLBo?usp=drive_link</t>
-        </is>
-      </c>
       <c r="AJ93" s="8" t="inlineStr">
         <is>
           <t/>
@@ -16933,7 +16939,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260518_1349170</t>
+          <t>SR_VTP_20260515_1348619</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -16943,7 +16949,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>CARTA N° 000869-2026-INVERMET-GP // INFORMATIVO</t>
+          <t>OFICIO N° 6425-2026-MTC/19.03 / INFORMATIVO</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -16953,7 +16959,7 @@
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>vtp_fernando.munoz</t>
+          <t>vtp_palomino.carlos</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
@@ -17028,17 +17034,17 @@
       </c>
       <c r="U94" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 16:26:00</t>
+          <t>15/05/2026 16:33:00</t>
         </is>
       </c>
       <c r="V94" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 16:55:00</t>
+          <t>15/05/2026 17:01:00</t>
         </is>
       </c>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>27/05/2026 16:55:00</t>
+          <t>26/05/2026 17:01:00</t>
         </is>
       </c>
       <c r="X94" s="8" t="inlineStr">
@@ -17053,16 +17059,12 @@
       </c>
       <c r="Z94" s="8" t="inlineStr">
         <is>
-          <t>1.00 Day</t>
+          <t>2.70 Days</t>
         </is>
       </c>
       <c r="AA94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-19 16:23:55.137 : [1]Nhận xét | Comments || N/A || Estimados,
-En respuesta a: [SR_VTP_20260518_1349170 / CARTA N° 000869-2026-INVERMET-GP]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
-Se adjunta link de documentos: 
-https://drive.google.com/drive/folders/1cBGXdrX9m3keAxVwt1KRKgfLQOjMNcMY?usp=drive_link </t>
+          <t xml:space="preserve">2026-05-20 09:26:19.339 : [1]Nhận xét | Comments || N/A || Si hay intereferencia en la zona indicada </t>
         </is>
       </c>
       <c r="AB94" s="8" t="inlineStr">
@@ -17077,7 +17079,7 @@
       </c>
       <c r="AD94" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AE94" s="8" t="inlineStr">
@@ -17102,11 +17104,7 @@
       </c>
       <c r="AI94" s="8" t="inlineStr">
         <is>
-          <t>Estimados,
-En respuesta a: [SR_VTP_20260518_1349170 / CARTA N° 000869-2026-INVERMET-GP]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
-Se adjunta link de documentos: 
-https://drive.google.com/drive/folders/1cBGXdrX9m3keAxVwt1KRKgfLQOjMNcMY?usp=drive_link</t>
+          <t>Si hay intereferencia en la zona indicada</t>
         </is>
       </c>
       <c r="AJ94" s="8" t="inlineStr">
@@ -17131,7 +17129,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260515_1348636</t>
+          <t>SR_VTP_20260515_1348605</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -17141,7 +17139,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Carta Nº 010-2026-CCAL / INFORMATIVO</t>
+          <t>Oficio Nº 6371-2026-MTC/19.03 // INFORMATIVO</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -17226,17 +17224,17 @@
       </c>
       <c r="U95" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 17:54:00</t>
+          <t>15/05/2026 16:24:00</t>
         </is>
       </c>
       <c r="V95" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 18:22:00</t>
+          <t>15/05/2026 16:54:00</t>
         </is>
       </c>
       <c r="W95" s="8" t="inlineStr">
         <is>
-          <t>27/05/2026 08:00:00</t>
+          <t>26/05/2026 16:54:00</t>
         </is>
       </c>
       <c r="X95" s="8" t="inlineStr">
@@ -17251,12 +17249,12 @@
       </c>
       <c r="Z95" s="8" t="inlineStr">
         <is>
-          <t>0.77 Day</t>
+          <t>2.73 Days</t>
         </is>
       </c>
       <c r="AA95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18 09:30:04.126 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona de trabajo indicada </t>
+          <t xml:space="preserve">2026-05-20 09:59:51.335 : [1]Nhận xét | Comments || N/A || si hay interferencia en la zona indicada </t>
         </is>
       </c>
       <c r="AB95" s="8" t="inlineStr">
@@ -17271,7 +17269,7 @@
       </c>
       <c r="AD95" s="8" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AE95" s="8" t="inlineStr">
@@ -17296,7 +17294,7 @@
       </c>
       <c r="AI95" s="8" t="inlineStr">
         <is>
-          <t>Si hay interferencia en la zona de trabajo indicada</t>
+          <t>si hay interferencia en la zona indicada</t>
         </is>
       </c>
       <c r="AJ95" s="8" t="inlineStr">
@@ -17321,7 +17319,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260515_1348591</t>
+          <t>SR_VTP_20260518_1349152</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -17331,7 +17329,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Oficio Nº 6346-2026-MTC/19.03 // INFORMATIVO</t>
+          <t>CARTA N° 06 – 2026 / INFORMATIVO</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -17416,17 +17414,17 @@
       </c>
       <c r="U96" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 16:19:00</t>
+          <t>18/05/2026 16:16:00</t>
         </is>
       </c>
       <c r="V96" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 16:49:00</t>
+          <t>18/05/2026 16:44:00</t>
         </is>
       </c>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 16:49:00</t>
+          <t>27/05/2026 16:44:00</t>
         </is>
       </c>
       <c r="X96" s="8" t="inlineStr">
@@ -17441,12 +17439,12 @@
       </c>
       <c r="Z96" s="8" t="inlineStr">
         <is>
-          <t>2.72 Days</t>
+          <t>1.73 Days</t>
         </is>
       </c>
       <c r="AA96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 09:40:23.683 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
+          <t xml:space="preserve">2026-05-20 09:47:54.337 : [1]Nhận xét | Comments || N/A || Si hay interferencia en la zona indicada </t>
         </is>
       </c>
       <c r="AB96" s="8" t="inlineStr">
@@ -17461,7 +17459,7 @@
       </c>
       <c r="AD96" s="8" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AE96" s="8" t="inlineStr">
@@ -17511,7 +17509,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260512_1347612</t>
+          <t>SR_VTP_20260515_1348506</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -17521,7 +17519,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>GT-0658-2026 / SOLICITUD DE IDENTIFICACIÓN DE UBICACIONES DE CABLEADO EN MAL ESTADO</t>
+          <t>Carta N° 026-2026_05MAY2026 / INFORMATIVO</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -17606,17 +17604,17 @@
       </c>
       <c r="U97" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 16:42:00</t>
+          <t>15/05/2026 11:24:00</t>
         </is>
       </c>
       <c r="V97" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 17:11:00</t>
+          <t>15/05/2026 11:44:00</t>
         </is>
       </c>
       <c r="W97" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 17:11:00</t>
+          <t>26/05/2026 11:44:00</t>
         </is>
       </c>
       <c r="X97" s="8" t="inlineStr">
@@ -17631,12 +17629,14 @@
       </c>
       <c r="Z97" s="8" t="inlineStr">
         <is>
-          <t>6.93 Days</t>
+          <t>2.21 Days</t>
         </is>
       </c>
       <c r="AA97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-21 15:00:52.062 : [1]Nhận xét | Comments || N/A || Se coordinó con TM Flavio Ingaroca para que pueda proporcionar las evidencias fotográficas, sobre los cables en desuso (si es el caso). Queda pendiente el envío de las mismas. </t>
+          <t xml:space="preserve">2026-05-19 16:32:17.078 : [1]Nhận xét | Comments || N/A || Estimados,
+En respuesta a: [SR_VTP_20260515_1348506 / Carta N° 026-2026_05MAY2026]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que NO contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud. </t>
         </is>
       </c>
       <c r="AB97" s="8" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="AD97" s="8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AE97" s="8" t="inlineStr">
@@ -17676,7 +17676,9 @@
       </c>
       <c r="AI97" s="8" t="inlineStr">
         <is>
-          <t>Se coordinó con TM Flavio Ingaroca para que pueda proporcionar las evidencias fotográficas, sobre los cables en desuso (si es el caso). Queda pendiente el envío de las mismas.</t>
+          <t>Estimados,
+En respuesta a: [SR_VTP_20260515_1348506 / Carta N° 026-2026_05MAY2026]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que NO contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.</t>
         </is>
       </c>
       <c r="AJ97" s="8" t="inlineStr">
@@ -17701,7 +17703,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260518_1349147</t>
+          <t>SR_VTP_20260513_1347945</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -17711,7 +17713,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>S-2026-0191 / INSPECCIÓN CONJUNTA</t>
+          <t>SE SOLICITA TODA DOCUMENTACIÓN AVANZADA EN SU MOMENTO POR PARTE DE JUAN SERNAQUE REFERENTE A PROYECTO ANILLO VIAL PERIFERICO</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -17721,7 +17723,7 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>vtp_fernando.munoz</t>
+          <t>vtp_bryam.broncano</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
@@ -17796,17 +17798,17 @@
       </c>
       <c r="U98" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 16:04:00</t>
+          <t>13/05/2026 15:24:00</t>
         </is>
       </c>
       <c r="V98" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 16:32:00</t>
+          <t>13/05/2026 15:47:00</t>
         </is>
       </c>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>27/05/2026 16:32:00</t>
+          <t>22/05/2026 15:47:00</t>
         </is>
       </c>
       <c r="X98" s="8" t="inlineStr">
@@ -17821,14 +17823,13 @@
       </c>
       <c r="Z98" s="8" t="inlineStr">
         <is>
-          <t>2.85 Days</t>
+          <t>6.00 Days</t>
         </is>
       </c>
       <c r="AA98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-21 12:27:23.122 : [1]Nhận xét | Comments || N/A || Se coordinó con el Ing. Luis Sánchez del Consorcio Santa Inés y con el TL Julio, Branch ICA, para llevar a cabo la inspección conjunta el día martes 26/05 a las 8am. 2026-05-21 12:30:13.363 : [1]Nhận xét | Comments || N/A || Se adjunta el número de contacto de los responsables:
-Ing. Luis Sánchez.  | Tlf.: +51 917 170 433
-TL ICA Julio Escate | Tlf.: +51 918 028 191 </t>
+          <t xml:space="preserve">2026-05-21 12:15:09.303 : [1]Nhận xét | Comments || N/A || se suben a carpeta los archvios que se recopilo de juan 2026-05-21 12:29:19.076 : [1]Nhận xét | Comments || N/A || archivos recuperados
+https://drive.google.com/drive/folders/1fdpOW-K8Co-nex1AGVCawTa64W4Wryv1?usp=drive_link 2026-05-21 12:30:12.943 : [1]Nhận xét | Comments || N/A || carpeta de juan: https://drive.google.com/drive/folders/12gs_ZWlOGriV-H-bMqFoGZdyob56uLBo?usp=drive_link </t>
         </is>
       </c>
       <c r="AB98" s="8" t="inlineStr">
@@ -17843,7 +17844,7 @@
       </c>
       <c r="AD98" s="8" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AE98" s="8" t="inlineStr">
@@ -17868,9 +17869,8 @@
       </c>
       <c r="AI98" s="8" t="inlineStr">
         <is>
-          <t>Se coordinó con el Ing. Luis Sánchez del Consorcio Santa Inés y con el TL Julio, Branch ICA, para llevar a cabo la inspección conjunta el día martes 26/05 a las 8am.,Se adjunta el número de contacto de los responsables:
-Ing. Luis Sánchez.  | Tlf.: +51 917 170 433
-TL ICA Julio Escate | Tlf.: +51 918 028 191</t>
+          <t>se suben a carpeta los archvios que se recopilo de juan,archivos recuperados
+https://drive.google.com/drive/folders/1fdpOW-K8Co-nex1AGVCawTa64W4Wryv1?usp=drive_link,carpeta de juan: https://drive.google.com/drive/folders/12gs_ZWlOGriV-H-bMqFoGZdyob56uLBo?usp=drive_link</t>
         </is>
       </c>
       <c r="AJ98" s="8" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260515_1348622</t>
+          <t>SR_VTP_20260515_1348596</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -17905,7 +17905,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>CARTA N° 000844-2026-INVERMET-GP / CRONOGRAMA Y PRESUPUESTO / DEADLINE: 10/06</t>
+          <t>OFICIO N° 6426-2026-MTC/19.03 / INFORMATIVO</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -17915,7 +17915,7 @@
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>vtp_bryam.broncano</t>
+          <t>vtp_palomino.carlos</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -17990,17 +17990,17 @@
       </c>
       <c r="U99" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 17:11:00</t>
+          <t>15/05/2026 16:28:00</t>
         </is>
       </c>
       <c r="V99" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 17:28:00</t>
+          <t>15/05/2026 16:56:00</t>
         </is>
       </c>
       <c r="W99" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 17:28:00</t>
+          <t>26/05/2026 16:56:00</t>
         </is>
       </c>
       <c r="X99" s="8" t="inlineStr">
@@ -18015,12 +18015,12 @@
       </c>
       <c r="Z99" s="8" t="inlineStr">
         <is>
-          <t>3.92 Days</t>
+          <t>0.70 Day</t>
         </is>
       </c>
       <c r="AA99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-21 15:08:30.179 : [1]Nhận xét | Comments || N/A || se tienen los documentos listos 2026-05-21 15:10:29.59 : [1]Nhận xét | Comments || N/A || https://drive.google.com/drive/folders/126-CzQ8E9JenK6RBGxlCOf7EWtMOeAfG?usp=drive_link </t>
+          <t xml:space="preserve">2026-05-18 09:13:51.206 : [1]Nhận xét | Comments || N/A || No hay interferencia en la zona indicada </t>
         </is>
       </c>
       <c r="AB99" s="8" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="AD99" s="8" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AE99" s="8" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AI99" s="8" t="inlineStr">
         <is>
-          <t>se tienen los documentos listos,https://drive.google.com/drive/folders/126-CzQ8E9JenK6RBGxlCOf7EWtMOeAfG?usp=drive_link</t>
+          <t>No hay interferencia en la zona indicada</t>
         </is>
       </c>
       <c r="AJ99" s="8" t="inlineStr">
@@ -18085,130 +18085,1104 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
+          <t>SR_VTP_20260514_1348313</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>OFICIO N° 6528-2026-MTC/19.03/ INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>vtp_fernando.munoz</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K100" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N100" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O100" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P100" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q100" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R100" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S100" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T100" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U100" s="8" t="inlineStr">
+        <is>
+          <t>14/05/2026 18:25:00</t>
+        </is>
+      </c>
+      <c r="V100" s="8" t="inlineStr">
+        <is>
+          <t>14/05/2026 18:53:00</t>
+        </is>
+      </c>
+      <c r="W100" s="8" t="inlineStr">
+        <is>
+          <t>26/05/2026 08:00:00</t>
+        </is>
+      </c>
+      <c r="X100" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z100" s="8" t="inlineStr">
+        <is>
+          <t>1.75 Days</t>
+        </is>
+      </c>
+      <c r="AA100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-18 12:24:13.827 : [1]Nhận xét | Comments || N/A || Estimados,
+En respuesta a: [SR_VTP_20260514_1348313 / OFICIO N° 6528-2026-MTC]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
+Se adjunta link de documentos: 
+https://drive.google.com/drive/folders/1FjgLZL9e8rlG8qG_kvMzV3ytFYVWx41Q?usp=drive_link </t>
+        </is>
+      </c>
+      <c r="AB100" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC100" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD100" s="8" t="inlineStr">
+        <is>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="AE100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG100" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH100" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI100" s="8" t="inlineStr">
+        <is>
+          <t>Estimados,
+En respuesta a: [SR_VTP_20260514_1348313 / OFICIO N° 6528-2026-MTC]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
+Se adjunta link de documentos: 
+https://drive.google.com/drive/folders/1FjgLZL9e8rlG8qG_kvMzV3ytFYVWx41Q?usp=drive_link</t>
+        </is>
+      </c>
+      <c r="AJ100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL100" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="101" customHeight="true" ht="12.5">
+      <c r="A101" s="11" t="n">
+        <v>93.0</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260515_1348600</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>Oficio Nº 6257-2026-MTC/19.03 // INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>vtp_fernando.munoz</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N101" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O101" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P101" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q101" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R101" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S101" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T101" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U101" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 16:13:00</t>
+        </is>
+      </c>
+      <c r="V101" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 16:42:00</t>
+        </is>
+      </c>
+      <c r="W101" s="8" t="inlineStr">
+        <is>
+          <t>26/05/2026 16:42:00</t>
+        </is>
+      </c>
+      <c r="X101" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z101" s="8" t="inlineStr">
+        <is>
+          <t>2.96 Days</t>
+        </is>
+      </c>
+      <c r="AA101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-20 15:16:21.824 : [1]Nhận xét | Comments || N/A || Estimados,
+En respuesta a: [SR_VTP_20260515_1348600 / Oficio Nº 6257-2026-MTC]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
+Se adjunta link de documentos: 
+https://drive.google.com/drive/folders/11pcKOkUdo8NFkLIDfr4BS3PBfgt9SWK3?usp=drive_link </t>
+        </is>
+      </c>
+      <c r="AB101" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC101" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD101" s="8" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AE101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG101" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH101" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI101" s="8" t="inlineStr">
+        <is>
+          <t>Estimados,
+En respuesta a: [SR_VTP_20260515_1348600 / Oficio Nº 6257-2026-MTC]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
+Se adjunta link de documentos: 
+https://drive.google.com/drive/folders/11pcKOkUdo8NFkLIDfr4BS3PBfgt9SWK3?usp=drive_link</t>
+        </is>
+      </c>
+      <c r="AJ101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL101" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="102" customHeight="true" ht="12.5">
+      <c r="A102" s="11" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260515_1348481</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Carta PSR2-F2-CPC-OTR-GEN-GLB-CAR-0068 // INSPECCION CONJUNTA</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>vtp_fernando.munoz</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K102" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M102" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N102" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O102" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P102" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q102" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R102" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S102" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T102" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U102" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 11:04:00</t>
+        </is>
+      </c>
+      <c r="V102" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 11:33:00</t>
+        </is>
+      </c>
+      <c r="W102" s="8" t="inlineStr">
+        <is>
+          <t>26/05/2026 11:33:00</t>
+        </is>
+      </c>
+      <c r="X102" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z102" s="8" t="inlineStr">
+        <is>
+          <t>1.15 Days</t>
+        </is>
+      </c>
+      <c r="AA102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-18 14:32:45.513 : [1]Nhận xét | Comments || N/A || Se coordinó con TM LIM4 y con representante de MTC, Jorge Fernández, para realizar la inspección conjunta el día viernes 22/05 a las 10.30 am. Queda pendiente la confirmación de la persona que será asignada para acompañar la inspección por parte de LIM4. </t>
+        </is>
+      </c>
+      <c r="AB102" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC102" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD102" s="8" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="AE102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG102" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH102" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI102" s="8" t="inlineStr">
+        <is>
+          <t>Se coordinó con TM LIM4 y con representante de MTC, Jorge Fernández, para realizar la inspección conjunta el día viernes 22/05 a las 10.30 am. Queda pendiente la confirmación de la persona que será asignada para acompañar la inspección por parte de LIM4.</t>
+        </is>
+      </c>
+      <c r="AJ102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL102" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="103" customHeight="true" ht="12.5">
+      <c r="A103" s="11" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260515_1348585</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Oficio Nº 6258-2026-MTC/19.03 // INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>vtp_fernando.munoz</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K103" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M103" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N103" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O103" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P103" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q103" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R103" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S103" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T103" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U103" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 16:11:00</t>
+        </is>
+      </c>
+      <c r="V103" s="8" t="inlineStr">
+        <is>
+          <t>15/05/2026 16:40:00</t>
+        </is>
+      </c>
+      <c r="W103" s="8" t="inlineStr">
+        <is>
+          <t>26/05/2026 16:40:00</t>
+        </is>
+      </c>
+      <c r="X103" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z103" s="8" t="inlineStr">
+        <is>
+          <t>2.07 Days</t>
+        </is>
+      </c>
+      <c r="AA103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-19 17:57:02.798 : [1]Nhận xét | Comments || N/A || Estimados,
+En respuesta a: [SR_VTP_20260515_1348585 / Oficio Nº 6258-2026-MTC]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
+Se adjunta link de documentos: 
+https://drive.google.com/drive/folders/1RfoR1HVDND9HyEPsj6QBsmUm1hFiJsjr?usp=drive_link </t>
+        </is>
+      </c>
+      <c r="AB103" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC103" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD103" s="8" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="AE103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG103" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH103" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI103" s="8" t="inlineStr">
+        <is>
+          <t>Estimados,
+En respuesta a: [SR_VTP_20260515_1348585 / Oficio Nº 6258-2026-MTC]
+Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
+Se adjunta link de documentos: 
+https://drive.google.com/drive/folders/1RfoR1HVDND9HyEPsj6QBsmUm1hFiJsjr?usp=drive_link</t>
+        </is>
+      </c>
+      <c r="AJ103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL103" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="104" customHeight="true" ht="12.5">
+      <c r="A104" s="11" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>SR_VTP_20260519_1349444</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>SO-MPM-LN-CT-588-2026 // INSPECCIÓN CONJUNTA</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>vtp_fernando.munoz</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K104" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L104" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M104" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N104" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O104" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P104" s="8" t="inlineStr">
+        <is>
+          <t>VTP_CABLE OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Q104" s="8" t="inlineStr">
+        <is>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
+        </is>
+      </c>
+      <c r="R104" s="8" t="inlineStr">
+        <is>
+          <t>vtp_jesus.gonzales.1</t>
+        </is>
+      </c>
+      <c r="S104" s="8" t="inlineStr">
+        <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+        </is>
+      </c>
+      <c r="T104" s="8" t="inlineStr">
+        <is>
+          <t>Peru (VTP)</t>
+        </is>
+      </c>
+      <c r="U104" s="8" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:51:00</t>
+        </is>
+      </c>
+      <c r="V104" s="8" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:19:00</t>
+        </is>
+      </c>
+      <c r="W104" s="8" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:19:00</t>
+        </is>
+      </c>
+      <c r="X104" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="Y104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z104" s="8" t="inlineStr">
+        <is>
+          <t>2.11 Days</t>
+        </is>
+      </c>
+      <c r="AA104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-21 17:32:17.518 : [1]Nhận xét | Comments || N/A || Se coordinó con TM LIM1 para realizar la inspección conjunta según la fecha propuesta por la Constructora MPM. El encuentro se pactó para ser realizado a las 10AM. </t>
+        </is>
+      </c>
+      <c r="AB104" s="8" t="inlineStr">
+        <is>
+          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
+        </is>
+      </c>
+      <c r="AC104" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD104" s="8" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AE104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG104" s="8" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AH104" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AI104" s="8" t="inlineStr">
+        <is>
+          <t>Se coordinó con TM LIM1 para realizar la inspección conjunta según la fecha propuesta por la Constructora MPM. El encuentro se pactó para ser realizado a las 10AM.</t>
+        </is>
+      </c>
+      <c r="AJ104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL104" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="105" customHeight="true" ht="12.5">
+      <c r="A105" s="11" t="n">
+        <v>97.0</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
           <t>SR_VTP_20260515_1348581</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>Oficio Nº 6259-2026-MTC/19.03 // INFORMATIVO</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F100" s="8" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>vtp_fernando.munoz</t>
         </is>
       </c>
-      <c r="G100" s="8" t="inlineStr">
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K100" s="8" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K105" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L100" s="8" t="inlineStr">
+      <c r="L105" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M100" s="8" t="inlineStr">
+      <c r="M105" s="8" t="inlineStr">
         <is>
           <t>In deadline</t>
         </is>
       </c>
-      <c r="N100" s="8" t="inlineStr">
+      <c r="N105" s="8" t="inlineStr">
         <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O105" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
         </is>
       </c>
-      <c r="P100" s="8" t="inlineStr">
+      <c r="P105" s="8" t="inlineStr">
         <is>
           <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
-      <c r="Q100" s="8" t="inlineStr">
+      <c r="Q105" s="8" t="inlineStr">
         <is>
           <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
-      <c r="R100" s="8" t="inlineStr">
+      <c r="R105" s="8" t="inlineStr">
         <is>
           <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
-      <c r="S100" s="8" t="inlineStr">
+      <c r="S105" s="8" t="inlineStr">
         <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
-      <c r="T100" s="8" t="inlineStr">
+      <c r="T105" s="8" t="inlineStr">
         <is>
           <t>Peru (VTP)</t>
         </is>
       </c>
-      <c r="U100" s="8" t="inlineStr">
+      <c r="U105" s="8" t="inlineStr">
         <is>
           <t>15/05/2026 16:05:00</t>
         </is>
       </c>
-      <c r="V100" s="8" t="inlineStr">
+      <c r="V105" s="8" t="inlineStr">
         <is>
           <t>15/05/2026 16:34:00</t>
         </is>
       </c>
-      <c r="W100" s="8" t="inlineStr">
+      <c r="W105" s="8" t="inlineStr">
         <is>
           <t>26/05/2026 16:34:00</t>
         </is>
       </c>
-      <c r="X100" s="8" t="inlineStr">
+      <c r="X105" s="8" t="inlineStr">
         <is>
           <t>22/05/2026 09:19:00</t>
         </is>
       </c>
-      <c r="Y100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z100" s="8" t="inlineStr">
+      <c r="Y105" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z105" s="8" t="inlineStr">
         <is>
           <t>2.94 Days</t>
         </is>
       </c>
-      <c r="AA100" s="8" t="inlineStr">
+      <c r="AA105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-20 14:35:28.026 : [1]Nhận xét | Comments || N/A || Estimados,
 En respuesta a: [SR_VTP_20260515_1348581 / Oficio Nº 6259-2026-MTC]
@@ -18217,42 +19191,42 @@
 https://drive.google.com/drive/folders/1gxvjrjQqVl4dQw7oONniCAyleqk3TMQ5?usp=drive_link </t>
         </is>
       </c>
-      <c r="AB100" s="8" t="inlineStr">
+      <c r="AB105" s="8" t="inlineStr">
         <is>
           <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
         </is>
       </c>
-      <c r="AC100" s="8" t="inlineStr">
+      <c r="AC105" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AD100" s="8" t="inlineStr">
+      <c r="AD105" s="8" t="inlineStr">
         <is>
           <t>4.72</t>
         </is>
       </c>
-      <c r="AE100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG100" s="8" t="inlineStr">
+      <c r="AE105" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF105" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG105" s="8" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="AH100" s="8" t="inlineStr">
+      <c r="AH105" s="8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AI100" s="8" t="inlineStr">
+      <c r="AI105" s="8" t="inlineStr">
         <is>
           <t>Estimados,
 En respuesta a: [SR_VTP_20260515_1348581 / Oficio Nº 6259-2026-MTC]
@@ -18261,980 +19235,6 @@
 https://drive.google.com/drive/folders/1gxvjrjQqVl4dQw7oONniCAyleqk3TMQ5?usp=drive_link</t>
         </is>
       </c>
-      <c r="AJ100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL100" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="101" customHeight="true" ht="12.5">
-      <c r="A101" s="11" t="n">
-        <v>93.0</v>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260519_1349444</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>SO-MPM-LN-CT-588-2026 // INSPECCIÓN CONJUNTA</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>vtp_fernando.munoz</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K101" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M101" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N101" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O101" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P101" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q101" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R101" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S101" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T101" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U101" s="8" t="inlineStr">
-        <is>
-          <t>19/05/2026 14:51:00</t>
-        </is>
-      </c>
-      <c r="V101" s="8" t="inlineStr">
-        <is>
-          <t>19/05/2026 15:19:00</t>
-        </is>
-      </c>
-      <c r="W101" s="8" t="inlineStr">
-        <is>
-          <t>28/05/2026 15:19:00</t>
-        </is>
-      </c>
-      <c r="X101" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z101" s="8" t="inlineStr">
-        <is>
-          <t>2.11 Days</t>
-        </is>
-      </c>
-      <c r="AA101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-21 17:32:17.518 : [1]Nhận xét | Comments || N/A || Se coordinó con TM LIM1 para realizar la inspección conjunta según la fecha propuesta por la Constructora MPM. El encuentro se pactó para ser realizado a las 10AM. </t>
-        </is>
-      </c>
-      <c r="AB101" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC101" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD101" s="8" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AE101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG101" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH101" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI101" s="8" t="inlineStr">
-        <is>
-          <t>Se coordinó con TM LIM1 para realizar la inspección conjunta según la fecha propuesta por la Constructora MPM. El encuentro se pactó para ser realizado a las 10AM.</t>
-        </is>
-      </c>
-      <c r="AJ101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL101" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="102" customHeight="true" ht="12.5">
-      <c r="A102" s="11" t="n">
-        <v>94.0</v>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260515_1348585</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>Oficio Nº 6258-2026-MTC/19.03 // INFORMATIVO</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>vtp_fernando.munoz</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K102" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M102" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N102" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O102" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P102" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q102" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R102" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S102" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T102" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U102" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 16:11:00</t>
-        </is>
-      </c>
-      <c r="V102" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 16:40:00</t>
-        </is>
-      </c>
-      <c r="W102" s="8" t="inlineStr">
-        <is>
-          <t>26/05/2026 16:40:00</t>
-        </is>
-      </c>
-      <c r="X102" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z102" s="8" t="inlineStr">
-        <is>
-          <t>2.07 Days</t>
-        </is>
-      </c>
-      <c r="AA102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-19 17:57:02.798 : [1]Nhận xét | Comments || N/A || Estimados,
-En respuesta a: [SR_VTP_20260515_1348585 / Oficio Nº 6258-2026-MTC]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
-Se adjunta link de documentos: 
-https://drive.google.com/drive/folders/1RfoR1HVDND9HyEPsj6QBsmUm1hFiJsjr?usp=drive_link </t>
-        </is>
-      </c>
-      <c r="AB102" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC102" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD102" s="8" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-      <c r="AE102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG102" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH102" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI102" s="8" t="inlineStr">
-        <is>
-          <t>Estimados,
-En respuesta a: [SR_VTP_20260515_1348585 / Oficio Nº 6258-2026-MTC]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
-Se adjunta link de documentos: 
-https://drive.google.com/drive/folders/1RfoR1HVDND9HyEPsj6QBsmUm1hFiJsjr?usp=drive_link</t>
-        </is>
-      </c>
-      <c r="AJ102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL102" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="103" customHeight="true" ht="12.5">
-      <c r="A103" s="11" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260515_1348481</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>Carta PSR2-F2-CPC-OTR-GEN-GLB-CAR-0068 // INSPECCION CONJUNTA</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>vtp_fernando.munoz</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K103" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L103" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M103" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N103" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O103" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P103" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q103" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R103" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S103" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T103" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U103" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 11:04:00</t>
-        </is>
-      </c>
-      <c r="V103" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 11:33:00</t>
-        </is>
-      </c>
-      <c r="W103" s="8" t="inlineStr">
-        <is>
-          <t>26/05/2026 11:33:00</t>
-        </is>
-      </c>
-      <c r="X103" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z103" s="8" t="inlineStr">
-        <is>
-          <t>1.15 Days</t>
-        </is>
-      </c>
-      <c r="AA103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-18 14:32:45.513 : [1]Nhận xét | Comments || N/A || Se coordinó con TM LIM4 y con representante de MTC, Jorge Fernández, para realizar la inspección conjunta el día viernes 22/05 a las 10.30 am. Queda pendiente la confirmación de la persona que será asignada para acompañar la inspección por parte de LIM4. </t>
-        </is>
-      </c>
-      <c r="AB103" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC103" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD103" s="8" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="AE103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG103" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH103" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI103" s="8" t="inlineStr">
-        <is>
-          <t>Se coordinó con TM LIM4 y con representante de MTC, Jorge Fernández, para realizar la inspección conjunta el día viernes 22/05 a las 10.30 am. Queda pendiente la confirmación de la persona que será asignada para acompañar la inspección por parte de LIM4.</t>
-        </is>
-      </c>
-      <c r="AJ103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL103" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="104" customHeight="true" ht="12.5">
-      <c r="A104" s="11" t="n">
-        <v>96.0</v>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260515_1348600</t>
-        </is>
-      </c>
-      <c r="C104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>Oficio Nº 6257-2026-MTC/19.03 // INFORMATIVO</t>
-        </is>
-      </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>vtp_fernando.munoz</t>
-        </is>
-      </c>
-      <c r="G104" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K104" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M104" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N104" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O104" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P104" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q104" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R104" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S104" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T104" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U104" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 16:13:00</t>
-        </is>
-      </c>
-      <c r="V104" s="8" t="inlineStr">
-        <is>
-          <t>15/05/2026 16:42:00</t>
-        </is>
-      </c>
-      <c r="W104" s="8" t="inlineStr">
-        <is>
-          <t>26/05/2026 16:42:00</t>
-        </is>
-      </c>
-      <c r="X104" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z104" s="8" t="inlineStr">
-        <is>
-          <t>2.96 Days</t>
-        </is>
-      </c>
-      <c r="AA104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 15:16:21.824 : [1]Nhận xét | Comments || N/A || Estimados,
-En respuesta a: [SR_VTP_20260515_1348600 / Oficio Nº 6257-2026-MTC]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
-Se adjunta link de documentos: 
-https://drive.google.com/drive/folders/11pcKOkUdo8NFkLIDfr4BS3PBfgt9SWK3?usp=drive_link </t>
-        </is>
-      </c>
-      <c r="AB104" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC104" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD104" s="8" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-      <c r="AE104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG104" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH104" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI104" s="8" t="inlineStr">
-        <is>
-          <t>Estimados,
-En respuesta a: [SR_VTP_20260515_1348600 / Oficio Nº 6257-2026-MTC]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
-Se adjunta link de documentos: 
-https://drive.google.com/drive/folders/11pcKOkUdo8NFkLIDfr4BS3PBfgt9SWK3?usp=drive_link</t>
-        </is>
-      </c>
-      <c r="AJ104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL104" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="105" customHeight="true" ht="12.5">
-      <c r="A105" s="11" t="n">
-        <v>97.0</v>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>SR_VTP_20260514_1348313</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t>OFICIO N° 6528-2026-MTC/19.03/ INFORMATIVO</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t>vtp_fernando.munoz</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I105" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J105" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K105" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L105" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M105" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N105" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O105" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P105" s="8" t="inlineStr">
-        <is>
-          <t>VTP_CABLE OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Q105" s="8" t="inlineStr">
-        <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
-        </is>
-      </c>
-      <c r="R105" s="8" t="inlineStr">
-        <is>
-          <t>vtp_jesus.gonzales.1</t>
-        </is>
-      </c>
-      <c r="S105" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
-        </is>
-      </c>
-      <c r="T105" s="8" t="inlineStr">
-        <is>
-          <t>Peru (VTP)</t>
-        </is>
-      </c>
-      <c r="U105" s="8" t="inlineStr">
-        <is>
-          <t>14/05/2026 18:25:00</t>
-        </is>
-      </c>
-      <c r="V105" s="8" t="inlineStr">
-        <is>
-          <t>14/05/2026 18:53:00</t>
-        </is>
-      </c>
-      <c r="W105" s="8" t="inlineStr">
-        <is>
-          <t>26/05/2026 08:00:00</t>
-        </is>
-      </c>
-      <c r="X105" s="8" t="inlineStr">
-        <is>
-          <t>22/05/2026 09:19:00</t>
-        </is>
-      </c>
-      <c r="Y105" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z105" s="8" t="inlineStr">
-        <is>
-          <t>1.75 Days</t>
-        </is>
-      </c>
-      <c r="AA105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-18 12:24:13.827 : [1]Nhận xét | Comments || N/A || Estimados,
-En respuesta a: [SR_VTP_20260514_1348313 / OFICIO N° 6528-2026-MTC]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
-Se adjunta link de documentos: 
-https://drive.google.com/drive/folders/1FjgLZL9e8rlG8qG_kvMzV3ytFYVWx41Q?usp=drive_link </t>
-        </is>
-      </c>
-      <c r="AB105" s="8" t="inlineStr">
-        <is>
-          <t>Luồng dịch vụ không có CR VTP | Service Flow Without CR VTP</t>
-        </is>
-      </c>
-      <c r="AC105" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AD105" s="8" t="inlineStr">
-        <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="AE105" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF105" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG105" s="8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="AH105" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AI105" s="8" t="inlineStr">
-        <is>
-          <t>Estimados,
-En respuesta a: [SR_VTP_20260514_1348313 / OFICIO N° 6528-2026-MTC]
-Después de haber realizado una validación con nuestra área y con los encargados de la zona, se pudo verificar que SI contamos con conexión de fibra óptica con tendido aéreo en las zonas de trabajo indicadas, por donde se precisa que se ejecutará su proyecto. Por lo tanto, remitimos la información necesaria para brindar atención a la solicitud.
-Se adjunta link de documentos: 
-https://drive.google.com/drive/folders/1FjgLZL9e8rlG8qG_kvMzV3ytFYVWx41Q?usp=drive_link</t>
-        </is>
-      </c>
       <c r="AJ105" s="8" t="inlineStr">
         <is>
           <t/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260515_1348596</t>
+          <t>SR_VTP_20260515_1348622</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -19267,7 +19267,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>OFICIO N° 6426-2026-MTC/19.03 / INFORMATIVO</t>
+          <t>CARTA N° 000844-2026-INVERMET-GP / CRONOGRAMA Y PRESUPUESTO / DEADLINE: 10/06</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -19277,7 +19277,7 @@
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>vtp_palomino.carlos</t>
+          <t>vtp_bryam.broncano</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
@@ -19352,17 +19352,17 @@
       </c>
       <c r="U106" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 16:28:00</t>
+          <t>15/05/2026 17:11:00</t>
         </is>
       </c>
       <c r="V106" s="8" t="inlineStr">
         <is>
-          <t>15/05/2026 16:56:00</t>
+          <t>15/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 16:56:00</t>
+          <t>26/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="X106" s="8" t="inlineStr">
@@ -19377,12 +19377,12 @@
       </c>
       <c r="Z106" s="8" t="inlineStr">
         <is>
-          <t>0.70 Day</t>
+          <t>3.92 Days</t>
         </is>
       </c>
       <c r="AA106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18 09:13:51.206 : [1]Nhận xét | Comments || N/A || No hay interferencia en la zona indicada </t>
+          <t xml:space="preserve">2026-05-21 15:08:30.179 : [1]Nhận xét | Comments || N/A || se tienen los documentos listos 2026-05-21 15:10:29.59 : [1]Nhận xét | Comments || N/A || https://drive.google.com/drive/folders/126-CzQ8E9JenK6RBGxlCOf7EWtMOeAfG?usp=drive_link </t>
         </is>
       </c>
       <c r="AB106" s="8" t="inlineStr">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="AD106" s="8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AE106" s="8" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="AI106" s="8" t="inlineStr">
         <is>
-          <t>No hay interferencia en la zona indicada</t>
+          <t>se tienen los documentos listos,https://drive.google.com/drive/folders/126-CzQ8E9JenK6RBGxlCOf7EWtMOeAfG?usp=drive_link</t>
         </is>
       </c>
       <c r="AJ106" s="8" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260513_1347920</t>
+          <t>SR_VTP_20260507_1346386</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>3ER UPDATE // Oficio N°1988-2026-MTC/20.11 // NOTIFICACIÓN- RETIRO DE POSTES EN DERECHO DE VIA // DEADLINE 15/5/2026</t>
+          <t>UPDATE // OFICIO N° 4196-2026-MTC/19.03 // REITERATIVO DE PRESUPUESTO Y CRONOGRAMA - PROYECTO MOCCUPE - DEADLINE 12/5/2026</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -20607,7 +20607,7 @@
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>vtp_fernando.munoz</t>
+          <t>vtp_bryam.broncano</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N113" s="8" t="inlineStr">
@@ -20682,17 +20682,17 @@
       </c>
       <c r="U113" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 14:14:00</t>
+          <t>07/05/2026 12:52:00</t>
         </is>
       </c>
       <c r="V113" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 14:42:00</t>
+          <t>07/05/2026 13:20:00</t>
         </is>
       </c>
       <c r="W113" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 14:42:00</t>
+          <t>12/05/2026 13:20:00</t>
         </is>
       </c>
       <c r="X113" s="8" t="inlineStr">
@@ -20707,13 +20707,13 @@
       </c>
       <c r="Z113" s="8" t="inlineStr">
         <is>
-          <t>4.80 Days</t>
+          <t>8.91 Days</t>
         </is>
       </c>
       <c r="AA113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18 12:46:16.308 : [1]Nhận xét | Comments || N/A || Se conversó con el TM de la zona, el cula indica que ya se realizó la inspección, y que estará sacando la cotización para los trabajos. Asímismo, 
-el cronograma de trabajos se estará realizando durante la semana. </t>
+          <t xml:space="preserve">2026-05-11 14:56:40.973 : [1]Nhận xét | Comments || N/A || se ha solicitado cotizacion de partner al TM LAM Carlos Tuñoque desde el 21/04, menciono que se tenia para el viernes 8, pero sigue sin dar respuesta sobre la cotizacion 2026-05-12 19:01:00.281 : [1]Nhận xét | Comments || N/A || TM LAM Paso cotizacion el dia de hoy 12/05/26 2026-05-12 19:23:03.675 : [1]Nhận xét | Comments || N/A || Se converso con el ingeniero del mtc para poder entregar durante la semana 2026-05-13 14:03:15.112 : [1]Nhận xét | Comments || N/A || por solictud de subdirector de transmision se esta generando un reporte para  subir a voffice para que puedan firmar (TM, VICE BRANCH, TL CABLE, VICE TX, DIRECTOR TX, DIRECTOR TC, Y CTO) 2026-05-20 10:38:20.215 : [1]Nhận xét | Comments || N/A || se ha vuelto a subir reporte a voffice por tercera vez 2026-05-20 10:39:19.957 : [1]Nhận xét | Comments || N/A || por parte de transmision se tiene los documentos listo
+https://drive.google.com/drive/folders/1scnmXxlNtOooB7Kd1ueK4zV0eoUi_NRp?usp=drive_link </t>
         </is>
       </c>
       <c r="AB113" s="8" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AD113" s="8" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AE113" s="8" t="inlineStr">
@@ -20753,8 +20753,8 @@
       </c>
       <c r="AI113" s="8" t="inlineStr">
         <is>
-          <t>Se conversó con el TM de la zona, el cula indica que ya se realizó la inspección, y que estará sacando la cotización para los trabajos. Asímismo, 
-el cronograma de trabajos se estará realizando durante la semana.</t>
+          <t>se ha solicitado cotizacion de partner al TM LAM Carlos Tuñoque desde el 21/04, menciono que se tenia para el viernes 8, pero sigue sin dar respuesta sobre la cotizacion,TM LAM Paso cotizacion el dia de hoy 12/05/26,Se converso con el ingeniero del mtc para poder entregar durante la semana,por solictud de subdirector de transmision se esta generando un reporte para  subir a voffice para que puedan firmar (TM, VICE BRANCH, TL CABLE, VICE TX, DIRECTOR TX, DIRECTOR TC, Y CTO),se ha vuelto a subir reporte a voffice por tercera vez,por parte de transmision se tiene los documentos listo
+https://drive.google.com/drive/folders/1scnmXxlNtOooB7Kd1ueK4zV0eoUi_NRp?usp=drive_link</t>
         </is>
       </c>
       <c r="AJ113" s="8" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346386</t>
+          <t>SR_VTP_20260513_1347920</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -20789,7 +20789,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>UPDATE // OFICIO N° 4196-2026-MTC/19.03 // REITERATIVO DE PRESUPUESTO Y CRONOGRAMA - PROYECTO MOCCUPE - DEADLINE 12/5/2026</t>
+          <t>3ER UPDATE // Oficio N°1988-2026-MTC/20.11 // NOTIFICACIÓN- RETIRO DE POSTES EN DERECHO DE VIA // DEADLINE 15/5/2026</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>vtp_bryam.broncano</t>
+          <t>vtp_fernando.munoz</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
@@ -20834,14 +20834,14 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N114" s="8" t="inlineStr">
+        <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="N114" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
       <c r="O114" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
@@ -20874,17 +20874,17 @@
       </c>
       <c r="U114" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 12:52:00</t>
+          <t>13/05/2026 14:14:00</t>
         </is>
       </c>
       <c r="V114" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 13:20:00</t>
+          <t>13/05/2026 14:42:00</t>
         </is>
       </c>
       <c r="W114" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 13:20:00</t>
+          <t>18/05/2026 14:42:00</t>
         </is>
       </c>
       <c r="X114" s="8" t="inlineStr">
@@ -20899,13 +20899,13 @@
       </c>
       <c r="Z114" s="8" t="inlineStr">
         <is>
-          <t>8.91 Days</t>
+          <t>4.80 Days</t>
         </is>
       </c>
       <c r="AA114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-11 14:56:40.973 : [1]Nhận xét | Comments || N/A || se ha solicitado cotizacion de partner al TM LAM Carlos Tuñoque desde el 21/04, menciono que se tenia para el viernes 8, pero sigue sin dar respuesta sobre la cotizacion 2026-05-12 19:01:00.281 : [1]Nhận xét | Comments || N/A || TM LAM Paso cotizacion el dia de hoy 12/05/26 2026-05-12 19:23:03.675 : [1]Nhận xét | Comments || N/A || Se converso con el ingeniero del mtc para poder entregar durante la semana 2026-05-13 14:03:15.112 : [1]Nhận xét | Comments || N/A || por solictud de subdirector de transmision se esta generando un reporte para  subir a voffice para que puedan firmar (TM, VICE BRANCH, TL CABLE, VICE TX, DIRECTOR TX, DIRECTOR TC, Y CTO) 2026-05-20 10:38:20.215 : [1]Nhận xét | Comments || N/A || se ha vuelto a subir reporte a voffice por tercera vez 2026-05-20 10:39:19.957 : [1]Nhận xét | Comments || N/A || por parte de transmision se tiene los documentos listo
-https://drive.google.com/drive/folders/1scnmXxlNtOooB7Kd1ueK4zV0eoUi_NRp?usp=drive_link </t>
+          <t xml:space="preserve">2026-05-18 12:46:16.308 : [1]Nhận xét | Comments || N/A || Se conversó con el TM de la zona, el cula indica que ya se realizó la inspección, y que estará sacando la cotización para los trabajos. Asímismo, 
+el cronograma de trabajos se estará realizando durante la semana. </t>
         </is>
       </c>
       <c r="AB114" s="8" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="AD114" s="8" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AE114" s="8" t="inlineStr">
@@ -20945,8 +20945,8 @@
       </c>
       <c r="AI114" s="8" t="inlineStr">
         <is>
-          <t>se ha solicitado cotizacion de partner al TM LAM Carlos Tuñoque desde el 21/04, menciono que se tenia para el viernes 8, pero sigue sin dar respuesta sobre la cotizacion,TM LAM Paso cotizacion el dia de hoy 12/05/26,Se converso con el ingeniero del mtc para poder entregar durante la semana,por solictud de subdirector de transmision se esta generando un reporte para  subir a voffice para que puedan firmar (TM, VICE BRANCH, TL CABLE, VICE TX, DIRECTOR TX, DIRECTOR TC, Y CTO),se ha vuelto a subir reporte a voffice por tercera vez,por parte de transmision se tiene los documentos listo
-https://drive.google.com/drive/folders/1scnmXxlNtOooB7Kd1ueK4zV0eoUi_NRp?usp=drive_link</t>
+          <t>Se conversó con el TM de la zona, el cula indica que ya se realizó la inspección, y que estará sacando la cotización para los trabajos. Asímismo, 
+el cronograma de trabajos se estará realizando durante la semana.</t>
         </is>
       </c>
       <c r="AJ114" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 5/26/26, 4:44 PM</t>
+          <t>Date Export: 5/26/26, 4:43 PM</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 5/27/26, 8:18 AM</t>
+          <t>Date Export: 5/27/26, 8:17 AM</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 5/28/26, 4:41 PM</t>
+          <t>Date Export: 5/28/26, 4:40 PM</t>
         </is>
       </c>
     </row>

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 5/29/26, 8:29 AM</t>
+          <t>Date Export: 5/29/26, 8:30 AM</t>
         </is>
       </c>
     </row>

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 5/30/26, 7:58 PM</t>
+          <t>Date Export: 6/1/26, 8:27 AM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="M49" s="8" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="M53" s="8" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="M59" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="M67" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="M77" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N77" s="8" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N78" s="8" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="M87" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N87" s="8" t="inlineStr">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N94" s="8" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N114" s="8" t="inlineStr">
@@ -26152,7 +26152,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N142" s="8" t="inlineStr">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N158" s="8" t="inlineStr">
@@ -29992,7 +29992,7 @@
       </c>
       <c r="M162" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N162" s="8" t="inlineStr">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N182" s="8" t="inlineStr">
@@ -35400,7 +35400,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N190" s="8" t="inlineStr">
@@ -35806,7 +35806,7 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N192" s="8" t="inlineStr">
@@ -37708,7 +37708,7 @@
       </c>
       <c r="M202" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N202" s="8" t="inlineStr">
@@ -57188,7 +57188,7 @@
       </c>
       <c r="M304" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N304" s="8" t="inlineStr">
@@ -61778,7 +61778,7 @@
       </c>
       <c r="M328" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N328" s="8" t="inlineStr">
@@ -61968,7 +61968,7 @@
       </c>
       <c r="M329" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N329" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/1/26, 11:10 AM</t>
+          <t>Date Export: 6/1/26, 11:09 AM</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/1/26, 6:49 PM</t>
+          <t>Date Export: 6/1/26, 7:32 PM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="O21" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>23.93</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="M57" s="8" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="M58" s="8" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="M59" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="M60" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/2/26, 7:33 PM</t>
+          <t>Date Export: 6/3/26, 8:29 AM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="M58" s="8" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="M59" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/3/26, 12:19 PM</t>
+          <t>Date Export: 6/3/26, 4:39 PM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353748</t>
+          <t>SR_VTP_20260601_1353742</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>SME_LINEA DE VISTA_VALIDACION DE CAPACIDAD_ MW 01.06 | 9 NEW VALIDATION</t>
+          <t>CARTA N° 000964-2026-INVERMET-GP / REITERATIVO DE CRONOGRAMA Y PRESUPUESTO</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t/>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -1947,22 +1947,22 @@
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q15" s="8" t="inlineStr">
         <is>
-          <t>Design/Redesign Corp MW links</t>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>vtp_edgar.arteaga</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 18:43:00</t>
+          <t>01/06/2026 18:31:00</t>
         </is>
       </c>
       <c r="V15" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 19:11:00</t>
+          <t>01/06/2026 18:47:00</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>05/06/2026 08:00:00</t>
+          <t>11/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X15" s="8" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AG15" s="8" t="inlineStr">
         <is>
-          <t>*</t>
+          <t/>
         </is>
       </c>
       <c r="AH15" s="8" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353742</t>
+          <t>SR_VTP_20260601_1353642</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>CARTA N° 000964-2026-INVERMET-GP / REITERATIVO DE CRONOGRAMA Y PRESUPUESTO</t>
+          <t>SME_SOLAR LED_CONFIGURACION ENLACE MW_30 mbps</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_vanessa.balbuena</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_MICROWAVE</t>
         </is>
       </c>
       <c r="Q16" s="8" t="inlineStr">
         <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
+          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>vtp_edgar.arteaga</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -2162,17 +2162,17 @@
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 18:31:00</t>
+          <t>01/06/2026 16:07:00</t>
         </is>
       </c>
       <c r="V16" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 18:47:00</t>
+          <t>01/06/2026 16:37:00</t>
         </is>
       </c>
       <c r="W16" s="8" t="inlineStr">
         <is>
-          <t>11/06/2026 08:00:00</t>
+          <t>08/06/2026 16:37:00</t>
         </is>
       </c>
       <c r="X16" s="8" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AG16" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*</t>
         </is>
       </c>
       <c r="AH16" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353642</t>
+          <t>SR_VTP_20260601_1353668</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>SME_SOLAR LED_CONFIGURACION ENLACE MW_30 mbps</t>
+          <t>LAL0150-LAL0393</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>vtp_vanessa.balbuena</t>
+          <t/>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2332,17 +2332,17 @@
       </c>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
+          <t>MW_RESTRUCTURE NETWORK</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>vtp_edgar.arteaga</t>
+          <t>vtp_kathy.valle</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -2352,17 +2352,17 @@
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 16:07:00</t>
+          <t>01/06/2026 16:06:00</t>
         </is>
       </c>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 16:37:00</t>
+          <t>01/06/2026 17:30:00</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 16:37:00</t>
+          <t>08/06/2026 17:30:00</t>
         </is>
       </c>
       <c r="X17" s="8" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="AG17" s="8" t="inlineStr">
         <is>
-          <t>*</t>
+          <t/>
         </is>
       </c>
       <c r="AH17" s="8" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353668</t>
+          <t>SR_VTP_20260601_1353536</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>LAL0150-LAL0393</t>
+          <t>Configuracion enlace plan PODER JUDICIAL</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_kelly.alvarado</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>MW_RESTRUCTURE NETWORK</t>
+          <t>MW_NEW INTEGRATION METRO NETWORK</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>vtp_kathy.valle</t>
+          <t>vtp_muchaypina.anthony</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -2542,17 +2542,17 @@
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 16:06:00</t>
+          <t>01/06/2026 12:59:00</t>
         </is>
       </c>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 17:30:00</t>
+          <t>01/06/2026 13:10:00</t>
         </is>
       </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 17:30:00</t>
+          <t>08/06/2026 13:10:00</t>
         </is>
       </c>
       <c r="X18" s="8" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353536</t>
+          <t>SR_VTP_20260601_1353479</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Configuracion enlace plan PODER JUDICIAL</t>
+          <t>RE: TECHNICAL REQUIREMENT - MLQ3 - Q4 CORP : CLAMP  COMPLIANCE</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>vtp_kelly.alvarado</t>
+          <t/>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>VTP_MICROWAVE</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>MW_NEW INTEGRATION METRO NETWORK</t>
+          <t>Technical review for biddings</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>vtp_muchaypina.anthony</t>
+          <t>vtp_judith.araujo</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 12:59:00</t>
+          <t>01/06/2026 10:39:00</t>
         </is>
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 13:10:00</t>
+          <t>01/06/2026 11:07:00</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 13:10:00</t>
+          <t>10/06/2026 11:07:00</t>
         </is>
       </c>
       <c r="X19" s="8" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353479</t>
+          <t>SR_VTP_20260528_1352447</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>RE: TECHNICAL REQUIREMENT - MLQ3 - Q4 CORP : CLAMP  COMPLIANCE</t>
+          <t>Carta N° 182247-CG-060 // PRESUPUESTO Y CRONOGRAMA // MEJORAMIENTO DE LA CARRETERA COCHAPATA (TUNEL TAYTAMAYO) // HUANUCO - ANCASH // deadline 10/06/2026</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_bryam.broncano</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -2897,22 +2897,22 @@
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>Technical review for biddings</t>
+          <t>Budget Project design for fiber relocation for MTC projects</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>vtp_judith.araujo</t>
+          <t>vtp_nayeli.casas</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2922,22 +2922,22 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 10:39:00</t>
+          <t>28/05/2026 17:56:00</t>
         </is>
       </c>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 11:07:00</t>
+          <t>28/05/2026 18:19:00</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>10/06/2026 11:07:00</t>
+          <t>19/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>01/06/2026 10:35:00</t>
         </is>
       </c>
       <c r="Y20" s="8" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260528_1352447</t>
+          <t>SR_VTP_20260601_1353478</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Carta N° 182247-CG-060 // PRESUPUESTO Y CRONOGRAMA // MEJORAMIENTO DE LA CARRETERA COCHAPATA (TUNEL TAYTAMAYO) // HUANUCO - ANCASH // deadline 10/06/2026</t>
+          <t>TECHNICAL EVALUATION: ML Q3 - Q4 CORP - MW</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>vtp_bryam.broncano</t>
+          <t/>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3087,22 +3087,22 @@
       </c>
       <c r="P21" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q21" s="8" t="inlineStr">
         <is>
-          <t>Budget Project design for fiber relocation for MTC projects</t>
+          <t>Technical review for biddings</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>vtp_nayeli.casas</t>
+          <t>vtp_alisson.astudillo</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -3112,22 +3112,22 @@
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 17:56:00</t>
+          <t>01/06/2026 10:34:00</t>
         </is>
       </c>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 18:19:00</t>
+          <t>01/06/2026 11:03:00</t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00:00</t>
+          <t>10/06/2026 11:03:00</t>
         </is>
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 10:35:00</t>
+          <t/>
         </is>
       </c>
       <c r="Y21" s="8" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353478</t>
+          <t>SR_VTP_20260601_1353450</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>TECHNICAL EVALUATION: ML Q3 - Q4 CORP - MW</t>
+          <t>TECHNICAL EVALUATION: ML Q3 - Q4 CORP - MUFAS ODF</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -3302,17 +3302,17 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 10:34:00</t>
+          <t>01/06/2026 10:32:00</t>
         </is>
       </c>
       <c r="V22" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 11:03:00</t>
+          <t>01/06/2026 11:01:00</t>
         </is>
       </c>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>10/06/2026 11:03:00</t>
+          <t>10/06/2026 11:01:00</t>
         </is>
       </c>
       <c r="X22" s="8" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353450</t>
+          <t>SR_VTP_20260529_1352992</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>TECHNICAL EVALUATION: ML Q3 - Q4 CORP - MUFAS ODF</t>
+          <t>TECHNICAL EVALUATION:  MLQ3 - Q4 CORP 052026.VTPr-Plastic Wedge Clamp</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>vtp_alisson.astudillo</t>
+          <t>vtp_judith.araujo</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 10:32:00</t>
+          <t>29/05/2026 18:59:00</t>
         </is>
       </c>
       <c r="V23" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 11:01:00</t>
+          <t>29/05/2026 19:28:00</t>
         </is>
       </c>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>10/06/2026 11:01:00</t>
+          <t>10/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X23" s="8" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352992</t>
+          <t>SR_VTP_20260529_1352989</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>TECHNICAL EVALUATION:  MLQ3 - Q4 CORP 052026.VTPr-Plastic Wedge Clamp</t>
+          <t>New cases congested  LAL0299-LAL0333</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -3612,69 +3612,69 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>VTP_MICROWAVE</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>MW_RESTRUCTURE NETWORK</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>vtp_kathy.valle</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
+        <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t>Technical review for biddings</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t>vtp_judith.araujo</t>
-        </is>
-      </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
-        </is>
-      </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
           <t>Peru (VTP)</t>
@@ -3682,17 +3682,17 @@
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 18:59:00</t>
+          <t>29/05/2026 18:36:00</t>
         </is>
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 19:28:00</t>
+          <t>29/05/2026 19:05:00</t>
         </is>
       </c>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>10/06/2026 08:00:00</t>
+          <t>08/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X24" s="8" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352989</t>
+          <t>SR_VTP_20260529_1352971</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>New cases congested  LAL0299-LAL0333</t>
+          <t>KCS Testing at MInka WH for IMP-3028 PO_02-01/2026/F/VTPr-2PT/FERRETERIA AMA</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -3847,22 +3847,22 @@
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>VTP_MICROWAVE</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>MW_RESTRUCTURE NETWORK</t>
+          <t>KCS for new goods of Transmission</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>vtp_kathy.valle</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 18:36:00</t>
+          <t>29/05/2026 17:20:00</t>
         </is>
       </c>
       <c r="V25" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 19:05:00</t>
+          <t>29/05/2026 17:48:00</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352971</t>
+          <t>SR_VTP_20260529_1352904</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for IMP-3028 PO_02-01/2026/F/VTPr-2PT/FERRETERIA AMA</t>
+          <t>KCS Testing at MInka WH for IMP-3007  01/2026/VTPr-THOAIANH/OPTICAL ACCESSORIES ML 2026</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -4062,17 +4062,17 @@
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:20:00</t>
+          <t>29/05/2026 15:21:00</t>
         </is>
       </c>
       <c r="V26" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:48:00</t>
+          <t>29/05/2026 15:49:00</t>
         </is>
       </c>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 08:00:00</t>
+          <t>05/06/2026 15:49:00</t>
         </is>
       </c>
       <c r="X26" s="8" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352904</t>
+          <t>SR_VTP_20260529_1352682</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for IMP-3007  01/2026/VTPr-THOAIANH/OPTICAL ACCESSORIES ML 2026</t>
+          <t>OFICIO N° 7531-2026-MTC/19.03 / INSPECCIÓN CONJUNTA</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t/>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
@@ -4227,22 +4227,22 @@
       </c>
       <c r="P27" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>KCS for new goods of Transmission</t>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -4252,17 +4252,17 @@
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 15:21:00</t>
+          <t>29/05/2026 09:15:00</t>
         </is>
       </c>
       <c r="V27" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 15:49:00</t>
+          <t>29/05/2026 09:44:00</t>
         </is>
       </c>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>05/06/2026 15:49:00</t>
+          <t>09/06/2026 09:44:00</t>
         </is>
       </c>
       <c r="X27" s="8" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352682</t>
+          <t>SR_VTP_20260528_1352463</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>OFICIO N° 7531-2026-MTC/19.03 / INSPECCIÓN CONJUNTA</t>
+          <t>Se solicita fecha de inicio de inicio de trabajo de: CRONOGRAMA GENERAL PARA LA LIBERACION DE LA INTERFERENCIA CON EL PROYECTO “REHABILITACIÓN Y MEJORAMIENTO DE LA CARRETERA EMP. RUTA 18A (PTE. RANCHO) - CHAGLLA - RUMICHACA. TRAMO I”</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 09:15:00</t>
+          <t>28/05/2026 17:36:00</t>
         </is>
       </c>
       <c r="V28" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 09:44:00</t>
+          <t>28/05/2026 18:03:00</t>
         </is>
       </c>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44:00</t>
+          <t>09/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X28" s="8" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260528_1352463</t>
+          <t>SR_VTP_20260522_1350563</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Se solicita fecha de inicio de inicio de trabajo de: CRONOGRAMA GENERAL PARA LA LIBERACION DE LA INTERFERENCIA CON EL PROYECTO “REHABILITACIÓN Y MEJORAMIENTO DE LA CARRETERA EMP. RUTA 18A (PTE. RANCHO) - CHAGLLA - RUMICHACA. TRAMO I”</t>
+          <t>PROYECTO MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
+          <t>Design transmission for corporate customers (&gt; 500 Link)</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>vtp_gerardo.alvarado</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 17:36:00</t>
+          <t>22/05/2026 16:42:00</t>
         </is>
       </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 18:03:00</t>
+          <t>22/05/2026 17:11:00</t>
         </is>
       </c>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>09/06/2026 08:00:00</t>
+          <t>06/07/2026 17:11:00</t>
         </is>
       </c>
       <c r="X29" s="8" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260522_1350563</t>
+          <t>SR_VTP_20260518_1349100</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>PROYECTO MINISTERIO PUBLICO</t>
+          <t>OXI_Ucayali Project - SMART CITY &amp; DARK FIBER &amp; INTERNET SERVICE - 101 sites</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 500 Link)</t>
+          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>vtp_gerardo.alvarado</t>
+          <t>vtp_julio.inga</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -4822,17 +4822,17 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 16:42:00</t>
+          <t>18/05/2026 11:34:00</t>
         </is>
       </c>
       <c r="V30" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 17:11:00</t>
+          <t>18/05/2026 12:03:00</t>
         </is>
       </c>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>06/07/2026 17:11:00</t>
+          <t>08/06/2026 12:03:00</t>
         </is>
       </c>
       <c r="X30" s="8" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260518_1349100</t>
+          <t>SR_VTP_20260525_1351186</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -4927,17 +4927,17 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>OXI_Ucayali Project - SMART CITY &amp; DARK FIBER &amp; INTERNET SERVICE - 101 sites</t>
+          <t>CAJ0222-CAJ2004_1  Recover monitor of link 1, Upgrade MW by configuration to 512QAM,  *</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
+          <t>Design/Redesign Metro MW links</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>vtp_julio.inga</t>
+          <t>vtp_kathy.valle</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -5012,22 +5012,22 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 11:34:00</t>
+          <t>25/05/2026 15:48:00</t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 12:03:00</t>
+          <t>25/05/2026 16:16:00</t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 12:03:00</t>
+          <t>28/05/2026 16:16:00</t>
         </is>
       </c>
       <c r="X31" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>26/05/2026 12:46:00</t>
         </is>
       </c>
       <c r="Y31" s="8" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AA31" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">2026-05-26 12:47:09.621 : [1]Nhận xét | Comments || N/A || Incorrect unit </t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AI31" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>Incorrect unit</t>
         </is>
       </c>
       <c r="AJ31" s="8" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1351186</t>
+          <t>SR_VTP_20260518_1349058</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>CAJ0222-CAJ2004_1  Recover monitor of link 1, Upgrade MW by configuration to 512QAM,  *</t>
+          <t>FACTIBILIDAD MINEDU 1K</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
@@ -5182,17 +5182,17 @@
       </c>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>Design/Redesign Metro MW links</t>
+          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>vtp_kathy.valle</t>
+          <t>vtp_thangnq1</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -5202,22 +5202,22 @@
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 15:48:00</t>
+          <t>18/05/2026 10:46:00</t>
         </is>
       </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 16:16:00</t>
+          <t>18/05/2026 11:15:00</t>
         </is>
       </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 16:16:00</t>
+          <t>08/06/2026 11:15:00</t>
         </is>
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 12:46:00</t>
+          <t>18/05/2026 14:31:00</t>
         </is>
       </c>
       <c r="Y32" s="8" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="AA32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26 12:47:09.621 : [1]Nhận xét | Comments || N/A || Incorrect unit </t>
+          <t xml:space="preserve">2026-05-18 14:31:19.315 : [1]Nhận xét | Comments || N/A || Elegir las categoria &gt; 500 links </t>
         </is>
       </c>
       <c r="AB32" s="8" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AI32" s="8" t="inlineStr">
         <is>
-          <t>Incorrect unit</t>
+          <t>Elegir las categoria &gt; 500 links</t>
         </is>
       </c>
       <c r="AJ32" s="8" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260518_1349058</t>
+          <t>SR_VTP_20260511_1347286</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>FACTIBILIDAD MINEDU 1K</t>
+          <t>KCS Testing at MInka WH for IMP-2987 03/2026/VTPr-VMC/CABLE 24FO-ML2026</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -5367,22 +5367,22 @@
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_DWDM</t>
         </is>
       </c>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
+          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>vtp_thangnq1</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -5392,22 +5392,22 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 10:46:00</t>
+          <t>11/05/2026 17:56:00</t>
         </is>
       </c>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 11:15:00</t>
+          <t>11/05/2026 18:23:00</t>
         </is>
       </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 11:15:00</t>
+          <t>18/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X33" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 14:31:00</t>
+          <t>12/05/2026 11:17:00</t>
         </is>
       </c>
       <c r="Y33" s="8" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="AA33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18 14:31:19.315 : [1]Nhận xét | Comments || N/A || Elegir las categoria &gt; 500 links </t>
+          <t xml:space="preserve">2026-05-12 11:17:09.237 : [1]Nhận xét | Comments || N/A || Wrong division </t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AI33" s="8" t="inlineStr">
         <is>
-          <t>Elegir las categoria &gt; 500 links</t>
+          <t>Wrong division</t>
         </is>
       </c>
       <c r="AJ33" s="8" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260511_1347286</t>
+          <t>SR_VTP_20260508_1346759</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for IMP-2987 03/2026/VTPr-VMC/CABLE 24FO-ML2026</t>
+          <t>KCS Testing at MInka WH for 01/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -5582,22 +5582,22 @@
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>11/05/2026 17:56:00</t>
+          <t>08/05/2026 14:39:00</t>
         </is>
       </c>
       <c r="V34" s="8" t="inlineStr">
         <is>
-          <t>11/05/2026 18:23:00</t>
+          <t>08/05/2026 15:04:00</t>
         </is>
       </c>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 08:00:00</t>
+          <t>14/05/2026 15:04:00</t>
         </is>
       </c>
       <c r="X34" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 11:17:00</t>
+          <t>08/05/2026 18:12:00</t>
         </is>
       </c>
       <c r="Y34" s="8" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AA34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-12 11:17:09.237 : [1]Nhận xét | Comments || N/A || Wrong division </t>
+          <t xml:space="preserve">2026-05-08 18:12:40.243 : [1]Nhận xét | Comments || N/A || Which plan? Not related to TRA. Detail that, </t>
         </is>
       </c>
       <c r="AB34" s="8" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AI34" s="8" t="inlineStr">
         <is>
-          <t>Wrong division</t>
+          <t>Which plan? Not related to TRA. Detail that,</t>
         </is>
       </c>
       <c r="AJ34" s="8" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260508_1346759</t>
+          <t>SR_VTP_20260507_1346521</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 01/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
+          <t>DISEÑO LAST MILLE -   MINEDU WAN</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -5747,22 +5747,22 @@
       </c>
       <c r="P35" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
+          <t>Design Transmission for new BTS "Less than 80"</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_ronald.jimenez</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -5772,22 +5772,22 @@
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 14:39:00</t>
+          <t>07/05/2026 17:47:00</t>
         </is>
       </c>
       <c r="V35" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 15:04:00</t>
+          <t>07/05/2026 18:10:00</t>
         </is>
       </c>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 15:04:00</t>
+          <t>13/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X35" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 18:12:00</t>
+          <t>08/05/2026 12:43:00</t>
         </is>
       </c>
       <c r="Y35" s="8" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AA35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 18:12:40.243 : [1]Nhận xét | Comments || N/A || Which plan? Not related to TRA. Detail that, </t>
+          <t xml:space="preserve">2026-05-08 12:43:00.713 : [1]Nhận xét | Comments || N/A || Cambiar de categoria a diseño &lt; 50 enlaces </t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AI35" s="8" t="inlineStr">
         <is>
-          <t>Which plan? Not related to TRA. Detail that,</t>
+          <t>Cambiar de categoria a diseño &lt; 50 enlaces</t>
         </is>
       </c>
       <c r="AJ35" s="8" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346521</t>
+          <t>SR_VTP_20260507_1346500</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE -   MINEDU WAN</t>
+          <t>KCS Testing at MInka WH for 03/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
@@ -5937,22 +5937,22 @@
       </c>
       <c r="P36" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_DWDM</t>
         </is>
       </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "Less than 80"</t>
+          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
         </is>
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>vtp_ronald.jimenez</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -5962,22 +5962,22 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:47:00</t>
+          <t>07/05/2026 16:51:00</t>
         </is>
       </c>
       <c r="V36" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 18:10:00</t>
+          <t>07/05/2026 17:20:00</t>
         </is>
       </c>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 08:00:00</t>
+          <t>13/05/2026 17:20:00</t>
         </is>
       </c>
       <c r="X36" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 12:43:00</t>
+          <t>08/05/2026 11:05:00</t>
         </is>
       </c>
       <c r="Y36" s="8" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AA36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 12:43:00.713 : [1]Nhận xét | Comments || N/A || Cambiar de categoria a diseño &lt; 50 enlaces </t>
+          <t xml:space="preserve">2026-05-08 11:05:45.017 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
         </is>
       </c>
       <c r="AB36" s="8" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="AI36" s="8" t="inlineStr">
         <is>
-          <t>Cambiar de categoria a diseño &lt; 50 enlaces</t>
+          <t>If requested without TRA confirmation of quality then that team responsible,</t>
         </is>
       </c>
       <c r="AJ36" s="8" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346500</t>
+          <t>SR_VTP_20260507_1346501</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 03/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
+          <t>KCS Testing at MInka WH for 02/2026/VTPr-GFORESTAL/ESSALUD/POLES</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 16:51:00</t>
+          <t>07/05/2026 16:59:00</t>
         </is>
       </c>
       <c r="V37" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:20:00</t>
+          <t>07/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="W37" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 17:20:00</t>
+          <t>13/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="X37" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 11:05:00</t>
+          <t>08/05/2026 11:02:00</t>
         </is>
       </c>
       <c r="Y37" s="8" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="AA37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 11:05:45.017 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
+          <t xml:space="preserve">2026-05-08 11:02:52.613 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
         </is>
       </c>
       <c r="AB37" s="8" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346501</t>
+          <t>SR_VTP_20260507_1346469</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 02/2026/VTPr-GFORESTAL/ESSALUD/POLES</t>
+          <t>DISEÑO LAST MILLE - HNHU (Hospital Nacional Hipólito Unanue)</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
@@ -6317,22 +6317,22 @@
       </c>
       <c r="P38" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
+          <t>Design Transmission for new BTS "Less than 80"</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_ronald.jimenez</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -6342,22 +6342,22 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 16:59:00</t>
+          <t>07/05/2026 15:40:00</t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:28:00</t>
+          <t>07/05/2026 15:57:00</t>
         </is>
       </c>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 17:28:00</t>
+          <t>12/05/2026 15:57:00</t>
         </is>
       </c>
       <c r="X38" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 11:02:00</t>
+          <t>07/05/2026 18:08:00</t>
         </is>
       </c>
       <c r="Y38" s="8" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="AA38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 11:02:52.613 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
+          <t xml:space="preserve">2026-05-07 18:04:17.794 : [1]Nhận xét | Comments || N/A || Pueder ser diseñado por Preventa, son 2 enlaces </t>
         </is>
       </c>
       <c r="AB38" s="8" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AI38" s="8" t="inlineStr">
         <is>
-          <t>If requested without TRA confirmation of quality then that team responsible,</t>
+          <t>Pueder ser diseñado por Preventa, son 2 enlaces</t>
         </is>
       </c>
       <c r="AJ38" s="8" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346469</t>
+          <t>SR_VTP_20260505_1345858</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE - HNHU (Hospital Nacional Hipólito Unanue)</t>
+          <t>DISEÑO LAST MILLE - INO -  2 LINKS</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -6532,22 +6532,22 @@
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 15:40:00</t>
+          <t>05/05/2026 16:59:00</t>
         </is>
       </c>
       <c r="V39" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 15:57:00</t>
+          <t>05/05/2026 17:22:00</t>
         </is>
       </c>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 15:57:00</t>
+          <t>08/05/2026 17:22:00</t>
         </is>
       </c>
       <c r="X39" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 18:08:00</t>
+          <t>06/05/2026 16:48:00</t>
         </is>
       </c>
       <c r="Y39" s="8" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AA39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-07 18:04:17.794 : [1]Nhận xét | Comments || N/A || Pueder ser diseñado por Preventa, son 2 enlaces </t>
+          <t xml:space="preserve">2026-05-06 16:48:30.879 : [1]Nhận xét | Comments || N/A || 2 enlaces, lo puede diseñar Preventa </t>
         </is>
       </c>
       <c r="AB39" s="8" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="AI39" s="8" t="inlineStr">
         <is>
-          <t>Pueder ser diseñado por Preventa, son 2 enlaces</t>
+          <t>2 enlaces, lo puede diseñar Preventa</t>
         </is>
       </c>
       <c r="AJ39" s="8" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260505_1345858</t>
+          <t>SR_VTP_20260504_1345314</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE - INO -  2 LINKS</t>
+          <t>Carta No. 000190-2026/PROINVERSION/DPP/VI.34 // INFORMATIVO</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_fernando.munoz</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -6697,22 +6697,22 @@
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "Less than 80"</t>
+          <t>Review letters of interference/notification/information about BITEL optical cable</t>
         </is>
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>vtp_ronald.jimenez</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -6722,22 +6722,22 @@
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
-          <t>05/05/2026 16:59:00</t>
+          <t>04/05/2026 11:24:00</t>
         </is>
       </c>
       <c r="V40" s="8" t="inlineStr">
         <is>
-          <t>05/05/2026 17:22:00</t>
+          <t>04/05/2026 11:53:00</t>
         </is>
       </c>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 17:22:00</t>
+          <t>07/05/2026 11:53:00</t>
         </is>
       </c>
       <c r="X40" s="8" t="inlineStr">
         <is>
-          <t>06/05/2026 16:48:00</t>
+          <t>04/05/2026 11:43:00</t>
         </is>
       </c>
       <c r="Y40" s="8" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AA40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-06 16:48:30.879 : [1]Nhận xét | Comments || N/A || 2 enlaces, lo puede diseñar Preventa </t>
+          <t xml:space="preserve">2026-05-04 11:43:26.02 : [1]Nhận xét | Comments || N/A || No se adjuntaron los archivos al momento de publicar el SR. </t>
         </is>
       </c>
       <c r="AB40" s="8" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AI40" s="8" t="inlineStr">
         <is>
-          <t>2 enlaces, lo puede diseñar Preventa</t>
+          <t>No se adjuntaron los archivos al momento de publicar el SR.</t>
         </is>
       </c>
       <c r="AJ40" s="8" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260504_1345314</t>
+          <t>SR_VTP_20260424_1343697</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Carta No. 000190-2026/PROINVERSION/DPP/VI.34 // INFORMATIVO</t>
+          <t>Solicito personal SOPORTE DE REVISIÓN MW EXISTENTE CLIENTE MINJUS - MINJUSDH0126_0413_INT</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>vtp_fernando.munoz</t>
+          <t>vtp_vanessa.balbuena</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
@@ -6887,22 +6887,22 @@
       </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_MICROWAVE</t>
         </is>
       </c>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>Review letters of interference/notification/information about BITEL optical cable</t>
+          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>danielmr_vtp</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Infrastructure Center VTP|Infrastructure Corporate Department</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -6912,22 +6912,22 @@
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:24:00</t>
+          <t>24/04/2026 10:42:00</t>
         </is>
       </c>
       <c r="V41" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:53:00</t>
+          <t>24/04/2026 11:12:00</t>
         </is>
       </c>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 11:53:00</t>
+          <t>30/04/2026 11:12:00</t>
         </is>
       </c>
       <c r="X41" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:43:00</t>
+          <t>24/04/2026 10:50:00</t>
         </is>
       </c>
       <c r="Y41" s="8" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="AA41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04 11:43:26.02 : [1]Nhận xét | Comments || N/A || No se adjuntaron los archivos al momento de publicar el SR. </t>
+          <t xml:space="preserve">2026-04-24 10:50:19.854 : [1]Nhận xét | Comments || N/A || Wrong unit </t>
         </is>
       </c>
       <c r="AB41" s="8" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="AG41" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*****</t>
         </is>
       </c>
       <c r="AH41" s="8" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AI41" s="8" t="inlineStr">
         <is>
-          <t>No se adjuntaron los archivos al momento de publicar el SR.</t>
+          <t>Wrong unit</t>
         </is>
       </c>
       <c r="AJ41" s="8" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260424_1343697</t>
+          <t>SR_VTP_20260601_1353748</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -7017,22 +7017,22 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Solicito personal SOPORTE DE REVISIÓN MW EXISTENTE CLIENTE MINJUS - MINJUSDH0126_0413_INT</t>
+          <t>SME_LINEA DE VISTA_VALIDACION DE CAPACIDAD_ MW 01.06 | 9 NEW VALIDATION</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>vtp_vanessa.balbuena</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
@@ -7077,22 +7077,22 @@
       </c>
       <c r="P42" s="8" t="inlineStr">
         <is>
-          <t>VTP_MICROWAVE</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
+          <t>Design/Redesign Corp MW links</t>
         </is>
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>danielmr_vtp</t>
+          <t>vtp_edgar.arteaga</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Infrastructure Center VTP|Infrastructure Corporate Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -7102,22 +7102,22 @@
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 10:42:00</t>
+          <t>01/06/2026 18:43:00</t>
         </is>
       </c>
       <c r="V42" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 11:12:00</t>
+          <t>01/06/2026 19:11:00</t>
         </is>
       </c>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>30/04/2026 11:12:00</t>
+          <t>05/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X42" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 10:50:00</t>
+          <t>03/06/2026 14:19:00</t>
         </is>
       </c>
       <c r="Y42" s="8" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="AA42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-24 10:50:19.854 : [1]Nhận xét | Comments || N/A || Wrong unit </t>
+          <t xml:space="preserve">2026-06-03 14:19:52.956 : [1]Nhận xét | Comments || N/A || According decision of TC, tra only evaluate projects over 100 </t>
         </is>
       </c>
       <c r="AB42" s="8" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="AG42" s="8" t="inlineStr">
         <is>
-          <t>*****</t>
+          <t>*</t>
         </is>
       </c>
       <c r="AH42" s="8" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AI42" s="8" t="inlineStr">
         <is>
-          <t>Wrong unit</t>
+          <t>According decision of TC, tra only evaluate projects over 100</t>
         </is>
       </c>
       <c r="AJ42" s="8" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/3/26, 7:30 PM</t>
+          <t>Date Export: 6/4/26, 8:28 AM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260603_1354525</t>
+          <t>SR_VTP_20260603_1354524</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>CAJ0059-CAJ0345</t>
+          <t>LAM0190B3U2-PIU0415_1</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260603_1354524</t>
+          <t>SR_VTP_20260603_1354525</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>LAM0190B3U2-PIU0415_1</t>
+          <t>CAJ0059-CAJ0345</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352971</t>
+          <t>SR_VTP_20260529_1352682</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for IMP-3028 PO_02-01/2026/F/VTPr-2PT/FERRETERIA AMA</t>
+          <t>OFICIO N° 7531-2026-MTC/19.03 / INSPECCIÓN CONJUNTA</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t/>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>KCS for new goods of Transmission</t>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:20:00</t>
+          <t>29/05/2026 09:15:00</t>
         </is>
       </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:48:00</t>
+          <t>29/05/2026 09:44:00</t>
         </is>
       </c>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 08:00:00</t>
+          <t>09/06/2026 09:44:00</t>
         </is>
       </c>
       <c r="X29" s="8" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352904</t>
+          <t>SR_VTP_20260528_1352463</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for IMP-3007  01/2026/VTPr-THOAIANH/OPTICAL ACCESSORIES ML 2026</t>
+          <t>Se solicita fecha de inicio de inicio de trabajo de: CRONOGRAMA GENERAL PARA LA LIBERACION DE LA INTERFERENCIA CON EL PROYECTO “REHABILITACIÓN Y MEJORAMIENTO DE LA CARRETERA EMP. RUTA 18A (PTE. RANCHO) - CHAGLLA - RUMICHACA. TRAMO I”</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t/>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="P30" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>KCS for new goods of Transmission</t>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -4822,17 +4822,17 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 15:21:00</t>
+          <t>28/05/2026 17:36:00</t>
         </is>
       </c>
       <c r="V30" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 15:49:00</t>
+          <t>28/05/2026 18:03:00</t>
         </is>
       </c>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>05/06/2026 15:49:00</t>
+          <t>09/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X30" s="8" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352682</t>
+          <t>SR_VTP_20260522_1350563</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>OFICIO N° 7531-2026-MTC/19.03 / INSPECCIÓN CONJUNTA</t>
+          <t>PROYECTO MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -4987,22 +4987,22 @@
       </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
+          <t>Design transmission for corporate customers (&gt; 500 Link)</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>vtp_gerardo.alvarado</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -5012,17 +5012,17 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 09:15:00</t>
+          <t>22/05/2026 16:42:00</t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 09:44:00</t>
+          <t>22/05/2026 17:11:00</t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44:00</t>
+          <t>06/07/2026 17:11:00</t>
         </is>
       </c>
       <c r="X31" s="8" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260528_1352463</t>
+          <t>SR_VTP_20260518_1349100</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Se solicita fecha de inicio de inicio de trabajo de: CRONOGRAMA GENERAL PARA LA LIBERACION DE LA INTERFERENCIA CON EL PROYECTO “REHABILITACIÓN Y MEJORAMIENTO DE LA CARRETERA EMP. RUTA 18A (PTE. RANCHO) - CHAGLLA - RUMICHACA. TRAMO I”</t>
+          <t>OXI_Ucayali Project - SMART CITY &amp; DARK FIBER &amp; INTERNET SERVICE - 101 sites</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -5177,22 +5177,22 @@
       </c>
       <c r="P32" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
+          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>vtp_julio.inga</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 17:36:00</t>
+          <t>18/05/2026 11:34:00</t>
         </is>
       </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 18:03:00</t>
+          <t>18/05/2026 12:03:00</t>
         </is>
       </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>09/06/2026 08:00:00</t>
+          <t>08/06/2026 12:03:00</t>
         </is>
       </c>
       <c r="X32" s="8" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260522_1350563</t>
+          <t>SR_VTP_20260525_1351186</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -5307,17 +5307,17 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>PROYECTO MINISTERIO PUBLICO</t>
+          <t>CAJ0222-CAJ2004_1  Recover monitor of link 1, Upgrade MW by configuration to 512QAM,  *</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 500 Link)</t>
+          <t>Design/Redesign Metro MW links</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>vtp_gerardo.alvarado</t>
+          <t>vtp_kathy.valle</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -5392,22 +5392,22 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 16:42:00</t>
+          <t>25/05/2026 15:48:00</t>
         </is>
       </c>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t>22/05/2026 17:11:00</t>
+          <t>25/05/2026 16:16:00</t>
         </is>
       </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t>06/07/2026 17:11:00</t>
+          <t>28/05/2026 16:16:00</t>
         </is>
       </c>
       <c r="X33" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>26/05/2026 12:46:00</t>
         </is>
       </c>
       <c r="Y33" s="8" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="AA33" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">2026-05-26 12:47:09.621 : [1]Nhận xét | Comments || N/A || Incorrect unit </t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AI33" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>Incorrect unit</t>
         </is>
       </c>
       <c r="AJ33" s="8" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260518_1349100</t>
+          <t>SR_VTP_20260518_1349058</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>OXI_Ucayali Project - SMART CITY &amp; DARK FIBER &amp; INTERNET SERVICE - 101 sites</t>
+          <t>FACTIBILIDAD MINEDU 1K</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>vtp_julio.inga</t>
+          <t>vtp_thangnq1</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
@@ -5582,22 +5582,22 @@
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 11:34:00</t>
+          <t>18/05/2026 10:46:00</t>
         </is>
       </c>
       <c r="V34" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 12:03:00</t>
+          <t>18/05/2026 11:15:00</t>
         </is>
       </c>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 12:03:00</t>
+          <t>08/06/2026 11:15:00</t>
         </is>
       </c>
       <c r="X34" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>18/05/2026 14:31:00</t>
         </is>
       </c>
       <c r="Y34" s="8" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AA34" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">2026-05-18 14:31:19.315 : [1]Nhận xét | Comments || N/A || Elegir las categoria &gt; 500 links </t>
         </is>
       </c>
       <c r="AB34" s="8" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AI34" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>Elegir las categoria &gt; 500 links</t>
         </is>
       </c>
       <c r="AJ34" s="8" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260525_1351186</t>
+          <t>SR_VTP_20260511_1347286</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>CAJ0222-CAJ2004_1  Recover monitor of link 1, Upgrade MW by configuration to 512QAM,  *</t>
+          <t>KCS Testing at MInka WH for IMP-2987 03/2026/VTPr-VMC/CABLE 24FO-ML2026</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -5747,22 +5747,22 @@
       </c>
       <c r="P35" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_DWDM</t>
         </is>
       </c>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>Design/Redesign Metro MW links</t>
+          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>vtp_kathy.valle</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -5772,22 +5772,22 @@
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 15:48:00</t>
+          <t>11/05/2026 17:56:00</t>
         </is>
       </c>
       <c r="V35" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 16:16:00</t>
+          <t>11/05/2026 18:23:00</t>
         </is>
       </c>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 16:16:00</t>
+          <t>18/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X35" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 12:46:00</t>
+          <t>12/05/2026 11:17:00</t>
         </is>
       </c>
       <c r="Y35" s="8" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AA35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26 12:47:09.621 : [1]Nhận xét | Comments || N/A || Incorrect unit </t>
+          <t xml:space="preserve">2026-05-12 11:17:09.237 : [1]Nhận xét | Comments || N/A || Wrong division </t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AI35" s="8" t="inlineStr">
         <is>
-          <t>Incorrect unit</t>
+          <t>Wrong division</t>
         </is>
       </c>
       <c r="AJ35" s="8" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260518_1349058</t>
+          <t>SR_VTP_20260508_1346759</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>FACTIBILIDAD MINEDU 1K</t>
+          <t>KCS Testing at MInka WH for 01/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
@@ -5937,22 +5937,22 @@
       </c>
       <c r="P36" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_DWDM</t>
         </is>
       </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
+          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
         </is>
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>vtp_thangnq1</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -5962,22 +5962,22 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 10:46:00</t>
+          <t>08/05/2026 14:39:00</t>
         </is>
       </c>
       <c r="V36" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 11:15:00</t>
+          <t>08/05/2026 15:04:00</t>
         </is>
       </c>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>08/06/2026 11:15:00</t>
+          <t>14/05/2026 15:04:00</t>
         </is>
       </c>
       <c r="X36" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 14:31:00</t>
+          <t>08/05/2026 18:12:00</t>
         </is>
       </c>
       <c r="Y36" s="8" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AA36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18 14:31:19.315 : [1]Nhận xét | Comments || N/A || Elegir las categoria &gt; 500 links </t>
+          <t xml:space="preserve">2026-05-08 18:12:40.243 : [1]Nhận xét | Comments || N/A || Which plan? Not related to TRA. Detail that, </t>
         </is>
       </c>
       <c r="AB36" s="8" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="AI36" s="8" t="inlineStr">
         <is>
-          <t>Elegir las categoria &gt; 500 links</t>
+          <t>Which plan? Not related to TRA. Detail that,</t>
         </is>
       </c>
       <c r="AJ36" s="8" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260511_1347286</t>
+          <t>SR_VTP_20260507_1346521</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for IMP-2987 03/2026/VTPr-VMC/CABLE 24FO-ML2026</t>
+          <t>DISEÑO LAST MILLE -   MINEDU WAN</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -6127,22 +6127,22 @@
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
+          <t>Design Transmission for new BTS "Less than 80"</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_ronald.jimenez</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>11/05/2026 17:56:00</t>
+          <t>07/05/2026 17:47:00</t>
         </is>
       </c>
       <c r="V37" s="8" t="inlineStr">
         <is>
-          <t>11/05/2026 18:23:00</t>
+          <t>07/05/2026 18:10:00</t>
         </is>
       </c>
       <c r="W37" s="8" t="inlineStr">
         <is>
-          <t>18/05/2026 08:00:00</t>
+          <t>13/05/2026 08:00:00</t>
         </is>
       </c>
       <c r="X37" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 11:17:00</t>
+          <t>08/05/2026 12:43:00</t>
         </is>
       </c>
       <c r="Y37" s="8" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="AA37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-12 11:17:09.237 : [1]Nhận xét | Comments || N/A || Wrong division </t>
+          <t xml:space="preserve">2026-05-08 12:43:00.713 : [1]Nhận xét | Comments || N/A || Cambiar de categoria a diseño &lt; 50 enlaces </t>
         </is>
       </c>
       <c r="AB37" s="8" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AI37" s="8" t="inlineStr">
         <is>
-          <t>Wrong division</t>
+          <t>Cambiar de categoria a diseño &lt; 50 enlaces</t>
         </is>
       </c>
       <c r="AJ37" s="8" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260508_1346759</t>
+          <t>SR_VTP_20260507_1346500</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 01/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
+          <t>KCS Testing at MInka WH for 03/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -6342,22 +6342,22 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 14:39:00</t>
+          <t>07/05/2026 16:51:00</t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 15:04:00</t>
+          <t>07/05/2026 17:20:00</t>
         </is>
       </c>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 15:04:00</t>
+          <t>13/05/2026 17:20:00</t>
         </is>
       </c>
       <c r="X38" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 18:12:00</t>
+          <t>08/05/2026 11:05:00</t>
         </is>
       </c>
       <c r="Y38" s="8" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="AA38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 18:12:40.243 : [1]Nhận xét | Comments || N/A || Which plan? Not related to TRA. Detail that, </t>
+          <t xml:space="preserve">2026-05-08 11:05:45.017 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
         </is>
       </c>
       <c r="AB38" s="8" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AI38" s="8" t="inlineStr">
         <is>
-          <t>Which plan? Not related to TRA. Detail that,</t>
+          <t>If requested without TRA confirmation of quality then that team responsible,</t>
         </is>
       </c>
       <c r="AJ38" s="8" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346521</t>
+          <t>SR_VTP_20260507_1346501</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE -   MINEDU WAN</t>
+          <t>KCS Testing at MInka WH for 02/2026/VTPr-GFORESTAL/ESSALUD/POLES</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_DWDM</t>
         </is>
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "Less than 80"</t>
+          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>vtp_ronald.jimenez</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -6532,22 +6532,22 @@
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:47:00</t>
+          <t>07/05/2026 16:59:00</t>
         </is>
       </c>
       <c r="V39" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 18:10:00</t>
+          <t>07/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 08:00:00</t>
+          <t>13/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="X39" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 12:43:00</t>
+          <t>08/05/2026 11:02:00</t>
         </is>
       </c>
       <c r="Y39" s="8" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AA39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 12:43:00.713 : [1]Nhận xét | Comments || N/A || Cambiar de categoria a diseño &lt; 50 enlaces </t>
+          <t xml:space="preserve">2026-05-08 11:02:52.613 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
         </is>
       </c>
       <c r="AB39" s="8" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="AI39" s="8" t="inlineStr">
         <is>
-          <t>Cambiar de categoria a diseño &lt; 50 enlaces</t>
+          <t>If requested without TRA confirmation of quality then that team responsible,</t>
         </is>
       </c>
       <c r="AJ39" s="8" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346500</t>
+          <t>SR_VTP_20260507_1346469</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 03/2026/VTPr-GFORESTAL/WOODEN POLES 9M</t>
+          <t>DISEÑO LAST MILLE - HNHU (Hospital Nacional Hipólito Unanue)</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
@@ -6697,22 +6697,22 @@
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
+          <t>Design Transmission for new BTS "Less than 80"</t>
         </is>
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_ronald.jimenez</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -6722,22 +6722,22 @@
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 16:51:00</t>
+          <t>07/05/2026 15:40:00</t>
         </is>
       </c>
       <c r="V40" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:20:00</t>
+          <t>07/05/2026 15:57:00</t>
         </is>
       </c>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 17:20:00</t>
+          <t>12/05/2026 15:57:00</t>
         </is>
       </c>
       <c r="X40" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 11:05:00</t>
+          <t>07/05/2026 18:08:00</t>
         </is>
       </c>
       <c r="Y40" s="8" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AA40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 11:05:45.017 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
+          <t xml:space="preserve">2026-05-07 18:04:17.794 : [1]Nhận xét | Comments || N/A || Pueder ser diseñado por Preventa, son 2 enlaces </t>
         </is>
       </c>
       <c r="AB40" s="8" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AI40" s="8" t="inlineStr">
         <is>
-          <t>If requested without TRA confirmation of quality then that team responsible,</t>
+          <t>Pueder ser diseñado por Preventa, son 2 enlaces</t>
         </is>
       </c>
       <c r="AJ40" s="8" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346501</t>
+          <t>SR_VTP_20260505_1345858</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>KCS Testing at MInka WH for 02/2026/VTPr-GFORESTAL/ESSALUD/POLES</t>
+          <t>DISEÑO LAST MILLE - INO -  2 LINKS</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_jeferson.pajuelo</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|DWDM Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
@@ -6887,22 +6887,22 @@
       </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>VTP_DWDM_Goods Inspection (KCS Testing for Technical Materials)</t>
+          <t>Design Transmission for new BTS "Less than 80"</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>vtp_jonathan.sialer</t>
+          <t>vtp_ronald.jimenez</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -6912,22 +6912,22 @@
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 16:59:00</t>
+          <t>05/05/2026 16:59:00</t>
         </is>
       </c>
       <c r="V41" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 17:28:00</t>
+          <t>05/05/2026 17:22:00</t>
         </is>
       </c>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t>13/05/2026 17:28:00</t>
+          <t>08/05/2026 17:22:00</t>
         </is>
       </c>
       <c r="X41" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 11:02:00</t>
+          <t>06/05/2026 16:48:00</t>
         </is>
       </c>
       <c r="Y41" s="8" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="AA41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-08 11:02:52.613 : [1]Nhận xét | Comments || N/A || If requested without TRA confirmation of quality then that team responsible, </t>
+          <t xml:space="preserve">2026-05-06 16:48:30.879 : [1]Nhận xét | Comments || N/A || 2 enlaces, lo puede diseñar Preventa </t>
         </is>
       </c>
       <c r="AB41" s="8" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AI41" s="8" t="inlineStr">
         <is>
-          <t>If requested without TRA confirmation of quality then that team responsible,</t>
+          <t>2 enlaces, lo puede diseñar Preventa</t>
         </is>
       </c>
       <c r="AJ41" s="8" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260507_1346469</t>
+          <t>SR_VTP_20260504_1345314</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE - HNHU (Hospital Nacional Hipólito Unanue)</t>
+          <t>Carta No. 000190-2026/PROINVERSION/DPP/VI.34 // INFORMATIVO</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_fernando.munoz</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -7077,22 +7077,22 @@
       </c>
       <c r="P42" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "Less than 80"</t>
+          <t>Review letters of interference/notification/information about BITEL optical cable</t>
         </is>
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>vtp_ronald.jimenez</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -7102,22 +7102,22 @@
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 15:40:00</t>
+          <t>04/05/2026 11:24:00</t>
         </is>
       </c>
       <c r="V42" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 15:57:00</t>
+          <t>04/05/2026 11:53:00</t>
         </is>
       </c>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>12/05/2026 15:57:00</t>
+          <t>07/05/2026 11:53:00</t>
         </is>
       </c>
       <c r="X42" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 18:08:00</t>
+          <t>04/05/2026 11:43:00</t>
         </is>
       </c>
       <c r="Y42" s="8" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="AA42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-07 18:04:17.794 : [1]Nhận xét | Comments || N/A || Pueder ser diseñado por Preventa, son 2 enlaces </t>
+          <t xml:space="preserve">2026-05-04 11:43:26.02 : [1]Nhận xét | Comments || N/A || No se adjuntaron los archivos al momento de publicar el SR. </t>
         </is>
       </c>
       <c r="AB42" s="8" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AI42" s="8" t="inlineStr">
         <is>
-          <t>Pueder ser diseñado por Preventa, son 2 enlaces</t>
+          <t>No se adjuntaron los archivos al momento de publicar el SR.</t>
         </is>
       </c>
       <c r="AJ42" s="8" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260505_1345858</t>
+          <t>SR_VTP_20260424_1343697</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO LAST MILLE - INO -  2 LINKS</t>
+          <t>Solicito personal SOPORTE DE REVISIÓN MW EXISTENTE CLIENTE MINJUS - MINJUSDH0126_0413_INT</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>vtp_jeferson.pajuelo</t>
+          <t>vtp_vanessa.balbuena</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
@@ -7267,22 +7267,22 @@
       </c>
       <c r="P43" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_MICROWAVE</t>
         </is>
       </c>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "Less than 80"</t>
+          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>vtp_ronald.jimenez</t>
+          <t>danielmr_vtp</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Infrastructure Center VTP|Infrastructure Corporate Department</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -7292,22 +7292,22 @@
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>05/05/2026 16:59:00</t>
+          <t>24/04/2026 10:42:00</t>
         </is>
       </c>
       <c r="V43" s="8" t="inlineStr">
         <is>
-          <t>05/05/2026 17:22:00</t>
+          <t>24/04/2026 11:12:00</t>
         </is>
       </c>
       <c r="W43" s="8" t="inlineStr">
         <is>
-          <t>08/05/2026 17:22:00</t>
+          <t>30/04/2026 11:12:00</t>
         </is>
       </c>
       <c r="X43" s="8" t="inlineStr">
         <is>
-          <t>06/05/2026 16:48:00</t>
+          <t>24/04/2026 10:50:00</t>
         </is>
       </c>
       <c r="Y43" s="8" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AA43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-06 16:48:30.879 : [1]Nhận xét | Comments || N/A || 2 enlaces, lo puede diseñar Preventa </t>
+          <t xml:space="preserve">2026-04-24 10:50:19.854 : [1]Nhận xét | Comments || N/A || Wrong unit </t>
         </is>
       </c>
       <c r="AB43" s="8" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AG43" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*****</t>
         </is>
       </c>
       <c r="AH43" s="8" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AI43" s="8" t="inlineStr">
         <is>
-          <t>2 enlaces, lo puede diseñar Preventa</t>
+          <t>Wrong unit</t>
         </is>
       </c>
       <c r="AJ43" s="8" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260504_1345314</t>
+          <t>SR_VTP_20260601_1353748</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -7397,22 +7397,22 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Carta No. 000190-2026/PROINVERSION/DPP/VI.34 // INFORMATIVO</t>
+          <t>SME_LINEA DE VISTA_VALIDACION DE CAPACIDAD_ MW 01.06 | 9 NEW VALIDATION</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>vtp_fernando.munoz</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -7457,22 +7457,22 @@
       </c>
       <c r="P44" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>Review letters of interference/notification/information about BITEL optical cable</t>
+          <t>Design/Redesign Corp MW links</t>
         </is>
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>vtp_edgar.arteaga</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -7482,22 +7482,22 @@
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:24:00</t>
+          <t>01/06/2026 18:43:00</t>
         </is>
       </c>
       <c r="V44" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:53:00</t>
+          <t>01/06/2026 19:11:00</t>
         </is>
       </c>
       <c r="W44" s="8" t="inlineStr">
         <is>
-          <t>07/05/2026 11:53:00</t>
+          <t>05/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X44" s="8" t="inlineStr">
         <is>
-          <t>04/05/2026 11:43:00</t>
+          <t>03/06/2026 14:19:00</t>
         </is>
       </c>
       <c r="Y44" s="8" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AA44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04 11:43:26.02 : [1]Nhận xét | Comments || N/A || No se adjuntaron los archivos al momento de publicar el SR. </t>
+          <t xml:space="preserve">2026-06-03 14:19:52.956 : [1]Nhận xét | Comments || N/A || According decision of TC, tra only evaluate projects over 100 </t>
         </is>
       </c>
       <c r="AB44" s="8" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AG44" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*</t>
         </is>
       </c>
       <c r="AH44" s="8" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="AI44" s="8" t="inlineStr">
         <is>
-          <t>No se adjuntaron los archivos al momento de publicar el SR.</t>
+          <t>According decision of TC, tra only evaluate projects over 100</t>
         </is>
       </c>
       <c r="AJ44" s="8" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260424_1343697</t>
+          <t>SR_VTP_20260528_1352458</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -7587,22 +7587,22 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Solicito personal SOPORTE DE REVISIÓN MW EXISTENTE CLIENTE MINJUS - MINJUSDH0126_0413_INT</t>
+          <t>TECHNICAL EVALUATION: ML Q3 - Q4 CORP - MUFAS ODF / MW</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>vtp_vanessa.balbuena</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -7647,22 +7647,22 @@
       </c>
       <c r="P45" s="8" t="inlineStr">
         <is>
-          <t>VTP_MICROWAVE</t>
+          <t>VTP_TRANS_Bidding</t>
         </is>
       </c>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>MW_NEW INTEGRATION CUSTOMER NETWORK</t>
+          <t>TRANS - Technical review for biddings</t>
         </is>
       </c>
       <c r="R45" s="8" t="inlineStr">
         <is>
-          <t>danielmr_vtp</t>
+          <t>vtp_alisson.astudillo</t>
         </is>
       </c>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Infrastructure Center VTP|Infrastructure Corporate Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -7672,22 +7672,22 @@
       </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 10:42:00</t>
+          <t>28/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="V45" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 11:12:00</t>
+          <t>28/05/2026 17:52:00</t>
         </is>
       </c>
       <c r="W45" s="8" t="inlineStr">
         <is>
-          <t>30/04/2026 11:12:00</t>
+          <t>05/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X45" s="8" t="inlineStr">
         <is>
-          <t>24/04/2026 10:50:00</t>
+          <t>01/06/2026 10:25:00</t>
         </is>
       </c>
       <c r="Y45" s="8" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="AA45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-24 10:50:19.854 : [1]Nhận xét | Comments || N/A || Wrong unit </t>
+          <t xml:space="preserve">2026-06-01 10:25:38.999 : [1]Nhận xét | Comments || N/A || Wrong division. </t>
         </is>
       </c>
       <c r="AB45" s="8" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AG45" s="8" t="inlineStr">
         <is>
-          <t>*****</t>
+          <t/>
         </is>
       </c>
       <c r="AH45" s="8" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="AI45" s="8" t="inlineStr">
         <is>
-          <t>Wrong unit</t>
+          <t>Wrong division.</t>
         </is>
       </c>
       <c r="AJ45" s="8" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260601_1353748</t>
+          <t>SR_VTP_20260528_1352222</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>SME_LINEA DE VISTA_VALIDACION DE CAPACIDAD_ MW 01.06 | 9 NEW VALIDATION</t>
+          <t>DISEÑO DE FACTIBILIDAD PARA COBERTURA MOVIL 4G/5G - CHINA UNICOM</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
@@ -7842,17 +7842,17 @@
       </c>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>Design/Redesign Corp MW links</t>
+          <t>Design Transmission for new BTS "More than 80"</t>
         </is>
       </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t>vtp_edgar.arteaga</t>
+          <t>vtp_ronald.jimenez</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -7862,22 +7862,22 @@
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 18:43:00</t>
+          <t>28/05/2026 10:35:00</t>
         </is>
       </c>
       <c r="V46" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 19:11:00</t>
+          <t>28/05/2026 10:49:00</t>
         </is>
       </c>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t>05/06/2026 08:00:00</t>
+          <t>04/06/2026 10:49:00</t>
         </is>
       </c>
       <c r="X46" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 14:19:00</t>
+          <t>30/05/2026 08:12:00</t>
         </is>
       </c>
       <c r="Y46" s="8" t="inlineStr">
@@ -7892,7 +7892,8 @@
       </c>
       <c r="AA46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 14:19:52.956 : [1]Nhận xét | Comments || N/A || According decision of TC, tra only evaluate projects over 100 </t>
+          <t xml:space="preserve">2026-05-30 08:12:29.214 : [1]Nhận xét | Comments || N/A || This only 1 BTS, TRA not responsible of coordinator in TC with RAD.
+Normal procedure request RAD give position and coordinate with all departments. </t>
         </is>
       </c>
       <c r="AB46" s="8" t="inlineStr">
@@ -7922,7 +7923,7 @@
       </c>
       <c r="AG46" s="8" t="inlineStr">
         <is>
-          <t>*</t>
+          <t/>
         </is>
       </c>
       <c r="AH46" s="8" t="inlineStr">
@@ -7932,7 +7933,8 @@
       </c>
       <c r="AI46" s="8" t="inlineStr">
         <is>
-          <t>According decision of TC, tra only evaluate projects over 100</t>
+          <t>This only 1 BTS, TRA not responsible of coordinator in TC with RAD.
+Normal procedure request RAD give position and coordinate with all departments.</t>
         </is>
       </c>
       <c r="AJ46" s="8" t="inlineStr">
@@ -7957,7 +7959,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260528_1352458</t>
+          <t>SR_VTP_20260528_1352501</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -7967,7 +7969,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>TECHNICAL EVALUATION: ML Q3 - Q4 CORP - MUFAS ODF / MW</t>
+          <t>SME_LINEA DE VISTA_VALIDACION DE CAPACIDAD_ MW 28.05 | 8 NEW VALIDATION</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -7982,7 +7984,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -8002,7 +8004,7 @@
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
@@ -8027,22 +8029,22 @@
       </c>
       <c r="P47" s="8" t="inlineStr">
         <is>
-          <t>VTP_TRANS_Bidding</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>TRANS - Technical review for biddings</t>
+          <t>Design/Redesign Corp MW links</t>
         </is>
       </c>
       <c r="R47" s="8" t="inlineStr">
         <is>
-          <t>vtp_alisson.astudillo</t>
+          <t>vtp_edgar.arteaga</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -8052,22 +8054,22 @@
       </c>
       <c r="U47" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 17:28:00</t>
+          <t>28/05/2026 19:24:00</t>
         </is>
       </c>
       <c r="V47" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 17:52:00</t>
+          <t>28/05/2026 19:52:00</t>
         </is>
       </c>
       <c r="W47" s="8" t="inlineStr">
         <is>
-          <t>05/06/2026 08:00:00</t>
+          <t>03/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X47" s="8" t="inlineStr">
         <is>
-          <t>01/06/2026 10:25:00</t>
+          <t>30/05/2026 08:11:00</t>
         </is>
       </c>
       <c r="Y47" s="8" t="inlineStr">
@@ -8082,7 +8084,7 @@
       </c>
       <c r="AA47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 10:25:38.999 : [1]Nhận xét | Comments || N/A || Wrong division. </t>
+          <t xml:space="preserve">2026-05-30 08:10:45.882 : [1]Nhận xét | Comments || N/A || No indica ubicacion del cliente ni donde enlace, imposible de procesar. </t>
         </is>
       </c>
       <c r="AB47" s="8" t="inlineStr">
@@ -8112,7 +8114,7 @@
       </c>
       <c r="AG47" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*</t>
         </is>
       </c>
       <c r="AH47" s="8" t="inlineStr">
@@ -8122,7 +8124,7 @@
       </c>
       <c r="AI47" s="8" t="inlineStr">
         <is>
-          <t>Wrong division.</t>
+          <t>No indica ubicacion del cliente ni donde enlace, imposible de procesar.</t>
         </is>
       </c>
       <c r="AJ47" s="8" t="inlineStr">
@@ -8147,7 +8149,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260528_1352222</t>
+          <t>SR_VTP_20260521_1350086</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -8157,7 +8159,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>DISEÑO DE FACTIBILIDAD PARA COBERTURA MOVIL 4G/5G - CHINA UNICOM</t>
+          <t>BDS - CORP - PMO - ENVIO DE MATERIAL SEGUN ULTIMO DISEÑO PARA NUEVA RUTA ARE0088-ARE0089 EN PROYECTO MSOUTHERN0723_0038_INT-AN02</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -8192,7 +8194,7 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
@@ -8222,12 +8224,12 @@
       </c>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>Design Transmission for new BTS "More than 80"</t>
+          <t>Design/redesign optical fiber routes</t>
         </is>
       </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>vtp_ronald.jimenez</t>
+          <t>wilsonvc_lim</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
@@ -8242,22 +8244,22 @@
       </c>
       <c r="U48" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 10:35:00</t>
+          <t>21/05/2026 11:58:00</t>
         </is>
       </c>
       <c r="V48" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 10:49:00</t>
+          <t>21/05/2026 15:00:00</t>
         </is>
       </c>
       <c r="W48" s="8" t="inlineStr">
         <is>
-          <t>04/06/2026 10:49:00</t>
+          <t>26/05/2026 15:00:00</t>
         </is>
       </c>
       <c r="X48" s="8" t="inlineStr">
         <is>
-          <t>30/05/2026 08:12:00</t>
+          <t>25/05/2026 09:26:00</t>
         </is>
       </c>
       <c r="Y48" s="8" t="inlineStr">
@@ -8272,8 +8274,7 @@
       </c>
       <c r="AA48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-30 08:12:29.214 : [1]Nhận xét | Comments || N/A || This only 1 BTS, TRA not responsible of coordinator in TC with RAD.
-Normal procedure request RAD give position and coordinate with all departments. </t>
+          <t xml:space="preserve">2026-05-25 09:26:39.946 : [1]Nhận xét | Comments || N/A || This CORP project, not TRA project. </t>
         </is>
       </c>
       <c r="AB48" s="8" t="inlineStr">
@@ -8313,8 +8314,7 @@
       </c>
       <c r="AI48" s="8" t="inlineStr">
         <is>
-          <t>This only 1 BTS, TRA not responsible of coordinator in TC with RAD.
-Normal procedure request RAD give position and coordinate with all departments.</t>
+          <t>This CORP project, not TRA project.</t>
         </is>
       </c>
       <c r="AJ48" s="8" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260528_1352501</t>
+          <t>SR_VTP_20260514_1348134</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>SME_LINEA DE VISTA_VALIDACION DE CAPACIDAD_ MW 28.05 | 8 NEW VALIDATION</t>
+          <t>CLIENTE: PNP || DESIGN OF BACK UP LINKS || 185 LINKS</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
@@ -8414,17 +8414,17 @@
       </c>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>Design/Redesign Corp MW links</t>
+          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
         </is>
       </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>vtp_edgar.arteaga</t>
+          <t>vtp_ulises.benvenuto</t>
         </is>
       </c>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Fixed broadband Center VTP|VTP FBB Design Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -8434,22 +8434,22 @@
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 19:24:00</t>
+          <t>14/05/2026 09:36:00</t>
         </is>
       </c>
       <c r="V49" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 19:52:00</t>
+          <t>14/05/2026 09:57:00</t>
         </is>
       </c>
       <c r="W49" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 08:00:00</t>
+          <t>04/06/2026 09:57:00</t>
         </is>
       </c>
       <c r="X49" s="8" t="inlineStr">
         <is>
-          <t>30/05/2026 08:11:00</t>
+          <t>21/05/2026 10:40:00</t>
         </is>
       </c>
       <c r="Y49" s="8" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="AA49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-30 08:10:45.882 : [1]Nhận xét | Comments || N/A || No indica ubicacion del cliente ni donde enlace, imposible de procesar. </t>
+          <t xml:space="preserve">2026-05-21 10:40:25.226 : [1]Nhận xét | Comments || N/A || No information attached </t>
         </is>
       </c>
       <c r="AB49" s="8" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="AG49" s="8" t="inlineStr">
         <is>
-          <t>*</t>
+          <t/>
         </is>
       </c>
       <c r="AH49" s="8" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AI49" s="8" t="inlineStr">
         <is>
-          <t>No indica ubicacion del cliente ni donde enlace, imposible de procesar.</t>
+          <t>No information attached</t>
         </is>
       </c>
       <c r="AJ49" s="8" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260521_1350086</t>
+          <t>SR_VTP_20260602_1353904</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -8539,22 +8539,22 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>BDS - CORP - PMO - ENVIO DE MATERIAL SEGUN ULTIMO DISEÑO PARA NUEVA RUTA ARE0088-ARE0089 EN PROYECTO MSOUTHERN0723_0038_INT-AN02</t>
+          <t>OFICIO N° 7314-2026-MTC/19.03 / INFORMATIVO</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Evaluated</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_fernando.munoz</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr">
@@ -8599,22 +8599,22 @@
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
+          <t>VTP_CABLE OPERATIONS</t>
         </is>
       </c>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>Design/redesign optical fiber routes</t>
+          <t>Review letters of notification/impact about BITEL optical cable</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>wilsonvc_lim</t>
+          <t>vtp_jesus.gonzales.1</t>
         </is>
       </c>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -8624,22 +8624,22 @@
       </c>
       <c r="U50" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 11:58:00</t>
+          <t>02/06/2026 11:11:00</t>
         </is>
       </c>
       <c r="V50" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 15:00:00</t>
+          <t>02/06/2026 11:32:00</t>
         </is>
       </c>
       <c r="W50" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 15:00:00</t>
+          <t>11/06/2026 11:32:00</t>
         </is>
       </c>
       <c r="X50" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 09:26:00</t>
+          <t>03/06/2026 11:30:00</t>
         </is>
       </c>
       <c r="Y50" s="8" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AA50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 09:26:39.946 : [1]Nhận xét | Comments || N/A || This CORP project, not TRA project. </t>
+          <t/>
         </is>
       </c>
       <c r="AB50" s="8" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="AI50" s="8" t="inlineStr">
         <is>
-          <t>This CORP project, not TRA project.</t>
+          <t/>
         </is>
       </c>
       <c r="AJ50" s="8" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260514_1348134</t>
+          <t>SR_VTP_20260514_1348235</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>CLIENTE: PNP || DESIGN OF BACK UP LINKS || 185 LINKS</t>
+          <t>TECHNICAL EVALUATION : PJ0226_1567_VPN - 042026/VTPr-PJ - ACCESSORIES</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Evaluated</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>Design transmission for corporate customers (&gt; 50 Link)</t>
+          <t>Technical review for biddings</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>vtp_ulises.benvenuto</t>
+          <t>vtp_judith.araujo</t>
         </is>
       </c>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Corporate Center B2B VTP|Tech Sale Department</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -8814,22 +8814,22 @@
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 09:36:00</t>
+          <t>14/05/2026 14:53:00</t>
         </is>
       </c>
       <c r="V51" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 09:57:00</t>
+          <t>14/05/2026 15:23:00</t>
         </is>
       </c>
       <c r="W51" s="8" t="inlineStr">
         <is>
-          <t>04/06/2026 09:57:00</t>
+          <t>25/05/2026 15:23:00</t>
         </is>
       </c>
       <c r="X51" s="8" t="inlineStr">
         <is>
-          <t>21/05/2026 10:40:00</t>
+          <t>29/05/2026 18:57:00</t>
         </is>
       </c>
       <c r="Y51" s="8" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="AA51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-21 10:40:25.226 : [1]Nhận xét | Comments || N/A || No information attached </t>
+          <t xml:space="preserve">2026-05-25 09:31:31.052 : [1]Nhận xét | Comments || N/A || On Friday 22/05 it was informed that need feedback from partners, so cannot process this SR. 2026-05-28 08:57:00.996 : [1]Nhận xét | Comments || N/A || Please not reopen feedback came yesterday, it affects KPI need time to process </t>
         </is>
       </c>
       <c r="AB51" s="8" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="AF51" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="AG51" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>*</t>
         </is>
       </c>
       <c r="AH51" s="8" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="AI51" s="8" t="inlineStr">
         <is>
-          <t>No information attached</t>
+          <t>On Friday 22/05 it was informed that need feedback from partners, so cannot process this SR.,Please not reopen feedback came yesterday, it affects KPI need time to process</t>
         </is>
       </c>
       <c r="AJ51" s="8" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260602_1353904</t>
+          <t>SR_VTP_20260526_1351468</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -8919,22 +8919,22 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>OFICIO N° 7314-2026-MTC/19.03 / INFORMATIVO</t>
+          <t>Test channel 28MHz (Ceragon) SAN2021-HUN5003_1</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Evaluated</t>
+          <t>Assigned Planning</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>vtp_fernando.munoz</t>
+          <t>vtp_diana.idrugo</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Cable Operations Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -8954,17 +8954,17 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
@@ -8979,22 +8979,22 @@
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>VTP_CABLE OPERATIONS</t>
+          <t>VTP_MICROWAVE</t>
         </is>
       </c>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>Review letters of notification/impact about BITEL optical cable</t>
+          <t>MW_RESTRUCTURE NETWORK</t>
         </is>
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>vtp_jesus.gonzales.1</t>
+          <t>vtp_kathy.valle</t>
         </is>
       </c>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|International Business VTP</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -9004,27 +9004,27 @@
       </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
-          <t>02/06/2026 11:11:00</t>
+          <t>26/05/2026 12:35:00</t>
         </is>
       </c>
       <c r="V52" s="8" t="inlineStr">
         <is>
-          <t>02/06/2026 11:32:00</t>
+          <t>26/05/2026 14:30:00</t>
         </is>
       </c>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>11/06/2026 11:32:00</t>
+          <t>02/06/2026 14:30:00</t>
         </is>
       </c>
       <c r="X52" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 11:30:00</t>
+          <t>03/06/2026 17:44:00</t>
         </is>
       </c>
       <c r="Y52" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>CR_NORMAL_TRANSMISSION_20025266410</t>
         </is>
       </c>
       <c r="Z52" s="8" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="AA52" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">2026-05-27 17:27:52.24 : [1]Nhận xét | Comments || N/A || Test channel 28MHz (Ceragon) SAN2021-HUN5003_1 </t>
         </is>
       </c>
       <c r="AB52" s="8" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AI52" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>Test channel 28MHz (Ceragon) SAN2021-HUN5003_1</t>
         </is>
       </c>
       <c r="AJ52" s="8" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260514_1348235</t>
+          <t>SR_VTP_20260529_1352959</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -9109,84 +9109,84 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>TECHNICAL EVALUATION : PJ0226_1567_VPN - 042026/VTPr-PJ - ACCESSORIES</t>
+          <t>. CAJ0059-CAJ0345   * Upgrade by config 112Mhz SIAEALFOPLUS2</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Evaluated</t>
+          <t>Assigned Planning</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>vtp_alvaro.martinez</t>
+          <t>vtp_luis.anthony</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="inlineStr">
+        <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N53" s="8" t="inlineStr">
+        <is>
+          <t>Out of deadline</t>
+        </is>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>VTP_TRANSMISSION</t>
+        </is>
+      </c>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t>VTP_MICROWAVE</t>
+        </is>
+      </c>
+      <c r="Q53" s="8" t="inlineStr">
+        <is>
+          <t>MW_RESTRUCTURE NETWORK</t>
+        </is>
+      </c>
+      <c r="R53" s="8" t="inlineStr">
+        <is>
+          <t>vtp_kathy.valle</t>
+        </is>
+      </c>
+      <c r="S53" s="8" t="inlineStr">
+        <is>
           <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K53" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="M53" s="8" t="inlineStr">
-        <is>
-          <t>In deadline</t>
-        </is>
-      </c>
-      <c r="N53" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
-      <c r="O53" s="8" t="inlineStr">
-        <is>
-          <t>VTP_TRANSMISSION</t>
-        </is>
-      </c>
-      <c r="P53" s="8" t="inlineStr">
-        <is>
-          <t>VTP_Design/Planning/Ensure Trans infra</t>
-        </is>
-      </c>
-      <c r="Q53" s="8" t="inlineStr">
-        <is>
-          <t>Technical review for biddings</t>
-        </is>
-      </c>
-      <c r="R53" s="8" t="inlineStr">
-        <is>
-          <t>vtp_judith.araujo</t>
-        </is>
-      </c>
-      <c r="S53" s="8" t="inlineStr">
-        <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Investment Department</t>
-        </is>
-      </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
           <t>Peru (VTP)</t>
@@ -9194,27 +9194,27 @@
       </c>
       <c r="U53" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 14:53:00</t>
+          <t>29/05/2026 17:04:00</t>
         </is>
       </c>
       <c r="V53" s="8" t="inlineStr">
         <is>
-          <t>14/05/2026 15:23:00</t>
+          <t>29/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="W53" s="8" t="inlineStr">
         <is>
-          <t>25/05/2026 15:23:00</t>
+          <t>05/06/2026 17:28:00</t>
         </is>
       </c>
       <c r="X53" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 18:57:00</t>
+          <t>29/05/2026 17:49:00</t>
         </is>
       </c>
       <c r="Y53" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>CR_NORMAL_TRANSMISSION_20025270215</t>
         </is>
       </c>
       <c r="Z53" s="8" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="AA53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25 09:31:31.052 : [1]Nhận xét | Comments || N/A || On Friday 22/05 it was informed that need feedback from partners, so cannot process this SR. 2026-05-28 08:57:00.996 : [1]Nhận xét | Comments || N/A || Please not reopen feedback came yesterday, it affects KPI need time to process </t>
+          <t xml:space="preserve">2026-05-29 17:48:48.653 : [1]Nhận xét | Comments || N/A || Is an upgrade. </t>
         </is>
       </c>
       <c r="AB53" s="8" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="AF53" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="AG53" s="8" t="inlineStr">
         <is>
-          <t>*</t>
+          <t/>
         </is>
       </c>
       <c r="AH53" s="8" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AI53" s="8" t="inlineStr">
         <is>
-          <t>On Friday 22/05 it was informed that need feedback from partners, so cannot process this SR.,Please not reopen feedback came yesterday, it affects KPI need time to process</t>
+          <t>Is an upgrade.</t>
         </is>
       </c>
       <c r="AJ53" s="8" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260526_1351468</t>
+          <t>SR_VTP_20260529_1352904</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -9299,22 +9299,22 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Test channel 28MHz (Ceragon) SAN2021-HUN5003_1</t>
+          <t>KCS Testing at MInka WH for IMP-3007  01/2026/VTPr-THOAIANH/OPTICAL ACCESSORIES ML 2026</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Assigned Planning</t>
+          <t>Concluded</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>vtp_diana.idrugo</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -9339,19 +9339,19 @@
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N54" s="8" t="inlineStr">
+        <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
       <c r="O54" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
@@ -9359,22 +9359,22 @@
       </c>
       <c r="P54" s="8" t="inlineStr">
         <is>
-          <t>VTP_MICROWAVE</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q54" s="8" t="inlineStr">
         <is>
-          <t>MW_RESTRUCTURE NETWORK</t>
+          <t>KCS for new goods of Transmission</t>
         </is>
       </c>
       <c r="R54" s="8" t="inlineStr">
         <is>
-          <t>vtp_kathy.valle</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
@@ -9384,37 +9384,37 @@
       </c>
       <c r="U54" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 12:35:00</t>
+          <t>29/05/2026 15:21:00</t>
         </is>
       </c>
       <c r="V54" s="8" t="inlineStr">
         <is>
-          <t>26/05/2026 14:30:00</t>
+          <t>29/05/2026 15:49:00</t>
         </is>
       </c>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>02/06/2026 14:30:00</t>
+          <t>05/06/2026 15:49:00</t>
         </is>
       </c>
       <c r="X54" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 17:44:00</t>
+          <t>03/06/2026 22:40:00</t>
         </is>
       </c>
       <c r="Y54" s="8" t="inlineStr">
         <is>
-          <t>CR_NORMAL_TRANSMISSION_20025266410</t>
+          <t/>
         </is>
       </c>
       <c r="Z54" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>3.30 Days</t>
         </is>
       </c>
       <c r="AA54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27 17:27:52.24 : [1]Nhận xét | Comments || N/A || Test channel 28MHz (Ceragon) SAN2021-HUN5003_1 </t>
+          <t/>
         </is>
       </c>
       <c r="AB54" s="8" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="AI54" s="8" t="inlineStr">
         <is>
-          <t>Test channel 28MHz (Ceragon) SAN2021-HUN5003_1</t>
+          <t/>
         </is>
       </c>
       <c r="AJ54" s="8" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352959</t>
+          <t>SR_VTP_20260529_1352971</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -9489,22 +9489,22 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>. CAJ0059-CAJ0345   * Upgrade by config 112Mhz SIAEALFOPLUS2</t>
+          <t>KCS Testing at MInka WH for IMP-3028 PO_02-01/2026/F/VTPr-2PT/FERRETERIA AMA</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Assigned Planning</t>
+          <t>Concluded</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>vtp_luis.anthony</t>
+          <t>vtp_alvaro.martinez</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Microwave Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M55" s="8" t="inlineStr">
@@ -9549,22 +9549,22 @@
       </c>
       <c r="P55" s="8" t="inlineStr">
         <is>
-          <t>VTP_MICROWAVE</t>
+          <t>VTP_Design/Planning/Ensure Trans infra</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr">
         <is>
-          <t>MW_RESTRUCTURE NETWORK</t>
+          <t>KCS for new goods of Transmission</t>
         </is>
       </c>
       <c r="R55" s="8" t="inlineStr">
         <is>
-          <t>vtp_kathy.valle</t>
+          <t>vtp_jonathan.sialer</t>
         </is>
       </c>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|Technical Center VTP|VTP Transmission Department|Design&amp;Planing Division</t>
+          <t>VIETTEL GROUP|Bitel (Viettel Peru Company - VTP)|VTP Asset Management Department|KCS Division</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
@@ -9574,37 +9574,37 @@
       </c>
       <c r="U55" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:04:00</t>
+          <t>29/05/2026 17:20:00</t>
         </is>
       </c>
       <c r="V55" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:28:00</t>
+          <t>29/05/2026 17:48:00</t>
         </is>
       </c>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>05/06/2026 17:28:00</t>
+          <t>08/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X55" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:49:00</t>
+          <t>03/06/2026 22:39:00</t>
         </is>
       </c>
       <c r="Y55" s="8" t="inlineStr">
         <is>
-          <t>CR_NORMAL_TRANSMISSION_20025270215</t>
+          <t/>
         </is>
       </c>
       <c r="Z55" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>3.22 Days</t>
         </is>
       </c>
       <c r="AA55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29 17:48:48.653 : [1]Nhận xét | Comments || N/A || Is an upgrade. </t>
+          <t/>
         </is>
       </c>
       <c r="AB55" s="8" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AI55" s="8" t="inlineStr">
         <is>
-          <t>Is an upgrade.</t>
+          <t/>
         </is>
       </c>
       <c r="AJ55" s="8" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260528_1352368</t>
+          <t>SR_VTP_20260528_1352386</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>JUN0084-JUN0085_OLD</t>
+          <t>AYA0128-JUN0283_OLD</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="U87" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 15:21:00</t>
+          <t>28/05/2026 15:22:00</t>
         </is>
       </c>
       <c r="V87" s="8" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260528_1352386</t>
+          <t>SR_VTP_20260528_1352368</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>AYA0128-JUN0283_OLD</t>
+          <t>JUN0084-JUN0085_OLD</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="U88" s="8" t="inlineStr">
         <is>
-          <t>28/05/2026 15:22:00</t>
+          <t>28/05/2026 15:21:00</t>
         </is>
       </c>
       <c r="V88" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/5/26, 4:30 PM</t>
+          <t>Date Export: 6/5/26, 4:31 PM</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M55" s="8" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/5/26, 7:30 PM</t>
+          <t>Date Export: 6/6/26, 7:38 PM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260603_1354512</t>
+          <t>SR_VTP_20260603_1354511</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>ARE0270-ARE0354_1, Reconfigure link to work in parallel</t>
+          <t>LAL0150-LAL0393</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>vtp_luis.anthony</t>
+          <t>vtp_diana.idrugo</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="U54" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 17:31:00</t>
+          <t>03/06/2026 17:22:00</t>
         </is>
       </c>
       <c r="V54" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 17:58:00</t>
+          <t>03/06/2026 17:52:00</t>
         </is>
       </c>
       <c r="W54" s="8" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="X54" s="8" t="inlineStr">
         <is>
-          <t>04/06/2026 16:50:00</t>
+          <t>04/06/2026 15:20:00</t>
         </is>
       </c>
       <c r="Y54" s="8" t="inlineStr">
         <is>
-          <t>CR_NORMAL_TRANSMISSION_20025282809</t>
+          <t/>
         </is>
       </c>
       <c r="Z54" s="8" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AA54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 12:10:25.064 : [1]Nhận xét | Comments || N/A || Reconfigure link in parallel. </t>
+          <t xml:space="preserve">2026-06-04 12:24:50.247 : [1]Nhận xét | Comments || N/A || test de interfrencia </t>
         </is>
       </c>
       <c r="AB54" s="8" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="AI54" s="8" t="inlineStr">
         <is>
-          <t>Reconfigure link in parallel.</t>
+          <t>test de interfrencia</t>
         </is>
       </c>
       <c r="AJ54" s="8" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260603_1354511</t>
+          <t>SR_VTP_20260529_1352959</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>LAL0150-LAL0393</t>
+          <t>. CAJ0059-CAJ0345   * Upgrade by config 112Mhz SIAEALFOPLUS2</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>vtp_diana.idrugo</t>
+          <t>vtp_luis.anthony</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>In due</t>
+          <t>Over due</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M55" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
@@ -9574,27 +9574,27 @@
       </c>
       <c r="U55" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 17:22:00</t>
+          <t>29/05/2026 17:04:00</t>
         </is>
       </c>
       <c r="V55" s="8" t="inlineStr">
         <is>
-          <t>03/06/2026 17:52:00</t>
+          <t>29/05/2026 17:28:00</t>
         </is>
       </c>
       <c r="W55" s="8" t="inlineStr">
         <is>
-          <t>11/06/2026 08:00:00</t>
+          <t>05/06/2026 17:28:00</t>
         </is>
       </c>
       <c r="X55" s="8" t="inlineStr">
         <is>
-          <t>04/06/2026 15:20:00</t>
+          <t>04/06/2026 14:15:00</t>
         </is>
       </c>
       <c r="Y55" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>CR_NORMAL_TRANSMISSION_20025270215</t>
         </is>
       </c>
       <c r="Z55" s="8" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="AA55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 12:24:50.247 : [1]Nhận xét | Comments || N/A || test de interfrencia </t>
+          <t xml:space="preserve">2026-05-29 17:48:48.653 : [1]Nhận xét | Comments || N/A || Is an upgrade. </t>
         </is>
       </c>
       <c r="AB55" s="8" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AI55" s="8" t="inlineStr">
         <is>
-          <t>test de interfrencia</t>
+          <t>Is an upgrade.</t>
         </is>
       </c>
       <c r="AJ55" s="8" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>SR_VTP_20260529_1352959</t>
+          <t>SR_VTP_20260603_1354512</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -9679,12 +9679,12 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>. CAJ0059-CAJ0345   * Upgrade by config 112Mhz SIAEALFOPLUS2</t>
+          <t>ARE0270-ARE0354_1, Reconfigure link to work in parallel</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Concluded</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Over due</t>
+          <t/>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
@@ -9719,19 +9719,19 @@
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr">
         <is>
+          <t>In deadline</t>
+        </is>
+      </c>
+      <c r="N56" s="8" t="inlineStr">
+        <is>
           <t>Out of deadline</t>
         </is>
       </c>
-      <c r="N56" s="8" t="inlineStr">
-        <is>
-          <t>Out of deadline</t>
-        </is>
-      </c>
       <c r="O56" s="8" t="inlineStr">
         <is>
           <t>VTP_TRANSMISSION</t>
@@ -9764,37 +9764,37 @@
       </c>
       <c r="U56" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:04:00</t>
+          <t>03/06/2026 17:31:00</t>
         </is>
       </c>
       <c r="V56" s="8" t="inlineStr">
         <is>
-          <t>29/05/2026 17:28:00</t>
+          <t>03/06/2026 17:58:00</t>
         </is>
       </c>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>05/06/2026 17:28:00</t>
+          <t>11/06/2026 08:00:00</t>
         </is>
       </c>
       <c r="X56" s="8" t="inlineStr">
         <is>
-          <t>04/06/2026 14:15:00</t>
+          <t>05/06/2026 19:35:00</t>
         </is>
       </c>
       <c r="Y56" s="8" t="inlineStr">
         <is>
-          <t>CR_NORMAL_TRANSMISSION_20025270215</t>
+          <t>CR_NORMAL_TRANSMISSION_20025282809</t>
         </is>
       </c>
       <c r="Z56" s="8" t="inlineStr">
         <is>
-          <t/>
+          <t>2.09 Days</t>
         </is>
       </c>
       <c r="AA56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-29 17:48:48.653 : [1]Nhận xét | Comments || N/A || Is an upgrade. </t>
+          <t xml:space="preserve">2026-06-04 12:10:25.064 : [1]Nhận xét | Comments || N/A || Reconfigure link in parallel. </t>
         </is>
       </c>
       <c r="AB56" s="8" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AI56" s="8" t="inlineStr">
         <is>
-          <t>Is an upgrade.</t>
+          <t>Reconfigure link in parallel.</t>
         </is>
       </c>
       <c r="AJ56" s="8" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N72" s="8" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M81" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N86" s="8" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N93" s="8" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N104" s="8" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N117" s="8" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N127" s="8" t="inlineStr">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N131" s="8" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N134" s="8" t="inlineStr">
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N159" s="8" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N189" s="8" t="inlineStr">
@@ -37694,7 +37694,7 @@
       </c>
       <c r="M202" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N202" s="8" t="inlineStr">
@@ -38264,7 +38264,7 @@
       </c>
       <c r="M205" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N205" s="8" t="inlineStr">
@@ -42286,7 +42286,7 @@
       </c>
       <c r="M226" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N226" s="8" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="M228" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N228" s="8" t="inlineStr">
@@ -44270,7 +44270,7 @@
       </c>
       <c r="M236" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N236" s="8" t="inlineStr">
@@ -46172,7 +46172,7 @@
       </c>
       <c r="M246" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N246" s="8" t="inlineStr">
@@ -65652,7 +65652,7 @@
       </c>
       <c r="M348" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N348" s="8" t="inlineStr">
@@ -70242,7 +70242,7 @@
       </c>
       <c r="M372" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N372" s="8" t="inlineStr">
@@ -70432,7 +70432,7 @@
       </c>
       <c r="M373" s="8" t="inlineStr">
         <is>
-          <t>In deadline</t>
+          <t>Out of deadline</t>
         </is>
       </c>
       <c r="N373" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/6/26, 7:38 PM</t>
+          <t>Date Export: 6/6/26, 7:39 PM</t>
         </is>
       </c>
     </row>

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/9/26, 7:36 PM</t>
+          <t>Date Export: 6/9/26, 7:35 PM</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/9/26, 8:28 AM</t>
+          <t>Date Export: 6/8/26, 7:36 PM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/12/26, 4:35 PM</t>
+          <t>Date Export: 6/12/26, 4:36 PM</t>
         </is>
       </c>
     </row>

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/13/26, 7:30 PM</t>
+          <t>Date Export: 6/13/26, 7:31 PM</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">

--- a/SR_REPORT.xlsx
+++ b/SR_REPORT.xlsx
@@ -535,7 +535,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Date Export: 6/13/26, 7:31 PM</t>
+          <t>Date Export: 6/15/26, 8:12 AM</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="M53" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="M63" s="8" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="M65" s="8" t="inlineStr">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N78" s="8" t="inlineStr">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N99" s="8" t="inlineStr">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N104" s="8" t="inlineStr">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N110" s="8" t="inlineStr">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N118" s="8" t="inlineStr">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N119" s="8" t="inlineStr">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N120" s="8" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N124" s="8" t="inlineStr">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N139" s="8" t="inlineStr">
@@ -26530,7 +26530,7 @@
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N144" s="8" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N176" s="8" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N180" s="8" t="inlineStr">
@@ -34994,7 +34994,7 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N188" s="8" t="inlineStr">
@@ -35184,7 +35184,7 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N189" s="8" t="inlineStr">
@@ -36704,7 +36704,7 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N197" s="8" t="inlineStr">
@@ -41300,7 +41300,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N221" s="8" t="inlineStr">
@@ -47248,7 +47248,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N252" s="8" t="inlineStr">
@@ -49750,7 +49750,7 @@
       </c>
       <c r="M265" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N265" s="8" t="inlineStr">
@@ -50320,7 +50320,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N268" s="8" t="inlineStr">
@@ -54540,7 +54540,7 @@
       </c>
       <c r="M290" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N290" s="8" t="inlineStr">
@@ -54756,7 +54756,7 @@
       </c>
       <c r="M291" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N291" s="8" t="inlineStr">
@@ -56136,7 +56136,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N298" s="8" t="inlineStr">
@@ -58228,7 +58228,7 @@
       </c>
       <c r="M309" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N309" s="8" t="inlineStr">
@@ -77708,7 +77708,7 @@
       </c>
       <c r="M411" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N411" s="8" t="inlineStr">
@@ -82298,7 +82298,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N435" s="8" t="inlineStr">
@@ -82488,7 +82488,7 @@
       </c>
       <c r="M436" s="8" t="inlineStr">
         <is>
-          <t>Out of deadline</t>
+          <t>In deadline</t>
         </is>
       </c>
       <c r="N436" s="8" t="inlineStr">
